--- a/raw/RT.xlsx
+++ b/raw/RT.xlsx
@@ -406,242 +406,242 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>00.30</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01.00</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>01.30</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>02.00</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>02.30</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03.00</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>03.30</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04.00</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04.30</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05.00</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>05.30</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06.00</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06.30</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07.00</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07.30</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08.00</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08.30</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09.00</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09.30</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12.30</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15.30</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16.30</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17.30</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19.30</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21.30</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22.30</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23.30</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>24.00</t>
         </is>
       </c>
     </row>
@@ -816,37 +816,37 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1017,31 +1017,31 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
@@ -1050,7 +1050,7 @@
         <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1223,40 +1223,40 @@
         <v>371.5</v>
       </c>
       <c r="C9" t="n">
+        <v>262</v>
+      </c>
+      <c r="D9" t="n">
+        <v>272</v>
+      </c>
+      <c r="E9" t="n">
+        <v>259</v>
+      </c>
+      <c r="F9" t="n">
+        <v>252</v>
+      </c>
+      <c r="G9" t="n">
+        <v>247</v>
+      </c>
+      <c r="H9" t="n">
+        <v>258</v>
+      </c>
+      <c r="I9" t="n">
+        <v>252</v>
+      </c>
+      <c r="J9" t="n">
+        <v>257</v>
+      </c>
+      <c r="K9" t="n">
+        <v>257</v>
+      </c>
+      <c r="L9" t="n">
+        <v>262</v>
+      </c>
+      <c r="M9" t="n">
         <v>248</v>
       </c>
-      <c r="D9" t="n">
-        <v>250</v>
-      </c>
-      <c r="E9" t="n">
-        <v>245</v>
-      </c>
-      <c r="F9" t="n">
-        <v>244</v>
-      </c>
-      <c r="G9" t="n">
-        <v>245</v>
-      </c>
-      <c r="H9" t="n">
-        <v>236</v>
-      </c>
-      <c r="I9" t="n">
-        <v>244</v>
-      </c>
-      <c r="J9" t="n">
-        <v>219</v>
-      </c>
-      <c r="K9" t="n">
-        <v>228</v>
-      </c>
-      <c r="L9" t="n">
-        <v>263</v>
-      </c>
-      <c r="M9" t="n">
-        <v>253</v>
-      </c>
       <c r="N9" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1429,40 +1429,40 @@
         <v>371.5</v>
       </c>
       <c r="C11" t="n">
+        <v>265</v>
+      </c>
+      <c r="D11" t="n">
         <v>253</v>
       </c>
-      <c r="D11" t="n">
-        <v>260</v>
-      </c>
       <c r="E11" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F11" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G11" t="n">
+        <v>250</v>
+      </c>
+      <c r="H11" t="n">
+        <v>253</v>
+      </c>
+      <c r="I11" t="n">
+        <v>251</v>
+      </c>
+      <c r="J11" t="n">
         <v>256</v>
       </c>
-      <c r="H11" t="n">
-        <v>250</v>
-      </c>
-      <c r="I11" t="n">
-        <v>260</v>
-      </c>
-      <c r="J11" t="n">
-        <v>260</v>
-      </c>
       <c r="K11" t="n">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="L11" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="M11" t="n">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="N11" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1635,40 +1635,40 @@
         <v>371.5</v>
       </c>
       <c r="C13" t="n">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="D13" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E13" t="n">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="F13" t="n">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="G13" t="n">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="H13" t="n">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="I13" t="n">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="J13" t="n">
         <v>262</v>
       </c>
       <c r="K13" t="n">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="L13" t="n">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M13" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="N13" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1841,40 +1841,40 @@
         <v>575.2</v>
       </c>
       <c r="C15" t="n">
-        <v>329</v>
+        <v>413</v>
       </c>
       <c r="D15" t="n">
-        <v>334</v>
+        <v>404</v>
       </c>
       <c r="E15" t="n">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="F15" t="n">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="G15" t="n">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="H15" t="n">
-        <v>380</v>
+        <v>415</v>
       </c>
       <c r="I15" t="n">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="J15" t="n">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="K15" t="n">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="L15" t="n">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="M15" t="n">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="N15" t="n">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2047,40 +2047,40 @@
         <v>575.2</v>
       </c>
       <c r="C17" t="n">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="D17" t="n">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="E17" t="n">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="F17" t="n">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="G17" t="n">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="H17" t="n">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="I17" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="J17" t="n">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="K17" t="n">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="L17" t="n">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="M17" t="n">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="N17" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2253,40 +2253,40 @@
         <v>575.2</v>
       </c>
       <c r="C19" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D19" t="n">
-        <v>399</v>
+        <v>334</v>
       </c>
       <c r="E19" t="n">
-        <v>392</v>
+        <v>333</v>
       </c>
       <c r="F19" t="n">
-        <v>396</v>
+        <v>335</v>
       </c>
       <c r="G19" t="n">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="H19" t="n">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="I19" t="n">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="J19" t="n">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="K19" t="n">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="L19" t="n">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="M19" t="n">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="N19" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2459,40 +2459,40 @@
         <v>172.5</v>
       </c>
       <c r="C21" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D21" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="E21" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="G21" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="H21" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="I21" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="J21" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="K21" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="L21" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="M21" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="N21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2665,37 +2665,37 @@
         <v>125</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2871,40 +2871,40 @@
         <v>125</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3080,37 +3080,37 @@
         <v>81</v>
       </c>
       <c r="D27" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E27" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F27" t="n">
+        <v>84</v>
+      </c>
+      <c r="G27" t="n">
+        <v>84</v>
+      </c>
+      <c r="H27" t="n">
+        <v>85</v>
+      </c>
+      <c r="I27" t="n">
+        <v>85</v>
+      </c>
+      <c r="J27" t="n">
         <v>87</v>
       </c>
-      <c r="G27" t="n">
+      <c r="K27" t="n">
+        <v>89</v>
+      </c>
+      <c r="L27" t="n">
+        <v>87</v>
+      </c>
+      <c r="M27" t="n">
         <v>81</v>
       </c>
-      <c r="H27" t="n">
-        <v>83</v>
-      </c>
-      <c r="I27" t="n">
-        <v>81</v>
-      </c>
-      <c r="J27" t="n">
-        <v>84</v>
-      </c>
-      <c r="K27" t="n">
-        <v>82</v>
-      </c>
-      <c r="L27" t="n">
-        <v>85</v>
-      </c>
-      <c r="M27" t="n">
-        <v>84</v>
-      </c>
       <c r="N27" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3313,10 +3313,10 @@
         <v>40</v>
       </c>
       <c r="M29" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N29" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>125</v>
       </c>
       <c r="C31" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D31" t="n">
         <v>85</v>
@@ -3498,10 +3498,10 @@
         <v>85</v>
       </c>
       <c r="F31" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G31" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H31" t="n">
         <v>84</v>
@@ -3510,19 +3510,19 @@
         <v>85</v>
       </c>
       <c r="J31" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K31" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L31" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M31" t="n">
         <v>85</v>
       </c>
       <c r="N31" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4107,40 +4107,40 @@
         <v>250</v>
       </c>
       <c r="C37" t="n">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="D37" t="n">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="E37" t="n">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="F37" t="n">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="G37" t="n">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="H37" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="I37" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="J37" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="K37" t="n">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="L37" t="n">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="M37" t="n">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="N37" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4313,40 +4313,40 @@
         <v>235</v>
       </c>
       <c r="C39" t="n">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="D39" t="n">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="E39" t="n">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="F39" t="n">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="G39" t="n">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="H39" t="n">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="I39" t="n">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="J39" t="n">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="K39" t="n">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="L39" t="n">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="M39" t="n">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="N39" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -4519,40 +4519,40 @@
         <v>235</v>
       </c>
       <c r="C41" t="n">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="D41" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="E41" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="F41" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="G41" t="n">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="H41" t="n">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="I41" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="J41" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="K41" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="L41" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="M41" t="n">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="N41" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -4931,37 +4931,37 @@
         <v>283.25</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>57</v>
       </c>
       <c r="N49" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         <v>57</v>
       </c>
       <c r="N51" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -5761,10 +5761,10 @@
         <v>56</v>
       </c>
       <c r="E53" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F53" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G53" t="n">
         <v>56</v>
@@ -5779,7 +5779,7 @@
         <v>56</v>
       </c>
       <c r="K53" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L53" t="n">
         <v>57</v>
@@ -5788,7 +5788,7 @@
         <v>57</v>
       </c>
       <c r="N53" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7197,40 +7197,40 @@
         <v>236</v>
       </c>
       <c r="C67" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D67" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E67" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F67" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G67" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H67" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I67" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J67" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K67" t="n">
+        <v>62</v>
+      </c>
+      <c r="L67" t="n">
+        <v>62</v>
+      </c>
+      <c r="M67" t="n">
         <v>63</v>
       </c>
-      <c r="L67" t="n">
-        <v>64</v>
-      </c>
-      <c r="M67" t="n">
-        <v>64</v>
-      </c>
       <c r="N67" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -7403,37 +7403,37 @@
         <v>212</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -7609,40 +7609,40 @@
         <v>212</v>
       </c>
       <c r="C71" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D71" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E71" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F71" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G71" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H71" t="n">
         <v>105</v>
       </c>
       <c r="I71" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J71" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K71" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L71" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M71" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N71" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -7815,40 +7815,40 @@
         <v>280</v>
       </c>
       <c r="C73" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D73" t="n">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="E73" t="n">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F73" t="n">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="G73" t="n">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="H73" t="n">
+        <v>255</v>
+      </c>
+      <c r="I73" t="n">
+        <v>252</v>
+      </c>
+      <c r="J73" t="n">
         <v>261</v>
       </c>
-      <c r="I73" t="n">
-        <v>275</v>
-      </c>
-      <c r="J73" t="n">
-        <v>263</v>
-      </c>
       <c r="K73" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="L73" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M73" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="N73" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -8021,40 +8021,40 @@
         <v>280</v>
       </c>
       <c r="C75" t="n">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="D75" t="n">
-        <v>281</v>
+        <v>250</v>
       </c>
       <c r="E75" t="n">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="F75" t="n">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="G75" t="n">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="H75" t="n">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="I75" t="n">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="J75" t="n">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="K75" t="n">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="L75" t="n">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="M75" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="N75" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -8227,40 +8227,40 @@
         <v>540</v>
       </c>
       <c r="C77" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="D77" t="n">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="E77" t="n">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="F77" t="n">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="G77" t="n">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="H77" t="n">
-        <v>399</v>
+        <v>434</v>
       </c>
       <c r="I77" t="n">
-        <v>396</v>
+        <v>477</v>
       </c>
       <c r="J77" t="n">
-        <v>404</v>
+        <v>478</v>
       </c>
       <c r="K77" t="n">
-        <v>397</v>
+        <v>467</v>
       </c>
       <c r="L77" t="n">
-        <v>405</v>
+        <v>469</v>
       </c>
       <c r="M77" t="n">
-        <v>406</v>
+        <v>468</v>
       </c>
       <c r="N77" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -8433,40 +8433,40 @@
         <v>323</v>
       </c>
       <c r="C79" t="n">
+        <v>270</v>
+      </c>
+      <c r="D79" t="n">
         <v>262</v>
       </c>
-      <c r="D79" t="n">
-        <v>261</v>
-      </c>
       <c r="E79" t="n">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="F79" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G79" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="H79" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="I79" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J79" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K79" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L79" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M79" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N79" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -8639,40 +8639,40 @@
         <v>323</v>
       </c>
       <c r="C81" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D81" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E81" t="n">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="F81" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G81" t="n">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="H81" t="n">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="I81" t="n">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="J81" t="n">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="K81" t="n">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="L81" t="n">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="M81" t="n">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="N81" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -8845,40 +8845,40 @@
         <v>323</v>
       </c>
       <c r="C83" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D83" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E83" t="n">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F83" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G83" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H83" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="I83" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J83" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="K83" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="L83" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="M83" t="n">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="N83" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -9051,37 +9051,37 @@
         <v>280</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -9257,40 +9257,40 @@
         <v>280</v>
       </c>
       <c r="C87" t="n">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D87" t="n">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="E87" t="n">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="F87" t="n">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="G87" t="n">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="H87" t="n">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="I87" t="n">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="J87" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="K87" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="L87" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="M87" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N87" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -9463,40 +9463,40 @@
         <v>280</v>
       </c>
       <c r="C89" t="n">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="D89" t="n">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="E89" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="F89" t="n">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="G89" t="n">
+        <v>274</v>
+      </c>
+      <c r="H89" t="n">
+        <v>273</v>
+      </c>
+      <c r="I89" t="n">
+        <v>275</v>
+      </c>
+      <c r="J89" t="n">
+        <v>276</v>
+      </c>
+      <c r="K89" t="n">
         <v>271</v>
       </c>
-      <c r="H89" t="n">
-        <v>270</v>
-      </c>
-      <c r="I89" t="n">
-        <v>268</v>
-      </c>
-      <c r="J89" t="n">
-        <v>271</v>
-      </c>
-      <c r="K89" t="n">
-        <v>269</v>
-      </c>
       <c r="L89" t="n">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="M89" t="n">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="N89" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -9669,40 +9669,40 @@
         <v>293</v>
       </c>
       <c r="C91" t="n">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="D91" t="n">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="E91" t="n">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="F91" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="G91" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="H91" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="I91" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="J91" t="n">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="K91" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="L91" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="M91" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N91" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -9875,40 +9875,40 @@
         <v>371.5</v>
       </c>
       <c r="C93" t="n">
-        <v>167</v>
+        <v>292</v>
       </c>
       <c r="D93" t="n">
-        <v>168</v>
+        <v>289</v>
       </c>
       <c r="E93" t="n">
-        <v>176</v>
+        <v>286</v>
       </c>
       <c r="F93" t="n">
-        <v>177</v>
+        <v>292</v>
       </c>
       <c r="G93" t="n">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="H93" t="n">
-        <v>171</v>
+        <v>278</v>
       </c>
       <c r="I93" t="n">
-        <v>175</v>
+        <v>262</v>
       </c>
       <c r="J93" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="K93" t="n">
-        <v>183</v>
+        <v>258</v>
       </c>
       <c r="L93" t="n">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="M93" t="n">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="N93" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>94</v>
       </c>
       <c r="D95" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E95" t="n">
         <v>94</v>
@@ -10108,13 +10108,13 @@
         <v>94</v>
       </c>
       <c r="L95" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M95" t="n">
         <v>94</v>
       </c>
       <c r="N95" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -10493,40 +10493,40 @@
         <v>124</v>
       </c>
       <c r="C99" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D99" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E99" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F99" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G99" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H99" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I99" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J99" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K99" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L99" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M99" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N99" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -10699,40 +10699,40 @@
         <v>90</v>
       </c>
       <c r="C101" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -11111,37 +11111,37 @@
         <v>100</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N105" t="n">
         <v>0</v>
@@ -11317,40 +11317,40 @@
         <v>70</v>
       </c>
       <c r="C107" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D107" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E107" t="n">
         <v>34</v>
       </c>
       <c r="F107" t="n">
+        <v>29</v>
+      </c>
+      <c r="G107" t="n">
+        <v>31</v>
+      </c>
+      <c r="H107" t="n">
         <v>30</v>
       </c>
-      <c r="G107" t="n">
+      <c r="I107" t="n">
         <v>30</v>
       </c>
-      <c r="H107" t="n">
-        <v>31</v>
-      </c>
-      <c r="I107" t="n">
-        <v>31</v>
-      </c>
       <c r="J107" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K107" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L107" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M107" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N107" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -11523,37 +11523,37 @@
         <v>235</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N109" t="n">
         <v>0</v>
@@ -11729,40 +11729,40 @@
         <v>235</v>
       </c>
       <c r="C111" t="n">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D111" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E111" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="F111" t="n">
+        <v>128</v>
+      </c>
+      <c r="G111" t="n">
+        <v>137</v>
+      </c>
+      <c r="H111" t="n">
+        <v>131</v>
+      </c>
+      <c r="I111" t="n">
         <v>136</v>
       </c>
-      <c r="G111" t="n">
-        <v>130</v>
-      </c>
-      <c r="H111" t="n">
-        <v>133</v>
-      </c>
-      <c r="I111" t="n">
-        <v>128</v>
-      </c>
       <c r="J111" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K111" t="n">
+        <v>131</v>
+      </c>
+      <c r="L111" t="n">
         <v>160</v>
       </c>
-      <c r="L111" t="n">
-        <v>132</v>
-      </c>
       <c r="M111" t="n">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="N111" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -11935,40 +11935,40 @@
         <v>70</v>
       </c>
       <c r="C113" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D113" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E113" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F113" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G113" t="n">
         <v>36</v>
       </c>
       <c r="H113" t="n">
+        <v>35</v>
+      </c>
+      <c r="I113" t="n">
+        <v>36</v>
+      </c>
+      <c r="J113" t="n">
+        <v>36</v>
+      </c>
+      <c r="K113" t="n">
         <v>37</v>
       </c>
-      <c r="I113" t="n">
-        <v>37</v>
-      </c>
-      <c r="J113" t="n">
-        <v>38</v>
-      </c>
-      <c r="K113" t="n">
+      <c r="L113" t="n">
+        <v>39</v>
+      </c>
+      <c r="M113" t="n">
         <v>40</v>
       </c>
-      <c r="L113" t="n">
-        <v>37</v>
-      </c>
-      <c r="M113" t="n">
-        <v>35</v>
-      </c>
       <c r="N113" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -12347,40 +12347,40 @@
         <v>165</v>
       </c>
       <c r="C117" t="n">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="D117" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E117" t="n">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="F117" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G117" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H117" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I117" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="J117" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="K117" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="L117" t="n">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="M117" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="N117" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -12553,40 +12553,40 @@
         <v>330</v>
       </c>
       <c r="C119" t="n">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="D119" t="n">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="E119" t="n">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="F119" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G119" t="n">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="H119" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="I119" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="J119" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="K119" t="n">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="L119" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="M119" t="n">
-        <v>152</v>
+        <v>236</v>
       </c>
       <c r="N119" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -12792,7 +12792,7 @@
         <v>64</v>
       </c>
       <c r="N121" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -12998,7 +12998,7 @@
         <v>64</v>
       </c>
       <c r="N123" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -13174,37 +13174,37 @@
         <v>62</v>
       </c>
       <c r="D125" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E125" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F125" t="n">
         <v>62</v>
       </c>
       <c r="G125" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H125" t="n">
         <v>62</v>
       </c>
       <c r="I125" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J125" t="n">
         <v>62</v>
       </c>
       <c r="K125" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L125" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M125" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N125" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -13581,40 +13581,40 @@
         <v>625</v>
       </c>
       <c r="C129" t="n">
+        <v>548</v>
+      </c>
+      <c r="D129" t="n">
         <v>551</v>
       </c>
-      <c r="D129" t="n">
-        <v>533</v>
-      </c>
       <c r="E129" t="n">
-        <v>503</v>
+        <v>551</v>
       </c>
       <c r="F129" t="n">
-        <v>498</v>
+        <v>547</v>
       </c>
       <c r="G129" t="n">
-        <v>500</v>
+        <v>547</v>
       </c>
       <c r="H129" t="n">
-        <v>498</v>
+        <v>545</v>
       </c>
       <c r="I129" t="n">
-        <v>497</v>
+        <v>549</v>
       </c>
       <c r="J129" t="n">
-        <v>501</v>
+        <v>568</v>
       </c>
       <c r="K129" t="n">
-        <v>500</v>
+        <v>603</v>
       </c>
       <c r="L129" t="n">
-        <v>540</v>
+        <v>601</v>
       </c>
       <c r="M129" t="n">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="N129" t="n">
-        <v>599</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -13787,40 +13787,40 @@
         <v>991</v>
       </c>
       <c r="C131" t="n">
-        <v>661</v>
+        <v>928</v>
       </c>
       <c r="D131" t="n">
-        <v>662</v>
+        <v>927</v>
       </c>
       <c r="E131" t="n">
-        <v>662</v>
+        <v>927</v>
       </c>
       <c r="F131" t="n">
-        <v>657</v>
+        <v>859</v>
       </c>
       <c r="G131" t="n">
-        <v>660</v>
+        <v>848</v>
       </c>
       <c r="H131" t="n">
-        <v>655</v>
+        <v>858</v>
       </c>
       <c r="I131" t="n">
-        <v>660</v>
+        <v>861</v>
       </c>
       <c r="J131" t="n">
-        <v>662</v>
+        <v>859</v>
       </c>
       <c r="K131" t="n">
-        <v>708</v>
+        <v>865</v>
       </c>
       <c r="L131" t="n">
-        <v>707</v>
+        <v>864</v>
       </c>
       <c r="M131" t="n">
-        <v>752</v>
+        <v>864</v>
       </c>
       <c r="N131" t="n">
-        <v>752</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -14199,40 +14199,40 @@
         <v>1000</v>
       </c>
       <c r="C135" t="n">
-        <v>766</v>
+        <v>926</v>
       </c>
       <c r="D135" t="n">
-        <v>765</v>
+        <v>927</v>
       </c>
       <c r="E135" t="n">
-        <v>766</v>
+        <v>926</v>
       </c>
       <c r="F135" t="n">
-        <v>770</v>
+        <v>917</v>
       </c>
       <c r="G135" t="n">
-        <v>707</v>
+        <v>826</v>
       </c>
       <c r="H135" t="n">
-        <v>700</v>
+        <v>814</v>
       </c>
       <c r="I135" t="n">
-        <v>701</v>
+        <v>743</v>
       </c>
       <c r="J135" t="n">
-        <v>700</v>
+        <v>738</v>
       </c>
       <c r="K135" t="n">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="L135" t="n">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="M135" t="n">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="N135" t="n">
-        <v>797</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -14405,40 +14405,40 @@
         <v>1000</v>
       </c>
       <c r="C137" t="n">
-        <v>765</v>
+        <v>925</v>
       </c>
       <c r="D137" t="n">
-        <v>764</v>
+        <v>925</v>
       </c>
       <c r="E137" t="n">
-        <v>766</v>
+        <v>924</v>
       </c>
       <c r="F137" t="n">
-        <v>765</v>
+        <v>908</v>
       </c>
       <c r="G137" t="n">
-        <v>701</v>
+        <v>817</v>
       </c>
       <c r="H137" t="n">
-        <v>699</v>
+        <v>793</v>
       </c>
       <c r="I137" t="n">
-        <v>699</v>
+        <v>734</v>
       </c>
       <c r="J137" t="n">
-        <v>700</v>
+        <v>736</v>
       </c>
       <c r="K137" t="n">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="L137" t="n">
+        <v>793</v>
+      </c>
+      <c r="M137" t="n">
         <v>797</v>
       </c>
-      <c r="M137" t="n">
-        <v>793</v>
-      </c>
       <c r="N137" t="n">
-        <v>793</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -14611,40 +14611,40 @@
         <v>14.48911</v>
       </c>
       <c r="C139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>2</v>
       </c>
       <c r="N143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -15127,37 +15127,37 @@
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N145" t="n">
         <v>0</v>
@@ -15364,7 +15364,7 @@
         <v>3</v>
       </c>
       <c r="N147" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -15772,7 +15772,7 @@
         <v>6</v>
       </c>
       <c r="N151" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -16563,7 +16563,7 @@
         <v>174.6</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -16593,7 +16593,7 @@
         <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N159" t="n">
         <v>0</v>
@@ -16802,7 +16802,7 @@
         <v>30</v>
       </c>
       <c r="N161" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -16993,7 +16993,7 @@
         <v>52</v>
       </c>
       <c r="I163" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J163" t="n">
         <v>52</v>
@@ -17008,7 +17008,7 @@
         <v>52</v>
       </c>
       <c r="N163" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -17184,7 +17184,7 @@
         <v>53</v>
       </c>
       <c r="D165" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E165" t="n">
         <v>53</v>
@@ -17193,7 +17193,7 @@
         <v>53</v>
       </c>
       <c r="G165" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H165" t="n">
         <v>53</v>
@@ -17214,7 +17214,7 @@
         <v>53</v>
       </c>
       <c r="N165" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -17387,7 +17387,7 @@
         <v>52</v>
       </c>
       <c r="C167" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D167" t="n">
         <v>46</v>
@@ -17399,7 +17399,7 @@
         <v>46</v>
       </c>
       <c r="G167" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H167" t="n">
         <v>46</v>
@@ -17408,19 +17408,19 @@
         <v>46</v>
       </c>
       <c r="J167" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K167" t="n">
         <v>46</v>
       </c>
       <c r="L167" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M167" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N167" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -17626,7 +17626,7 @@
         <v>42</v>
       </c>
       <c r="N169" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -17832,7 +17832,7 @@
         <v>42</v>
       </c>
       <c r="N171" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -19683,7 +19683,7 @@
         <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N189" t="n">
         <v>0</v>
@@ -20713,7 +20713,7 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N199" t="n">
         <v>0</v>
@@ -21095,40 +21095,40 @@
         <v>239.55</v>
       </c>
       <c r="C203" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D203" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E203" t="n">
         <v>49</v>
       </c>
       <c r="F203" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G203" t="n">
         <v>48</v>
       </c>
       <c r="H203" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I203" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J203" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K203" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L203" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M203" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N203" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -21528,7 +21528,7 @@
         <v>100</v>
       </c>
       <c r="J207" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K207" t="n">
         <v>100</v>
@@ -21540,7 +21540,7 @@
         <v>100</v>
       </c>
       <c r="N207" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -22331,37 +22331,37 @@
         <v>140</v>
       </c>
       <c r="C215" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D215" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E215" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F215" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G215" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H215" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I215" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J215" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K215" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N215" t="n">
         <v>0</v>
@@ -23161,34 +23161,34 @@
         <v>183</v>
       </c>
       <c r="E223" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F223" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G223" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H223" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I223" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J223" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K223" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="L223" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M223" t="n">
         <v>194</v>
       </c>
       <c r="N223" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -23361,40 +23361,40 @@
         <v>290</v>
       </c>
       <c r="C225" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="D225" t="n">
+        <v>186</v>
+      </c>
+      <c r="E225" t="n">
+        <v>186</v>
+      </c>
+      <c r="F225" t="n">
+        <v>180</v>
+      </c>
+      <c r="G225" t="n">
         <v>179</v>
       </c>
-      <c r="E225" t="n">
-        <v>179</v>
-      </c>
-      <c r="F225" t="n">
-        <v>177</v>
-      </c>
-      <c r="G225" t="n">
-        <v>181</v>
-      </c>
       <c r="H225" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I225" t="n">
+        <v>175</v>
+      </c>
+      <c r="J225" t="n">
+        <v>172</v>
+      </c>
+      <c r="K225" t="n">
+        <v>185</v>
+      </c>
+      <c r="L225" t="n">
         <v>178</v>
       </c>
-      <c r="J225" t="n">
-        <v>179</v>
-      </c>
-      <c r="K225" t="n">
-        <v>179</v>
-      </c>
-      <c r="L225" t="n">
-        <v>192</v>
-      </c>
       <c r="M225" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="N225" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -23567,40 +23567,40 @@
         <v>290</v>
       </c>
       <c r="C227" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D227" t="n">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="E227" t="n">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="F227" t="n">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="G227" t="n">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="H227" t="n">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="I227" t="n">
+        <v>179</v>
+      </c>
+      <c r="J227" t="n">
+        <v>177</v>
+      </c>
+      <c r="K227" t="n">
         <v>195</v>
       </c>
-      <c r="J227" t="n">
-        <v>197</v>
-      </c>
-      <c r="K227" t="n">
-        <v>197</v>
-      </c>
       <c r="L227" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M227" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N227" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -23806,7 +23806,7 @@
         <v>23</v>
       </c>
       <c r="N229" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -24012,7 +24012,7 @@
         <v>23</v>
       </c>
       <c r="N231" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -24218,7 +24218,7 @@
         <v>23</v>
       </c>
       <c r="N233" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -24424,7 +24424,7 @@
         <v>27</v>
       </c>
       <c r="N235" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -24630,7 +24630,7 @@
         <v>27</v>
       </c>
       <c r="N237" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -25009,40 +25009,40 @@
         <v>91.7287</v>
       </c>
       <c r="C241" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D241" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E241" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F241" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G241" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H241" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I241" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J241" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K241" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L241" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M241" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N241" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -25215,40 +25215,40 @@
         <v>126.78023</v>
       </c>
       <c r="C243" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D243" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E243" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F243" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G243" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H243" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I243" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J243" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K243" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="L243" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="M243" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="N243" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -25421,40 +25421,40 @@
         <v>123.36635</v>
       </c>
       <c r="C245" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D245" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E245" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F245" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G245" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H245" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="I245" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="J245" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="K245" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L245" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M245" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="N245" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -25627,10 +25627,10 @@
         <v>122.32919</v>
       </c>
       <c r="C247" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D247" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E247" t="n">
         <v>116</v>
@@ -25645,10 +25645,10 @@
         <v>116</v>
       </c>
       <c r="I247" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J247" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K247" t="n">
         <v>116</v>
@@ -25657,10 +25657,10 @@
         <v>116</v>
       </c>
       <c r="M247" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N247" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -25833,40 +25833,40 @@
         <v>150</v>
       </c>
       <c r="C249" t="n">
+        <v>22</v>
+      </c>
+      <c r="D249" t="n">
+        <v>25</v>
+      </c>
+      <c r="E249" t="n">
         <v>28</v>
       </c>
-      <c r="D249" t="n">
-        <v>30</v>
-      </c>
-      <c r="E249" t="n">
-        <v>31</v>
-      </c>
       <c r="F249" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G249" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H249" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I249" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J249" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K249" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="L249" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="M249" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N249" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -26039,40 +26039,40 @@
         <v>61.2732</v>
       </c>
       <c r="C251" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D251" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E251" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F251" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G251" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H251" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I251" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J251" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K251" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L251" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M251" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N251" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -26245,40 +26245,40 @@
         <v>33</v>
       </c>
       <c r="C253" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D253" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E253" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F253" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G253" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H253" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I253" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J253" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K253" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L253" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M253" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N253" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -26451,40 +26451,40 @@
         <v>660</v>
       </c>
       <c r="C255" t="n">
-        <v>450</v>
+        <v>551</v>
       </c>
       <c r="D255" t="n">
-        <v>450</v>
+        <v>551</v>
       </c>
       <c r="E255" t="n">
-        <v>451</v>
+        <v>550</v>
       </c>
       <c r="F255" t="n">
-        <v>451</v>
+        <v>545</v>
       </c>
       <c r="G255" t="n">
-        <v>451</v>
+        <v>551</v>
       </c>
       <c r="H255" t="n">
-        <v>451</v>
+        <v>545</v>
       </c>
       <c r="I255" t="n">
-        <v>449</v>
+        <v>551</v>
       </c>
       <c r="J255" t="n">
-        <v>451</v>
+        <v>599</v>
       </c>
       <c r="K255" t="n">
-        <v>451</v>
+        <v>644</v>
       </c>
       <c r="L255" t="n">
-        <v>500</v>
+        <v>643</v>
       </c>
       <c r="M255" t="n">
-        <v>496</v>
+        <v>644</v>
       </c>
       <c r="N255" t="n">
-        <v>497</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -26657,40 +26657,40 @@
         <v>47</v>
       </c>
       <c r="C257" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D257" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E257" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F257" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G257" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H257" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I257" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J257" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K257" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N257" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -26863,37 +26863,37 @@
         <v>35.5</v>
       </c>
       <c r="C259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N259" t="n">
         <v>0</v>
@@ -27069,40 +27069,40 @@
         <v>36.3</v>
       </c>
       <c r="C261" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D261" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E261" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F261" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H261" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I261" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J261" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K261" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -27278,37 +27278,37 @@
         <v>57</v>
       </c>
       <c r="D263" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E263" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F263" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G263" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H263" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I263" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J263" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K263" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L263" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M263" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N263" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -27481,22 +27481,22 @@
         <v>18.5378</v>
       </c>
       <c r="C265" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D265" t="n">
         <v>17</v>
       </c>
       <c r="E265" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F265" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G265" t="n">
         <v>17</v>
       </c>
       <c r="H265" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I265" t="n">
         <v>17</v>
@@ -27505,16 +27505,16 @@
         <v>17</v>
       </c>
       <c r="K265" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L265" t="n">
         <v>17</v>
       </c>
       <c r="M265" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N265" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -27893,40 +27893,40 @@
         <v>880</v>
       </c>
       <c r="C269" t="n">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D269" t="n">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="E269" t="n">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F269" t="n">
-        <v>507</v>
+        <v>544</v>
       </c>
       <c r="G269" t="n">
-        <v>487</v>
+        <v>518</v>
       </c>
       <c r="H269" t="n">
-        <v>539</v>
+        <v>456</v>
       </c>
       <c r="I269" t="n">
-        <v>551</v>
+        <v>452</v>
       </c>
       <c r="J269" t="n">
-        <v>535</v>
+        <v>474</v>
       </c>
       <c r="K269" t="n">
-        <v>599</v>
+        <v>501</v>
       </c>
       <c r="L269" t="n">
-        <v>524</v>
+        <v>602</v>
       </c>
       <c r="M269" t="n">
-        <v>547</v>
+        <v>694</v>
       </c>
       <c r="N269" t="n">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -28099,40 +28099,40 @@
         <v>880</v>
       </c>
       <c r="C271" t="n">
-        <v>605</v>
+        <v>539</v>
       </c>
       <c r="D271" t="n">
+        <v>612</v>
+      </c>
+      <c r="E271" t="n">
+        <v>608</v>
+      </c>
+      <c r="F271" t="n">
+        <v>522</v>
+      </c>
+      <c r="G271" t="n">
         <v>577</v>
       </c>
-      <c r="E271" t="n">
-        <v>589</v>
-      </c>
-      <c r="F271" t="n">
-        <v>525</v>
-      </c>
-      <c r="G271" t="n">
-        <v>505</v>
-      </c>
       <c r="H271" t="n">
-        <v>506</v>
+        <v>452</v>
       </c>
       <c r="I271" t="n">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="J271" t="n">
-        <v>564</v>
+        <v>473</v>
       </c>
       <c r="K271" t="n">
-        <v>579</v>
+        <v>537</v>
       </c>
       <c r="L271" t="n">
-        <v>538</v>
+        <v>594</v>
       </c>
       <c r="M271" t="n">
-        <v>548</v>
+        <v>673</v>
       </c>
       <c r="N271" t="n">
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -28305,40 +28305,40 @@
         <v>924</v>
       </c>
       <c r="C273" t="n">
-        <v>715</v>
+        <v>915</v>
       </c>
       <c r="D273" t="n">
-        <v>713</v>
+        <v>908</v>
       </c>
       <c r="E273" t="n">
-        <v>713</v>
+        <v>911</v>
       </c>
       <c r="F273" t="n">
-        <v>705</v>
+        <v>911</v>
       </c>
       <c r="G273" t="n">
-        <v>705</v>
+        <v>854</v>
       </c>
       <c r="H273" t="n">
-        <v>676</v>
+        <v>775</v>
       </c>
       <c r="I273" t="n">
-        <v>675</v>
+        <v>768</v>
       </c>
       <c r="J273" t="n">
-        <v>673</v>
+        <v>764</v>
       </c>
       <c r="K273" t="n">
-        <v>752</v>
+        <v>800</v>
       </c>
       <c r="L273" t="n">
-        <v>809</v>
+        <v>911</v>
       </c>
       <c r="M273" t="n">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="N273" t="n">
-        <v>908</v>
+        <v>0</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -29235,40 +29235,40 @@
       </c>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="n">
-        <v>3.50011</v>
+        <v>4</v>
       </c>
       <c r="D283" t="n">
-        <v>3.5004</v>
+        <v>4</v>
       </c>
       <c r="E283" t="n">
-        <v>3.49662</v>
+        <v>4</v>
       </c>
       <c r="F283" t="n">
-        <v>3.49346</v>
+        <v>4</v>
       </c>
       <c r="G283" t="n">
-        <v>3.50561</v>
+        <v>4</v>
       </c>
       <c r="H283" t="n">
-        <v>3.49962</v>
+        <v>4</v>
       </c>
       <c r="I283" t="n">
-        <v>3.5018</v>
+        <v>4</v>
       </c>
       <c r="J283" t="n">
-        <v>3.50346</v>
+        <v>3</v>
       </c>
       <c r="K283" t="n">
-        <v>3.50469</v>
+        <v>4</v>
       </c>
       <c r="L283" t="n">
-        <v>3.49931</v>
+        <v>4</v>
       </c>
       <c r="M283" t="n">
-        <v>3.49646</v>
+        <v>4</v>
       </c>
       <c r="N283" t="n">
-        <v>3.49891</v>
+        <v>0</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -29439,40 +29439,40 @@
       </c>
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="n">
-        <v>2.67492</v>
+        <v>3</v>
       </c>
       <c r="D285" t="n">
-        <v>2.67502</v>
+        <v>3</v>
       </c>
       <c r="E285" t="n">
-        <v>2.67202</v>
+        <v>3</v>
       </c>
       <c r="F285" t="n">
-        <v>2.6748</v>
+        <v>3</v>
       </c>
       <c r="G285" t="n">
-        <v>2.67287</v>
+        <v>3</v>
       </c>
       <c r="H285" t="n">
-        <v>2.67037</v>
+        <v>3</v>
       </c>
       <c r="I285" t="n">
-        <v>2.6718</v>
+        <v>3</v>
       </c>
       <c r="J285" t="n">
-        <v>2.67215</v>
+        <v>3</v>
       </c>
       <c r="K285" t="n">
-        <v>2.67315</v>
+        <v>3</v>
       </c>
       <c r="L285" t="n">
-        <v>2.67416</v>
+        <v>3</v>
       </c>
       <c r="M285" t="n">
-        <v>2.6719</v>
+        <v>3</v>
       </c>
       <c r="N285" t="n">
-        <v>2.67102</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -29643,40 +29643,40 @@
       </c>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
-        <v>0.13371</v>
+        <v>2</v>
       </c>
       <c r="D287" t="n">
-        <v>0.16207</v>
+        <v>2</v>
       </c>
       <c r="E287" t="n">
-        <v>0.18188</v>
+        <v>2</v>
       </c>
       <c r="F287" t="n">
-        <v>0.18386</v>
+        <v>2</v>
       </c>
       <c r="G287" t="n">
-        <v>0.24961</v>
+        <v>2</v>
       </c>
       <c r="H287" t="n">
-        <v>0.27388</v>
+        <v>2</v>
       </c>
       <c r="I287" t="n">
-        <v>0.28033</v>
+        <v>2</v>
       </c>
       <c r="J287" t="n">
-        <v>0.29331</v>
+        <v>2</v>
       </c>
       <c r="K287" t="n">
-        <v>0.28455</v>
+        <v>2</v>
       </c>
       <c r="L287" t="n">
-        <v>0.28431</v>
+        <v>2</v>
       </c>
       <c r="M287" t="n">
-        <v>0.25174</v>
+        <v>2</v>
       </c>
       <c r="N287" t="n">
-        <v>0.21812</v>
+        <v>0</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -30669,37 +30669,37 @@
       </c>
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M297" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N297" t="n">
         <v>0</v>
@@ -31285,40 +31285,40 @@
         <v>126</v>
       </c>
       <c r="C303" t="n">
-        <v>30.00874</v>
+        <v>26</v>
       </c>
       <c r="D303" t="n">
-        <v>29.42444</v>
+        <v>26</v>
       </c>
       <c r="E303" t="n">
-        <v>29.81681</v>
+        <v>30</v>
       </c>
       <c r="F303" t="n">
-        <v>30.06437</v>
+        <v>31</v>
       </c>
       <c r="G303" t="n">
-        <v>29.69829</v>
+        <v>31</v>
       </c>
       <c r="H303" t="n">
-        <v>29.40321</v>
+        <v>30</v>
       </c>
       <c r="I303" t="n">
-        <v>30.03617</v>
+        <v>31</v>
       </c>
       <c r="J303" t="n">
-        <v>29.92709</v>
+        <v>31</v>
       </c>
       <c r="K303" t="n">
-        <v>29.66627</v>
+        <v>31</v>
       </c>
       <c r="L303" t="n">
-        <v>29.68864</v>
+        <v>31</v>
       </c>
       <c r="M303" t="n">
-        <v>29.31729</v>
+        <v>31</v>
       </c>
       <c r="N303" t="n">
-        <v>29.0416</v>
+        <v>0</v>
       </c>
       <c r="O303" t="n">
         <v>0</v>
@@ -31697,40 +31697,40 @@
         <v>93</v>
       </c>
       <c r="C307" t="n">
-        <v>89.85722</v>
+        <v>82</v>
       </c>
       <c r="D307" t="n">
-        <v>89.85832000000001</v>
+        <v>81</v>
       </c>
       <c r="E307" t="n">
-        <v>89.75787</v>
+        <v>92</v>
       </c>
       <c r="F307" t="n">
-        <v>89.56264</v>
+        <v>92</v>
       </c>
       <c r="G307" t="n">
-        <v>89.61765</v>
+        <v>92</v>
       </c>
       <c r="H307" t="n">
-        <v>89.76607</v>
+        <v>92</v>
       </c>
       <c r="I307" t="n">
-        <v>89.68575</v>
+        <v>91</v>
       </c>
       <c r="J307" t="n">
-        <v>89.66618</v>
+        <v>91</v>
       </c>
       <c r="K307" t="n">
-        <v>89.77458</v>
+        <v>91</v>
       </c>
       <c r="L307" t="n">
-        <v>89.55602</v>
+        <v>92</v>
       </c>
       <c r="M307" t="n">
-        <v>88.6152</v>
+        <v>92</v>
       </c>
       <c r="N307" t="n">
-        <v>88.94421</v>
+        <v>0</v>
       </c>
       <c r="O307" t="n">
         <v>0</v>
@@ -32109,40 +32109,40 @@
         <v>126</v>
       </c>
       <c r="C311" t="n">
-        <v>29.51879</v>
+        <v>27</v>
       </c>
       <c r="D311" t="n">
-        <v>29.22726</v>
+        <v>67</v>
       </c>
       <c r="E311" t="n">
-        <v>29.50314</v>
+        <v>34</v>
       </c>
       <c r="F311" t="n">
-        <v>29.44311</v>
+        <v>34</v>
       </c>
       <c r="G311" t="n">
-        <v>29.355</v>
+        <v>34</v>
       </c>
       <c r="H311" t="n">
-        <v>29.29005</v>
+        <v>34</v>
       </c>
       <c r="I311" t="n">
-        <v>29.23647</v>
+        <v>34</v>
       </c>
       <c r="J311" t="n">
-        <v>29.15468</v>
+        <v>34</v>
       </c>
       <c r="K311" t="n">
-        <v>29.25095</v>
+        <v>34</v>
       </c>
       <c r="L311" t="n">
-        <v>29.39917</v>
+        <v>34</v>
       </c>
       <c r="M311" t="n">
-        <v>29.18423</v>
+        <v>34</v>
       </c>
       <c r="N311" t="n">
-        <v>28.47847</v>
+        <v>0</v>
       </c>
       <c r="O311" t="n">
         <v>0</v>
@@ -32315,40 +32315,40 @@
         <v>93</v>
       </c>
       <c r="C313" t="n">
-        <v>92.39735</v>
+        <v>75</v>
       </c>
       <c r="D313" t="n">
-        <v>92.40863</v>
+        <v>60</v>
       </c>
       <c r="E313" t="n">
-        <v>92.938</v>
+        <v>0</v>
       </c>
       <c r="F313" t="n">
-        <v>92.38619</v>
+        <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>92.54067000000001</v>
+        <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>92.72181999999999</v>
+        <v>0</v>
       </c>
       <c r="I313" t="n">
-        <v>92.51143</v>
+        <v>0</v>
       </c>
       <c r="J313" t="n">
-        <v>92.67894</v>
+        <v>0</v>
       </c>
       <c r="K313" t="n">
-        <v>91.92757</v>
+        <v>0</v>
       </c>
       <c r="L313" t="n">
-        <v>92.21307</v>
+        <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>92.41221</v>
+        <v>0</v>
       </c>
       <c r="N313" t="n">
-        <v>92.68948</v>
+        <v>0</v>
       </c>
       <c r="O313" t="n">
         <v>0</v>
@@ -32521,37 +32521,37 @@
         <v>93</v>
       </c>
       <c r="C315" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="D315" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="E315" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F315" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H315" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="I315" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J315" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="K315" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M315" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N315" t="n">
         <v>0</v>
@@ -33139,40 +33139,40 @@
         <v>615</v>
       </c>
       <c r="C321" t="n">
-        <v>458.23044</v>
+        <v>459</v>
       </c>
       <c r="D321" t="n">
-        <v>458.28857</v>
+        <v>460</v>
       </c>
       <c r="E321" t="n">
-        <v>459.52872</v>
+        <v>457</v>
       </c>
       <c r="F321" t="n">
-        <v>459.21515</v>
+        <v>460</v>
       </c>
       <c r="G321" t="n">
-        <v>458.16153</v>
+        <v>458</v>
       </c>
       <c r="H321" t="n">
-        <v>457.63904</v>
+        <v>459</v>
       </c>
       <c r="I321" t="n">
-        <v>457.80612</v>
+        <v>459</v>
       </c>
       <c r="J321" t="n">
-        <v>458.13791</v>
+        <v>459</v>
       </c>
       <c r="K321" t="n">
-        <v>458.33676</v>
+        <v>458</v>
       </c>
       <c r="L321" t="n">
-        <v>458.34155</v>
+        <v>459</v>
       </c>
       <c r="M321" t="n">
-        <v>458.34164</v>
+        <v>460</v>
       </c>
       <c r="N321" t="n">
-        <v>458.08081</v>
+        <v>0</v>
       </c>
       <c r="O321" t="n">
         <v>0</v>
@@ -33345,40 +33345,40 @@
         <v>280</v>
       </c>
       <c r="C323" t="n">
-        <v>240.34709</v>
+        <v>251</v>
       </c>
       <c r="D323" t="n">
-        <v>239.55202</v>
+        <v>252</v>
       </c>
       <c r="E323" t="n">
-        <v>240.37738</v>
+        <v>252</v>
       </c>
       <c r="F323" t="n">
-        <v>240.23276</v>
+        <v>250</v>
       </c>
       <c r="G323" t="n">
-        <v>240.35275</v>
+        <v>251</v>
       </c>
       <c r="H323" t="n">
-        <v>240.55005</v>
+        <v>251</v>
       </c>
       <c r="I323" t="n">
-        <v>240.7218</v>
+        <v>252</v>
       </c>
       <c r="J323" t="n">
-        <v>240.77379</v>
+        <v>252</v>
       </c>
       <c r="K323" t="n">
-        <v>241.00205</v>
+        <v>245</v>
       </c>
       <c r="L323" t="n">
-        <v>240.9884</v>
+        <v>243</v>
       </c>
       <c r="M323" t="n">
-        <v>240.56776</v>
+        <v>241</v>
       </c>
       <c r="N323" t="n">
-        <v>240.51727</v>
+        <v>0</v>
       </c>
       <c r="O323" t="n">
         <v>0</v>
@@ -33551,40 +33551,40 @@
         <v>280</v>
       </c>
       <c r="C325" t="n">
-        <v>240.64128</v>
+        <v>253</v>
       </c>
       <c r="D325" t="n">
-        <v>240.48358</v>
+        <v>251</v>
       </c>
       <c r="E325" t="n">
-        <v>240.3447</v>
+        <v>251</v>
       </c>
       <c r="F325" t="n">
-        <v>240.24333</v>
+        <v>252</v>
       </c>
       <c r="G325" t="n">
-        <v>240.54662</v>
+        <v>255</v>
       </c>
       <c r="H325" t="n">
-        <v>239.69673</v>
+        <v>252</v>
       </c>
       <c r="I325" t="n">
-        <v>239.69417</v>
+        <v>252</v>
       </c>
       <c r="J325" t="n">
-        <v>239.75533</v>
+        <v>246</v>
       </c>
       <c r="K325" t="n">
-        <v>240.08629</v>
+        <v>252</v>
       </c>
       <c r="L325" t="n">
-        <v>240.62453</v>
+        <v>246</v>
       </c>
       <c r="M325" t="n">
-        <v>240.35053</v>
+        <v>240</v>
       </c>
       <c r="N325" t="n">
-        <v>239.70384</v>
+        <v>0</v>
       </c>
       <c r="O325" t="n">
         <v>0</v>
@@ -33757,40 +33757,40 @@
         <v>54.56099</v>
       </c>
       <c r="C327" t="n">
-        <v>32.08543</v>
+        <v>32</v>
       </c>
       <c r="D327" t="n">
-        <v>32.25919</v>
+        <v>32</v>
       </c>
       <c r="E327" t="n">
-        <v>31.75706</v>
+        <v>32</v>
       </c>
       <c r="F327" t="n">
-        <v>32.26627</v>
+        <v>32</v>
       </c>
       <c r="G327" t="n">
-        <v>32.13763</v>
+        <v>32</v>
       </c>
       <c r="H327" t="n">
-        <v>32.08992</v>
+        <v>32</v>
       </c>
       <c r="I327" t="n">
-        <v>32.26454</v>
+        <v>32</v>
       </c>
       <c r="J327" t="n">
-        <v>32.10565</v>
+        <v>32</v>
       </c>
       <c r="K327" t="n">
-        <v>32.22826</v>
+        <v>32</v>
       </c>
       <c r="L327" t="n">
-        <v>32.10874</v>
+        <v>32</v>
       </c>
       <c r="M327" t="n">
-        <v>31.79111</v>
+        <v>32</v>
       </c>
       <c r="N327" t="n">
-        <v>32.03236</v>
+        <v>0</v>
       </c>
       <c r="O327" t="n">
         <v>0</v>
@@ -33963,40 +33963,40 @@
         <v>281</v>
       </c>
       <c r="C329" t="n">
-        <v>182.89819</v>
+        <v>278</v>
       </c>
       <c r="D329" t="n">
-        <v>182.4303</v>
+        <v>277</v>
       </c>
       <c r="E329" t="n">
-        <v>182.57245</v>
+        <v>277</v>
       </c>
       <c r="F329" t="n">
-        <v>183.20544</v>
+        <v>277</v>
       </c>
       <c r="G329" t="n">
-        <v>182.9207</v>
+        <v>277</v>
       </c>
       <c r="H329" t="n">
-        <v>182.85115</v>
+        <v>249</v>
       </c>
       <c r="I329" t="n">
-        <v>181.85678</v>
+        <v>250</v>
       </c>
       <c r="J329" t="n">
-        <v>181.75916</v>
+        <v>250</v>
       </c>
       <c r="K329" t="n">
-        <v>189.12878</v>
+        <v>257</v>
       </c>
       <c r="L329" t="n">
-        <v>203.72615</v>
+        <v>276</v>
       </c>
       <c r="M329" t="n">
-        <v>233.11746</v>
+        <v>275</v>
       </c>
       <c r="N329" t="n">
-        <v>277.23257</v>
+        <v>0</v>
       </c>
       <c r="O329" t="n">
         <v>0</v>
@@ -34169,40 +34169,40 @@
         <v>281</v>
       </c>
       <c r="C331" t="n">
-        <v>181.36304</v>
+        <v>277</v>
       </c>
       <c r="D331" t="n">
-        <v>181.89519</v>
+        <v>277</v>
       </c>
       <c r="E331" t="n">
-        <v>181.04173</v>
+        <v>276</v>
       </c>
       <c r="F331" t="n">
-        <v>180.11713</v>
+        <v>276</v>
       </c>
       <c r="G331" t="n">
-        <v>180.95711</v>
+        <v>276</v>
       </c>
       <c r="H331" t="n">
-        <v>181.6116</v>
+        <v>249</v>
       </c>
       <c r="I331" t="n">
-        <v>182.38664</v>
+        <v>249</v>
       </c>
       <c r="J331" t="n">
-        <v>182.33196</v>
+        <v>249</v>
       </c>
       <c r="K331" t="n">
-        <v>196.05524</v>
+        <v>257</v>
       </c>
       <c r="L331" t="n">
-        <v>230.70473</v>
+        <v>275</v>
       </c>
       <c r="M331" t="n">
-        <v>265.06119</v>
+        <v>276</v>
       </c>
       <c r="N331" t="n">
-        <v>271.76172</v>
+        <v>0</v>
       </c>
       <c r="O331" t="n">
         <v>0</v>
@@ -34581,40 +34581,40 @@
         <v>945</v>
       </c>
       <c r="C335" t="n">
-        <v>499.45105</v>
+        <v>507</v>
       </c>
       <c r="D335" t="n">
-        <v>496.6394</v>
+        <v>504</v>
       </c>
       <c r="E335" t="n">
-        <v>501.87262</v>
+        <v>502</v>
       </c>
       <c r="F335" t="n">
-        <v>495.72928</v>
+        <v>502</v>
       </c>
       <c r="G335" t="n">
-        <v>495.46912</v>
+        <v>511</v>
       </c>
       <c r="H335" t="n">
-        <v>503.89456</v>
+        <v>503</v>
       </c>
       <c r="I335" t="n">
-        <v>501.17322</v>
+        <v>491</v>
       </c>
       <c r="J335" t="n">
-        <v>499.69559</v>
+        <v>495</v>
       </c>
       <c r="K335" t="n">
-        <v>500.54688</v>
+        <v>504</v>
       </c>
       <c r="L335" t="n">
-        <v>498.45361</v>
+        <v>497</v>
       </c>
       <c r="M335" t="n">
-        <v>501.29956</v>
+        <v>494</v>
       </c>
       <c r="N335" t="n">
-        <v>500.45923</v>
+        <v>0</v>
       </c>
       <c r="O335" t="n">
         <v>0</v>
@@ -34787,40 +34787,40 @@
         <v>950</v>
       </c>
       <c r="C337" t="n">
-        <v>874.86285</v>
+        <v>895</v>
       </c>
       <c r="D337" t="n">
-        <v>846.05823</v>
+        <v>896</v>
       </c>
       <c r="E337" t="n">
-        <v>843.07709</v>
+        <v>893</v>
       </c>
       <c r="F337" t="n">
-        <v>844.84253</v>
+        <v>894</v>
       </c>
       <c r="G337" t="n">
-        <v>842.15192</v>
+        <v>886</v>
       </c>
       <c r="H337" t="n">
-        <v>843.2626299999999</v>
+        <v>892</v>
       </c>
       <c r="I337" t="n">
-        <v>846.00842</v>
+        <v>894</v>
       </c>
       <c r="J337" t="n">
-        <v>844.89136</v>
+        <v>893</v>
       </c>
       <c r="K337" t="n">
-        <v>890.77863</v>
+        <v>906</v>
       </c>
       <c r="L337" t="n">
-        <v>924.80768</v>
+        <v>911</v>
       </c>
       <c r="M337" t="n">
-        <v>917.67157</v>
+        <v>911</v>
       </c>
       <c r="N337" t="n">
-        <v>916.5423</v>
+        <v>0</v>
       </c>
       <c r="O337" t="n">
         <v>0</v>
@@ -34993,40 +34993,40 @@
         <v>950</v>
       </c>
       <c r="C339" t="n">
-        <v>872.76788</v>
+        <v>892</v>
       </c>
       <c r="D339" t="n">
-        <v>839.30054</v>
+        <v>891</v>
       </c>
       <c r="E339" t="n">
-        <v>838.2226000000001</v>
+        <v>889</v>
       </c>
       <c r="F339" t="n">
-        <v>829.2166099999999</v>
+        <v>887</v>
       </c>
       <c r="G339" t="n">
-        <v>839.44128</v>
+        <v>893</v>
       </c>
       <c r="H339" t="n">
-        <v>838.3380100000001</v>
+        <v>887</v>
       </c>
       <c r="I339" t="n">
-        <v>839.66919</v>
+        <v>889</v>
       </c>
       <c r="J339" t="n">
-        <v>839.28229</v>
+        <v>885</v>
       </c>
       <c r="K339" t="n">
-        <v>888.63513</v>
+        <v>907</v>
       </c>
       <c r="L339" t="n">
-        <v>913.70227</v>
+        <v>906</v>
       </c>
       <c r="M339" t="n">
-        <v>913.05866</v>
+        <v>907</v>
       </c>
       <c r="N339" t="n">
-        <v>908.73517</v>
+        <v>0</v>
       </c>
       <c r="O339" t="n">
         <v>0</v>
@@ -35199,40 +35199,40 @@
         <v>1000</v>
       </c>
       <c r="C341" t="n">
-        <v>935.23328</v>
+        <v>967</v>
       </c>
       <c r="D341" t="n">
-        <v>936.8213500000001</v>
+        <v>978</v>
       </c>
       <c r="E341" t="n">
-        <v>977.51904</v>
+        <v>977</v>
       </c>
       <c r="F341" t="n">
-        <v>977.94281</v>
+        <v>977</v>
       </c>
       <c r="G341" t="n">
-        <v>973.89307</v>
+        <v>977</v>
       </c>
       <c r="H341" t="n">
-        <v>936.58655</v>
+        <v>964</v>
       </c>
       <c r="I341" t="n">
-        <v>925.22186</v>
+        <v>929</v>
       </c>
       <c r="J341" t="n">
-        <v>934.0122699999999</v>
+        <v>934</v>
       </c>
       <c r="K341" t="n">
-        <v>933.53632</v>
+        <v>977</v>
       </c>
       <c r="L341" t="n">
-        <v>934.28162</v>
+        <v>977</v>
       </c>
       <c r="M341" t="n">
-        <v>976.27881</v>
+        <v>980</v>
       </c>
       <c r="N341" t="n">
-        <v>904.33991</v>
+        <v>0</v>
       </c>
       <c r="O341" t="n">
         <v>0</v>
@@ -35405,40 +35405,40 @@
         <v>1000</v>
       </c>
       <c r="C343" t="n">
-        <v>933.36609</v>
+        <v>972</v>
       </c>
       <c r="D343" t="n">
-        <v>936.84937</v>
+        <v>978</v>
       </c>
       <c r="E343" t="n">
-        <v>977.45789</v>
+        <v>973</v>
       </c>
       <c r="F343" t="n">
-        <v>977.55981</v>
+        <v>972</v>
       </c>
       <c r="G343" t="n">
-        <v>976.16052</v>
+        <v>977</v>
       </c>
       <c r="H343" t="n">
-        <v>933.64941</v>
+        <v>956</v>
       </c>
       <c r="I343" t="n">
-        <v>931.8457</v>
+        <v>930</v>
       </c>
       <c r="J343" t="n">
-        <v>931.86707</v>
+        <v>931</v>
       </c>
       <c r="K343" t="n">
-        <v>926.13141</v>
+        <v>976</v>
       </c>
       <c r="L343" t="n">
-        <v>934.78326</v>
+        <v>974</v>
       </c>
       <c r="M343" t="n">
-        <v>973.60992</v>
+        <v>978</v>
       </c>
       <c r="N343" t="n">
-        <v>897.78803</v>
+        <v>0</v>
       </c>
       <c r="O343" t="n">
         <v>0</v>
@@ -35611,40 +35611,40 @@
         <v>660.8</v>
       </c>
       <c r="C345" t="n">
-        <v>504.59769</v>
+        <v>553</v>
       </c>
       <c r="D345" t="n">
-        <v>504.83286</v>
+        <v>411</v>
       </c>
       <c r="E345" t="n">
-        <v>506.996</v>
+        <v>372</v>
       </c>
       <c r="F345" t="n">
-        <v>503.60025</v>
+        <v>374</v>
       </c>
       <c r="G345" t="n">
-        <v>501.21988</v>
+        <v>376</v>
       </c>
       <c r="H345" t="n">
-        <v>506.56586</v>
+        <v>375</v>
       </c>
       <c r="I345" t="n">
-        <v>505.78622</v>
+        <v>376</v>
       </c>
       <c r="J345" t="n">
-        <v>526.02026</v>
+        <v>374</v>
       </c>
       <c r="K345" t="n">
-        <v>589.74005</v>
+        <v>373</v>
       </c>
       <c r="L345" t="n">
-        <v>618.09723</v>
+        <v>377</v>
       </c>
       <c r="M345" t="n">
-        <v>606.21326</v>
+        <v>436</v>
       </c>
       <c r="N345" t="n">
-        <v>601.53113</v>
+        <v>0</v>
       </c>
       <c r="O345" t="n">
         <v>0</v>
@@ -35817,40 +35817,40 @@
         <v>660.8</v>
       </c>
       <c r="C347" t="n">
-        <v>505.07724</v>
+        <v>646</v>
       </c>
       <c r="D347" t="n">
-        <v>509.48267</v>
+        <v>644</v>
       </c>
       <c r="E347" t="n">
-        <v>506.75119</v>
+        <v>646</v>
       </c>
       <c r="F347" t="n">
-        <v>517.28882</v>
+        <v>645</v>
       </c>
       <c r="G347" t="n">
-        <v>519.29364</v>
+        <v>645</v>
       </c>
       <c r="H347" t="n">
-        <v>509.78333</v>
+        <v>645</v>
       </c>
       <c r="I347" t="n">
-        <v>509.25736</v>
+        <v>647</v>
       </c>
       <c r="J347" t="n">
-        <v>528.50916</v>
+        <v>647</v>
       </c>
       <c r="K347" t="n">
-        <v>577.92871</v>
+        <v>651</v>
       </c>
       <c r="L347" t="n">
-        <v>617.30896</v>
+        <v>647</v>
       </c>
       <c r="M347" t="n">
-        <v>612.92072</v>
+        <v>644</v>
       </c>
       <c r="N347" t="n">
-        <v>607.39258</v>
+        <v>0</v>
       </c>
       <c r="O347" t="n">
         <v>0</v>
@@ -36023,40 +36023,40 @@
         <v>661.1</v>
       </c>
       <c r="C349" t="n">
-        <v>507.82065</v>
+        <v>643</v>
       </c>
       <c r="D349" t="n">
-        <v>500.15189</v>
+        <v>641</v>
       </c>
       <c r="E349" t="n">
-        <v>496.67343</v>
+        <v>640</v>
       </c>
       <c r="F349" t="n">
-        <v>496.56198</v>
+        <v>640</v>
       </c>
       <c r="G349" t="n">
-        <v>496.85059</v>
+        <v>640</v>
       </c>
       <c r="H349" t="n">
-        <v>493.62061</v>
+        <v>644</v>
       </c>
       <c r="I349" t="n">
-        <v>496.25299</v>
+        <v>644</v>
       </c>
       <c r="J349" t="n">
-        <v>497.02487</v>
+        <v>644</v>
       </c>
       <c r="K349" t="n">
-        <v>522.7028800000001</v>
+        <v>646</v>
       </c>
       <c r="L349" t="n">
-        <v>539.85077</v>
+        <v>638</v>
       </c>
       <c r="M349" t="n">
-        <v>585.84686</v>
+        <v>644</v>
       </c>
       <c r="N349" t="n">
-        <v>592.23718</v>
+        <v>0</v>
       </c>
       <c r="O349" t="n">
         <v>0</v>
@@ -36229,40 +36229,40 @@
         <v>661.1</v>
       </c>
       <c r="C351" t="n">
-        <v>499.70856</v>
+        <v>637</v>
       </c>
       <c r="D351" t="n">
-        <v>495.73563</v>
+        <v>631</v>
       </c>
       <c r="E351" t="n">
-        <v>492.00333</v>
+        <v>637</v>
       </c>
       <c r="F351" t="n">
-        <v>492.59445</v>
+        <v>634</v>
       </c>
       <c r="G351" t="n">
-        <v>489.62585</v>
+        <v>636</v>
       </c>
       <c r="H351" t="n">
-        <v>488.54794</v>
+        <v>639</v>
       </c>
       <c r="I351" t="n">
-        <v>480.28894</v>
+        <v>638</v>
       </c>
       <c r="J351" t="n">
-        <v>492.9563</v>
+        <v>640</v>
       </c>
       <c r="K351" t="n">
-        <v>518.7467</v>
+        <v>640</v>
       </c>
       <c r="L351" t="n">
-        <v>539.87793</v>
+        <v>637</v>
       </c>
       <c r="M351" t="n">
-        <v>582.48999</v>
+        <v>637</v>
       </c>
       <c r="N351" t="n">
-        <v>584.92035</v>
+        <v>0</v>
       </c>
       <c r="O351" t="n">
         <v>0</v>
@@ -37367,40 +37367,40 @@
         <v>164.86</v>
       </c>
       <c r="C363" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D363" t="n">
         <v>53</v>
       </c>
       <c r="E363" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F363" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G363" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H363" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I363" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J363" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K363" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L363" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M363" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N363" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="O363" t="n">
         <v>0</v>
@@ -37985,40 +37985,40 @@
         <v>100</v>
       </c>
       <c r="C369" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D369" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E369" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F369" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G369" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H369" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="I369" t="n">
+        <v>106</v>
+      </c>
+      <c r="J369" t="n">
         <v>105</v>
       </c>
-      <c r="J369" t="n">
-        <v>103</v>
-      </c>
       <c r="K369" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L369" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M369" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N369" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="O369" t="n">
         <v>0</v>
@@ -39015,40 +39015,40 @@
         <v>34.33</v>
       </c>
       <c r="C379" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D379" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E379" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F379" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G379" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H379" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I379" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J379" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K379" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L379" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M379" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N379" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O379" t="n">
         <v>0</v>
@@ -39427,37 +39427,37 @@
         <v>26.81</v>
       </c>
       <c r="C383" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D383" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E383" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F383" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H383" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I383" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J383" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K383" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L383" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M383" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N383" t="n">
         <v>0</v>
@@ -39633,40 +39633,40 @@
         <v>26.81</v>
       </c>
       <c r="C385" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D385" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E385" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F385" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H385" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I385" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J385" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K385" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L385" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M385" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N385" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O385" t="n">
         <v>0</v>
@@ -39870,7 +39870,7 @@
         <v>8</v>
       </c>
       <c r="N387" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O387" t="n">
         <v>0</v>
@@ -40074,7 +40074,7 @@
         <v>6</v>
       </c>
       <c r="N389" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O389" t="n">
         <v>0</v>
@@ -40280,7 +40280,7 @@
         <v>2</v>
       </c>
       <c r="N391" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O391" t="n">
         <v>0</v>
@@ -40674,7 +40674,7 @@
         <v>8</v>
       </c>
       <c r="H395" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I395" t="n">
         <v>0</v>
@@ -41722,7 +41722,7 @@
         <v>91</v>
       </c>
       <c r="N405" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="O405" t="n">
         <v>0</v>
@@ -41895,13 +41895,13 @@
         <v>166.5</v>
       </c>
       <c r="C407" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D407" t="n">
         <v>90</v>
       </c>
       <c r="E407" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F407" t="n">
         <v>90</v>
@@ -41910,10 +41910,10 @@
         <v>90</v>
       </c>
       <c r="H407" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I407" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J407" t="n">
         <v>90</v>
@@ -41925,10 +41925,10 @@
         <v>90</v>
       </c>
       <c r="M407" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N407" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O407" t="n">
         <v>0</v>
@@ -42101,40 +42101,40 @@
         <v>370</v>
       </c>
       <c r="C409" t="n">
-        <v>256</v>
+        <v>329</v>
       </c>
       <c r="D409" t="n">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="E409" t="n">
-        <v>258</v>
+        <v>329</v>
       </c>
       <c r="F409" t="n">
-        <v>256</v>
+        <v>333</v>
       </c>
       <c r="G409" t="n">
-        <v>255</v>
+        <v>334</v>
       </c>
       <c r="H409" t="n">
-        <v>259</v>
+        <v>347</v>
       </c>
       <c r="I409" t="n">
-        <v>256</v>
+        <v>332</v>
       </c>
       <c r="J409" t="n">
-        <v>254</v>
+        <v>325</v>
       </c>
       <c r="K409" t="n">
-        <v>255</v>
+        <v>328</v>
       </c>
       <c r="L409" t="n">
-        <v>255</v>
+        <v>327</v>
       </c>
       <c r="M409" t="n">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="N409" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="O409" t="n">
         <v>0</v>
@@ -42307,40 +42307,40 @@
         <v>370</v>
       </c>
       <c r="C411" t="n">
-        <v>259</v>
+        <v>325</v>
       </c>
       <c r="D411" t="n">
-        <v>255</v>
+        <v>321</v>
       </c>
       <c r="E411" t="n">
-        <v>255</v>
+        <v>327</v>
       </c>
       <c r="F411" t="n">
-        <v>253</v>
+        <v>327</v>
       </c>
       <c r="G411" t="n">
-        <v>258</v>
+        <v>324</v>
       </c>
       <c r="H411" t="n">
-        <v>254</v>
+        <v>326</v>
       </c>
       <c r="I411" t="n">
-        <v>255</v>
+        <v>327</v>
       </c>
       <c r="J411" t="n">
-        <v>250</v>
+        <v>314</v>
       </c>
       <c r="K411" t="n">
-        <v>256</v>
+        <v>313</v>
       </c>
       <c r="L411" t="n">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="M411" t="n">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="N411" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="O411" t="n">
         <v>0</v>
@@ -42931,25 +42931,25 @@
         <v>65</v>
       </c>
       <c r="E417" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F417" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G417" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H417" t="n">
         <v>65</v>
       </c>
       <c r="I417" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J417" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K417" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L417" t="n">
         <v>65</v>
@@ -42958,7 +42958,7 @@
         <v>65</v>
       </c>
       <c r="N417" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="O417" t="n">
         <v>0</v>
@@ -43134,37 +43134,37 @@
         <v>50</v>
       </c>
       <c r="D419" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E419" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F419" t="n">
         <v>51</v>
       </c>
       <c r="G419" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H419" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I419" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J419" t="n">
         <v>50</v>
       </c>
       <c r="K419" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L419" t="n">
         <v>50</v>
       </c>
       <c r="M419" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N419" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="O419" t="n">
         <v>0</v>
@@ -43337,37 +43337,37 @@
         <v>100</v>
       </c>
       <c r="C421" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D421" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E421" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F421" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G421" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H421" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I421" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J421" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="K421" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L421" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M421" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="N421" t="n">
         <v>0</v>
@@ -43543,40 +43543,40 @@
         <v>100</v>
       </c>
       <c r="C423" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D423" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="E423" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F423" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G423" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H423" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I423" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="J423" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K423" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="L423" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M423" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="N423" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="O423" t="n">
         <v>0</v>
@@ -43749,40 +43749,40 @@
         <v>165</v>
       </c>
       <c r="C425" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D425" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E425" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F425" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G425" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H425" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I425" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J425" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K425" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L425" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M425" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N425" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="O425" t="n">
         <v>0</v>
@@ -44367,40 +44367,40 @@
         <v>100</v>
       </c>
       <c r="C431" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D431" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="E431" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F431" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G431" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="H431" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I431" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="J431" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="K431" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="L431" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="M431" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="N431" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O431" t="n">
         <v>0</v>
@@ -44573,40 +44573,40 @@
         <v>170</v>
       </c>
       <c r="C433" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D433" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E433" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F433" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G433" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H433" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I433" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J433" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K433" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L433" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M433" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N433" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="O433" t="n">
         <v>0</v>
@@ -44779,40 +44779,40 @@
         <v>100</v>
       </c>
       <c r="C435" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D435" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E435" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F435" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G435" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="H435" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="I435" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="J435" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="K435" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L435" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M435" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="N435" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="O435" t="n">
         <v>0</v>
@@ -45838,7 +45838,7 @@
         <v>1</v>
       </c>
       <c r="N445" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O445" t="n">
         <v>0</v>
@@ -46042,7 +46042,7 @@
         <v>1</v>
       </c>
       <c r="N447" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O447" t="n">
         <v>0</v>
@@ -46248,7 +46248,7 @@
         <v>1</v>
       </c>
       <c r="N449" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O449" t="n">
         <v>0</v>
@@ -46421,40 +46421,40 @@
         <v>323</v>
       </c>
       <c r="C451" t="n">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D451" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="E451" t="n">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="F451" t="n">
-        <v>248</v>
+        <v>297</v>
       </c>
       <c r="G451" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="H451" t="n">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="I451" t="n">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="J451" t="n">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="K451" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L451" t="n">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="M451" t="n">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="N451" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="O451" t="n">
         <v>0</v>
@@ -46833,40 +46833,40 @@
         <v>615</v>
       </c>
       <c r="C455" t="n">
-        <v>398</v>
+        <v>586</v>
       </c>
       <c r="D455" t="n">
-        <v>380</v>
+        <v>530</v>
       </c>
       <c r="E455" t="n">
-        <v>359</v>
+        <v>502</v>
       </c>
       <c r="F455" t="n">
-        <v>354</v>
+        <v>504</v>
       </c>
       <c r="G455" t="n">
-        <v>348</v>
+        <v>497</v>
       </c>
       <c r="H455" t="n">
-        <v>356</v>
+        <v>500</v>
       </c>
       <c r="I455" t="n">
-        <v>355</v>
+        <v>503</v>
       </c>
       <c r="J455" t="n">
-        <v>352</v>
+        <v>531</v>
       </c>
       <c r="K455" t="n">
-        <v>399</v>
+        <v>579</v>
       </c>
       <c r="L455" t="n">
-        <v>436</v>
+        <v>584</v>
       </c>
       <c r="M455" t="n">
-        <v>498</v>
+        <v>588</v>
       </c>
       <c r="N455" t="n">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="O455" t="n">
         <v>0</v>
@@ -47039,40 +47039,40 @@
         <v>280</v>
       </c>
       <c r="C457" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D457" t="n">
+        <v>202</v>
+      </c>
+      <c r="E457" t="n">
+        <v>202</v>
+      </c>
+      <c r="F457" t="n">
+        <v>203</v>
+      </c>
+      <c r="G457" t="n">
+        <v>198</v>
+      </c>
+      <c r="H457" t="n">
+        <v>198</v>
+      </c>
+      <c r="I457" t="n">
         <v>201</v>
       </c>
-      <c r="E457" t="n">
+      <c r="J457" t="n">
         <v>201</v>
       </c>
-      <c r="F457" t="n">
-        <v>201</v>
-      </c>
-      <c r="G457" t="n">
-        <v>199</v>
-      </c>
-      <c r="H457" t="n">
-        <v>202</v>
-      </c>
-      <c r="I457" t="n">
-        <v>200</v>
-      </c>
-      <c r="J457" t="n">
-        <v>197</v>
-      </c>
       <c r="K457" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="L457" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="M457" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="N457" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="O457" t="n">
         <v>0</v>
@@ -48069,40 +48069,40 @@
         <v>610</v>
       </c>
       <c r="C467" t="n">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="D467" t="n">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="E467" t="n">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="F467" t="n">
-        <v>392</v>
+        <v>496</v>
       </c>
       <c r="G467" t="n">
-        <v>340</v>
+        <v>492</v>
       </c>
       <c r="H467" t="n">
-        <v>349</v>
+        <v>485</v>
       </c>
       <c r="I467" t="n">
-        <v>347</v>
+        <v>496</v>
       </c>
       <c r="J467" t="n">
-        <v>351</v>
+        <v>513</v>
       </c>
       <c r="K467" t="n">
-        <v>404</v>
+        <v>591</v>
       </c>
       <c r="L467" t="n">
-        <v>451</v>
+        <v>594</v>
       </c>
       <c r="M467" t="n">
-        <v>488</v>
+        <v>595</v>
       </c>
       <c r="N467" t="n">
-        <v>496</v>
+        <v>0</v>
       </c>
       <c r="O467" t="n">
         <v>0</v>
@@ -48275,40 +48275,40 @@
         <v>610</v>
       </c>
       <c r="C469" t="n">
-        <v>530</v>
+        <v>501</v>
       </c>
       <c r="D469" t="n">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E469" t="n">
-        <v>467</v>
+        <v>505</v>
       </c>
       <c r="F469" t="n">
-        <v>397</v>
+        <v>497</v>
       </c>
       <c r="G469" t="n">
-        <v>349</v>
+        <v>497</v>
       </c>
       <c r="H469" t="n">
-        <v>352</v>
+        <v>497</v>
       </c>
       <c r="I469" t="n">
-        <v>355</v>
+        <v>497</v>
       </c>
       <c r="J469" t="n">
-        <v>354</v>
+        <v>539</v>
       </c>
       <c r="K469" t="n">
-        <v>403</v>
+        <v>604</v>
       </c>
       <c r="L469" t="n">
-        <v>450</v>
+        <v>602</v>
       </c>
       <c r="M469" t="n">
-        <v>490</v>
+        <v>606</v>
       </c>
       <c r="N469" t="n">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="O469" t="n">
         <v>0</v>
@@ -48481,40 +48481,40 @@
         <v>811</v>
       </c>
       <c r="C471" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D471" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E471" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F471" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G471" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H471" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I471" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J471" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K471" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L471" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="M471" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="N471" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O471" t="n">
         <v>0</v>
@@ -48687,40 +48687,40 @@
         <v>610</v>
       </c>
       <c r="C473" t="n">
-        <v>401</v>
+        <v>548</v>
       </c>
       <c r="D473" t="n">
-        <v>351</v>
+        <v>521</v>
       </c>
       <c r="E473" t="n">
-        <v>350</v>
+        <v>488</v>
       </c>
       <c r="F473" t="n">
-        <v>350</v>
+        <v>486</v>
       </c>
       <c r="G473" t="n">
-        <v>351</v>
+        <v>491</v>
       </c>
       <c r="H473" t="n">
-        <v>351</v>
+        <v>501</v>
       </c>
       <c r="I473" t="n">
-        <v>350</v>
+        <v>503</v>
       </c>
       <c r="J473" t="n">
-        <v>350</v>
+        <v>530</v>
       </c>
       <c r="K473" t="n">
-        <v>395</v>
+        <v>593</v>
       </c>
       <c r="L473" t="n">
-        <v>442</v>
+        <v>624</v>
       </c>
       <c r="M473" t="n">
-        <v>489</v>
+        <v>603</v>
       </c>
       <c r="N473" t="n">
-        <v>484</v>
+        <v>0</v>
       </c>
       <c r="O473" t="n">
         <v>0</v>
@@ -49099,7 +49099,7 @@
         <v>35.86615</v>
       </c>
       <c r="C477" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D477" t="n">
         <v>34</v>
@@ -49111,16 +49111,16 @@
         <v>34</v>
       </c>
       <c r="G477" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H477" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I477" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J477" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K477" t="n">
         <v>34</v>
@@ -49132,7 +49132,7 @@
         <v>33</v>
       </c>
       <c r="N477" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O477" t="n">
         <v>0</v>
@@ -49619,46 +49619,46 @@
         <v>18.3</v>
       </c>
       <c r="C483" t="n">
-        <v>6.12</v>
+        <v>5.99</v>
       </c>
       <c r="D483" t="n">
-        <v>6.45</v>
+        <v>6.21</v>
       </c>
       <c r="E483" t="n">
-        <v>6.48</v>
+        <v>6.52</v>
       </c>
       <c r="F483" t="n">
-        <v>5.96</v>
+        <v>6.25</v>
       </c>
       <c r="G483" t="n">
-        <v>6.09</v>
+        <v>6.17</v>
       </c>
       <c r="H483" t="n">
-        <v>5.73</v>
+        <v>6.4</v>
       </c>
       <c r="I483" t="n">
-        <v>5.79</v>
+        <v>6.02</v>
       </c>
       <c r="J483" t="n">
-        <v>6.24</v>
+        <v>6.51</v>
       </c>
       <c r="K483" t="n">
-        <v>6.24</v>
+        <v>5.99</v>
       </c>
       <c r="L483" t="n">
-        <v>5.95</v>
+        <v>5.89</v>
       </c>
       <c r="M483" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="N483" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="O483" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="P483" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q483" t="n">
         <v>0</v>
@@ -50443,46 +50443,46 @@
         <v>102.23</v>
       </c>
       <c r="C491" t="n">
-        <v>98.54000000000001</v>
+        <v>100.33</v>
       </c>
       <c r="D491" t="n">
-        <v>99.36</v>
+        <v>100.28</v>
       </c>
       <c r="E491" t="n">
-        <v>98.97</v>
+        <v>100.29</v>
       </c>
       <c r="F491" t="n">
-        <v>99.23</v>
+        <v>100.11</v>
       </c>
       <c r="G491" t="n">
-        <v>99.41</v>
+        <v>99.94</v>
       </c>
       <c r="H491" t="n">
-        <v>99.31999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I491" t="n">
-        <v>99.36</v>
+        <v>100.09</v>
       </c>
       <c r="J491" t="n">
-        <v>99.27</v>
+        <v>100.52</v>
       </c>
       <c r="K491" t="n">
-        <v>99.31999999999999</v>
+        <v>100.15</v>
       </c>
       <c r="L491" t="n">
-        <v>99.33</v>
+        <v>100.28</v>
       </c>
       <c r="M491" t="n">
-        <v>60.4</v>
+        <v>100.03</v>
       </c>
       <c r="N491" t="n">
-        <v>99.7</v>
+        <v>100.39</v>
       </c>
       <c r="O491" t="n">
-        <v>99.40000000000001</v>
+        <v>100.37</v>
       </c>
       <c r="P491" t="n">
-        <v>99.2</v>
+        <v>0</v>
       </c>
       <c r="Q491" t="n">
         <v>0</v>
@@ -50649,46 +50649,46 @@
         <v>130.44</v>
       </c>
       <c r="C493" t="n">
+        <v>85.95999999999999</v>
+      </c>
+      <c r="D493" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="E493" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="F493" t="n">
+        <v>85.98999999999999</v>
+      </c>
+      <c r="G493" t="n">
         <v>86.23</v>
       </c>
-      <c r="D493" t="n">
-        <v>86.14</v>
-      </c>
-      <c r="E493" t="n">
-        <v>86.06999999999999</v>
-      </c>
-      <c r="F493" t="n">
-        <v>86.05</v>
-      </c>
-      <c r="G493" t="n">
-        <v>86.09999999999999</v>
-      </c>
       <c r="H493" t="n">
-        <v>86.06999999999999</v>
+        <v>86.58</v>
       </c>
       <c r="I493" t="n">
-        <v>85.84</v>
+        <v>86.47</v>
       </c>
       <c r="J493" t="n">
-        <v>86.40000000000001</v>
+        <v>86.19</v>
       </c>
       <c r="K493" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="L493" t="n">
         <v>85.93000000000001</v>
       </c>
-      <c r="L493" t="n">
-        <v>85.7</v>
-      </c>
       <c r="M493" t="n">
-        <v>85.48</v>
+        <v>85.73</v>
       </c>
       <c r="N493" t="n">
-        <v>85.48</v>
+        <v>85.95</v>
       </c>
       <c r="O493" t="n">
-        <v>86.01000000000001</v>
+        <v>85.87</v>
       </c>
       <c r="P493" t="n">
-        <v>85.98999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q493" t="n">
         <v>0</v>
@@ -50855,13 +50855,13 @@
         <v>40</v>
       </c>
       <c r="C495" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="D495" t="n">
-        <v>30.4</v>
+        <v>0</v>
       </c>
       <c r="E495" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="F495" t="n">
         <v>0</v>
@@ -51061,7 +51061,7 @@
         <v>40</v>
       </c>
       <c r="C497" t="n">
-        <v>30.67</v>
+        <v>0</v>
       </c>
       <c r="D497" t="n">
         <v>0</v>
@@ -51267,13 +51267,13 @@
         <v>16.67</v>
       </c>
       <c r="C499" t="n">
-        <v>11.34</v>
+        <v>0</v>
       </c>
       <c r="D499" t="n">
-        <v>11.07</v>
+        <v>0</v>
       </c>
       <c r="E499" t="n">
-        <v>11.07</v>
+        <v>0</v>
       </c>
       <c r="F499" t="n">
         <v>0</v>
@@ -51473,16 +51473,16 @@
         <v>16.67</v>
       </c>
       <c r="C501" t="n">
-        <v>10.77</v>
+        <v>0</v>
       </c>
       <c r="D501" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E501" t="n">
-        <v>11.47</v>
+        <v>0</v>
       </c>
       <c r="F501" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="G501" t="n">
         <v>0</v>
@@ -51679,16 +51679,16 @@
         <v>16.67</v>
       </c>
       <c r="C503" t="n">
-        <v>10.85</v>
+        <v>0</v>
       </c>
       <c r="D503" t="n">
-        <v>10.88</v>
+        <v>0</v>
       </c>
       <c r="E503" t="n">
-        <v>11.38</v>
+        <v>0</v>
       </c>
       <c r="F503" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="G503" t="n">
         <v>0</v>
@@ -51885,46 +51885,46 @@
         <v>15.2</v>
       </c>
       <c r="C505" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="D505" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="E505" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="F505" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="G505" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="H505" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="I505" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J505" t="n">
         <v>14.16</v>
       </c>
-      <c r="D505" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="E505" t="n">
-        <v>13.37</v>
-      </c>
-      <c r="F505" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="G505" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="H505" t="n">
-        <v>13.73</v>
-      </c>
-      <c r="I505" t="n">
-        <v>13.51</v>
-      </c>
-      <c r="J505" t="n">
-        <v>14</v>
-      </c>
       <c r="K505" t="n">
-        <v>13.99</v>
+        <v>14.01</v>
       </c>
       <c r="L505" t="n">
-        <v>13.53</v>
+        <v>14.26</v>
       </c>
       <c r="M505" t="n">
-        <v>14.76</v>
+        <v>14.32</v>
       </c>
       <c r="N505" t="n">
-        <v>14.03</v>
+        <v>13.64</v>
       </c>
       <c r="O505" t="n">
-        <v>13.63</v>
+        <v>12.86</v>
       </c>
       <c r="P505" t="n">
-        <v>13.54</v>
+        <v>0</v>
       </c>
       <c r="Q505" t="n">
         <v>0</v>
@@ -52091,46 +52091,46 @@
         <v>15.2</v>
       </c>
       <c r="C507" t="n">
-        <v>13.5</v>
+        <v>14.37</v>
       </c>
       <c r="D507" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="E507" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="F507" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="G507" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="H507" t="n">
         <v>14.43</v>
       </c>
-      <c r="E507" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="F507" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="G507" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="H507" t="n">
-        <v>14.07</v>
-      </c>
       <c r="I507" t="n">
-        <v>14.39</v>
+        <v>14.82</v>
       </c>
       <c r="J507" t="n">
-        <v>14.68</v>
+        <v>15.36</v>
       </c>
       <c r="K507" t="n">
-        <v>14.08</v>
+        <v>15.24</v>
       </c>
       <c r="L507" t="n">
-        <v>14.1</v>
+        <v>14.75</v>
       </c>
       <c r="M507" t="n">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="N507" t="n">
-        <v>14.47</v>
+        <v>13.68</v>
       </c>
       <c r="O507" t="n">
-        <v>15.14</v>
+        <v>14.17</v>
       </c>
       <c r="P507" t="n">
-        <v>14.96</v>
+        <v>0</v>
       </c>
       <c r="Q507" t="n">
         <v>0</v>
@@ -52297,46 +52297,46 @@
         <v>15.2</v>
       </c>
       <c r="C509" t="n">
-        <v>13.56</v>
+        <v>13.01</v>
       </c>
       <c r="D509" t="n">
-        <v>14.2</v>
+        <v>13.36</v>
       </c>
       <c r="E509" t="n">
-        <v>13.78</v>
+        <v>13.6</v>
       </c>
       <c r="F509" t="n">
-        <v>13.73</v>
+        <v>14.62</v>
       </c>
       <c r="G509" t="n">
-        <v>14.24</v>
+        <v>15.12</v>
       </c>
       <c r="H509" t="n">
-        <v>12.83</v>
+        <v>14.91</v>
       </c>
       <c r="I509" t="n">
-        <v>14.36</v>
+        <v>14.89</v>
       </c>
       <c r="J509" t="n">
-        <v>14.12</v>
+        <v>14.85</v>
       </c>
       <c r="K509" t="n">
-        <v>14.13</v>
+        <v>14.73</v>
       </c>
       <c r="L509" t="n">
-        <v>14.18</v>
+        <v>15.02</v>
       </c>
       <c r="M509" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="N509" t="n">
-        <v>13.58</v>
+        <v>14.7</v>
       </c>
       <c r="O509" t="n">
-        <v>13.75</v>
+        <v>13.54</v>
       </c>
       <c r="P509" t="n">
-        <v>14.14</v>
+        <v>0</v>
       </c>
       <c r="Q509" t="n">
         <v>0</v>
@@ -52503,46 +52503,46 @@
         <v>15.2</v>
       </c>
       <c r="C511" t="n">
-        <v>13.58</v>
+        <v>0</v>
       </c>
       <c r="D511" t="n">
-        <v>13.54</v>
+        <v>0</v>
       </c>
       <c r="E511" t="n">
-        <v>13.76</v>
+        <v>0</v>
       </c>
       <c r="F511" t="n">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="G511" t="n">
-        <v>13.98</v>
+        <v>0</v>
       </c>
       <c r="H511" t="n">
-        <v>12.78</v>
+        <v>0</v>
       </c>
       <c r="I511" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="J511" t="n">
-        <v>13.76</v>
+        <v>0</v>
       </c>
       <c r="K511" t="n">
-        <v>13.99</v>
+        <v>0</v>
       </c>
       <c r="L511" t="n">
-        <v>13.28</v>
+        <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>14.22</v>
+        <v>0</v>
       </c>
       <c r="N511" t="n">
-        <v>10.72</v>
+        <v>0</v>
       </c>
       <c r="O511" t="n">
-        <v>14.06</v>
+        <v>0</v>
       </c>
       <c r="P511" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="Q511" t="n">
         <v>0</v>
@@ -52709,46 +52709,46 @@
         <v>15.2</v>
       </c>
       <c r="C513" t="n">
-        <v>13.46</v>
+        <v>14</v>
       </c>
       <c r="D513" t="n">
-        <v>15.19</v>
+        <v>14.86</v>
       </c>
       <c r="E513" t="n">
-        <v>13.56</v>
+        <v>15.29</v>
       </c>
       <c r="F513" t="n">
-        <v>13.81</v>
+        <v>14.48</v>
       </c>
       <c r="G513" t="n">
-        <v>14.62</v>
+        <v>13.76</v>
       </c>
       <c r="H513" t="n">
-        <v>14.33</v>
+        <v>14.09</v>
       </c>
       <c r="I513" t="n">
-        <v>13.15</v>
+        <v>15</v>
       </c>
       <c r="J513" t="n">
-        <v>13.17</v>
+        <v>13.62</v>
       </c>
       <c r="K513" t="n">
-        <v>13.86</v>
+        <v>14.71</v>
       </c>
       <c r="L513" t="n">
-        <v>14.43</v>
+        <v>14.58</v>
       </c>
       <c r="M513" t="n">
-        <v>13.65</v>
+        <v>15.41</v>
       </c>
       <c r="N513" t="n">
-        <v>13.54</v>
+        <v>13.92</v>
       </c>
       <c r="O513" t="n">
-        <v>12.74</v>
+        <v>15.53</v>
       </c>
       <c r="P513" t="n">
-        <v>13.88</v>
+        <v>0</v>
       </c>
       <c r="Q513" t="n">
         <v>0</v>
@@ -52915,46 +52915,46 @@
         <v>15.2</v>
       </c>
       <c r="C515" t="n">
-        <v>14.51</v>
+        <v>14.67</v>
       </c>
       <c r="D515" t="n">
-        <v>13.12</v>
+        <v>15.06</v>
       </c>
       <c r="E515" t="n">
-        <v>13.65</v>
+        <v>14.33</v>
       </c>
       <c r="F515" t="n">
-        <v>13.55</v>
+        <v>14.95</v>
       </c>
       <c r="G515" t="n">
-        <v>14.54</v>
+        <v>14.66</v>
       </c>
       <c r="H515" t="n">
-        <v>14.88</v>
+        <v>14.15</v>
       </c>
       <c r="I515" t="n">
-        <v>13.68</v>
+        <v>13.75</v>
       </c>
       <c r="J515" t="n">
-        <v>14.2</v>
+        <v>14.03</v>
       </c>
       <c r="K515" t="n">
-        <v>14.26</v>
+        <v>15.75</v>
       </c>
       <c r="L515" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="M515" t="n">
-        <v>14.36</v>
+        <v>15.11</v>
       </c>
       <c r="N515" t="n">
-        <v>13.44</v>
+        <v>14.98</v>
       </c>
       <c r="O515" t="n">
-        <v>14.43</v>
+        <v>14.63</v>
       </c>
       <c r="P515" t="n">
-        <v>13.35</v>
+        <v>0</v>
       </c>
       <c r="Q515" t="n">
         <v>0</v>
@@ -53121,46 +53121,46 @@
         <v>15.2</v>
       </c>
       <c r="C517" t="n">
-        <v>11.83</v>
+        <v>0</v>
       </c>
       <c r="D517" t="n">
-        <v>13.03</v>
+        <v>0</v>
       </c>
       <c r="E517" t="n">
-        <v>13.55</v>
+        <v>0</v>
       </c>
       <c r="F517" t="n">
-        <v>13.08</v>
+        <v>0</v>
       </c>
       <c r="G517" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="H517" t="n">
-        <v>13.64</v>
+        <v>0</v>
       </c>
       <c r="I517" t="n">
-        <v>13.49</v>
+        <v>0</v>
       </c>
       <c r="J517" t="n">
-        <v>13.82</v>
+        <v>0</v>
       </c>
       <c r="K517" t="n">
-        <v>13.56</v>
+        <v>0</v>
       </c>
       <c r="L517" t="n">
-        <v>13.64</v>
+        <v>0</v>
       </c>
       <c r="M517" t="n">
-        <v>13.17</v>
+        <v>0</v>
       </c>
       <c r="N517" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="O517" t="n">
-        <v>13.76</v>
+        <v>0</v>
       </c>
       <c r="P517" t="n">
-        <v>14.03</v>
+        <v>0</v>
       </c>
       <c r="Q517" t="n">
         <v>0</v>
@@ -53327,46 +53327,46 @@
         <v>15.2</v>
       </c>
       <c r="C519" t="n">
-        <v>14.55</v>
+        <v>12.1</v>
       </c>
       <c r="D519" t="n">
-        <v>14.79</v>
+        <v>11.45</v>
       </c>
       <c r="E519" t="n">
-        <v>13.96</v>
+        <v>11.91</v>
       </c>
       <c r="F519" t="n">
-        <v>14.64</v>
+        <v>11.24</v>
       </c>
       <c r="G519" t="n">
-        <v>14.03</v>
+        <v>11.66</v>
       </c>
       <c r="H519" t="n">
-        <v>13.8</v>
+        <v>11.14</v>
       </c>
       <c r="I519" t="n">
-        <v>14.5</v>
+        <v>11.43</v>
       </c>
       <c r="J519" t="n">
-        <v>14.02</v>
+        <v>13.41</v>
       </c>
       <c r="K519" t="n">
-        <v>14.1</v>
+        <v>12.9</v>
       </c>
       <c r="L519" t="n">
-        <v>14.44</v>
+        <v>13.4</v>
       </c>
       <c r="M519" t="n">
-        <v>13.23</v>
+        <v>12.77</v>
       </c>
       <c r="N519" t="n">
-        <v>13.06</v>
+        <v>13.38</v>
       </c>
       <c r="O519" t="n">
-        <v>14.47</v>
+        <v>13.24</v>
       </c>
       <c r="P519" t="n">
-        <v>13.76</v>
+        <v>0</v>
       </c>
       <c r="Q519" t="n">
         <v>0</v>
@@ -53533,46 +53533,46 @@
         <v>15.2</v>
       </c>
       <c r="C521" t="n">
-        <v>13.53</v>
+        <v>13.89</v>
       </c>
       <c r="D521" t="n">
-        <v>13.03</v>
+        <v>12.87</v>
       </c>
       <c r="E521" t="n">
-        <v>12.45</v>
+        <v>13.96</v>
       </c>
       <c r="F521" t="n">
-        <v>13.21</v>
+        <v>13.04</v>
       </c>
       <c r="G521" t="n">
-        <v>12.91</v>
+        <v>13.27</v>
       </c>
       <c r="H521" t="n">
-        <v>13.5</v>
+        <v>13.42</v>
       </c>
       <c r="I521" t="n">
-        <v>13.05</v>
+        <v>13.78</v>
       </c>
       <c r="J521" t="n">
-        <v>12.8</v>
+        <v>12.51</v>
       </c>
       <c r="K521" t="n">
-        <v>12.6</v>
+        <v>13.63</v>
       </c>
       <c r="L521" t="n">
-        <v>11.99</v>
+        <v>12.79</v>
       </c>
       <c r="M521" t="n">
-        <v>12.54</v>
+        <v>12.58</v>
       </c>
       <c r="N521" t="n">
-        <v>13.72</v>
+        <v>14.09</v>
       </c>
       <c r="O521" t="n">
-        <v>13.24</v>
+        <v>13.19</v>
       </c>
       <c r="P521" t="n">
-        <v>13.79</v>
+        <v>0</v>
       </c>
       <c r="Q521" t="n">
         <v>0</v>
@@ -53739,46 +53739,46 @@
         <v>15.2</v>
       </c>
       <c r="C523" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="D523" t="n">
-        <v>12.33</v>
+        <v>0</v>
       </c>
       <c r="E523" t="n">
-        <v>13.21</v>
+        <v>0</v>
       </c>
       <c r="F523" t="n">
-        <v>13.29</v>
+        <v>0</v>
       </c>
       <c r="G523" t="n">
-        <v>12.05</v>
+        <v>0</v>
       </c>
       <c r="H523" t="n">
-        <v>13.29</v>
+        <v>0</v>
       </c>
       <c r="I523" t="n">
-        <v>13.08</v>
+        <v>0</v>
       </c>
       <c r="J523" t="n">
-        <v>12.95</v>
+        <v>0</v>
       </c>
       <c r="K523" t="n">
-        <v>13.16</v>
+        <v>0</v>
       </c>
       <c r="L523" t="n">
-        <v>13.18</v>
+        <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>13.53</v>
+        <v>0</v>
       </c>
       <c r="N523" t="n">
-        <v>13.03</v>
+        <v>0</v>
       </c>
       <c r="O523" t="n">
-        <v>13.31</v>
+        <v>0</v>
       </c>
       <c r="P523" t="n">
-        <v>12.88</v>
+        <v>0</v>
       </c>
       <c r="Q523" t="n">
         <v>0</v>
@@ -53945,46 +53945,46 @@
         <v>15.2</v>
       </c>
       <c r="C525" t="n">
-        <v>15.14</v>
+        <v>0</v>
       </c>
       <c r="D525" t="n">
-        <v>14.98</v>
+        <v>0</v>
       </c>
       <c r="E525" t="n">
-        <v>14.86</v>
+        <v>0</v>
       </c>
       <c r="F525" t="n">
-        <v>15.26</v>
+        <v>0</v>
       </c>
       <c r="G525" t="n">
-        <v>14.61</v>
+        <v>0</v>
       </c>
       <c r="H525" t="n">
-        <v>13.31</v>
+        <v>0</v>
       </c>
       <c r="I525" t="n">
-        <v>14.45</v>
+        <v>0</v>
       </c>
       <c r="J525" t="n">
-        <v>14.21</v>
+        <v>0</v>
       </c>
       <c r="K525" t="n">
-        <v>14.58</v>
+        <v>0</v>
       </c>
       <c r="L525" t="n">
-        <v>14.4</v>
+        <v>0</v>
       </c>
       <c r="M525" t="n">
-        <v>14.92</v>
+        <v>0</v>
       </c>
       <c r="N525" t="n">
-        <v>14.51</v>
+        <v>0</v>
       </c>
       <c r="O525" t="n">
-        <v>13.76</v>
+        <v>0</v>
       </c>
       <c r="P525" t="n">
-        <v>13.73</v>
+        <v>0</v>
       </c>
       <c r="Q525" t="n">
         <v>0</v>
@@ -54151,46 +54151,46 @@
         <v>15.2</v>
       </c>
       <c r="C527" t="n">
-        <v>14</v>
+        <v>14.58</v>
       </c>
       <c r="D527" t="n">
-        <v>14.09</v>
+        <v>15.01</v>
       </c>
       <c r="E527" t="n">
-        <v>14.28</v>
+        <v>14.56</v>
       </c>
       <c r="F527" t="n">
-        <v>14.43</v>
+        <v>14.93</v>
       </c>
       <c r="G527" t="n">
-        <v>14.24</v>
+        <v>14.7</v>
       </c>
       <c r="H527" t="n">
-        <v>13.23</v>
+        <v>14.11</v>
       </c>
       <c r="I527" t="n">
-        <v>13.48</v>
+        <v>15.38</v>
       </c>
       <c r="J527" t="n">
-        <v>13.54</v>
+        <v>14.29</v>
       </c>
       <c r="K527" t="n">
-        <v>13.26</v>
+        <v>15.14</v>
       </c>
       <c r="L527" t="n">
-        <v>13.4</v>
+        <v>14.65</v>
       </c>
       <c r="M527" t="n">
-        <v>13.46</v>
+        <v>13.44</v>
       </c>
       <c r="N527" t="n">
-        <v>13.73</v>
+        <v>14.92</v>
       </c>
       <c r="O527" t="n">
-        <v>14.03</v>
+        <v>14.62</v>
       </c>
       <c r="P527" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="Q527" t="n">
         <v>0</v>
@@ -54357,46 +54357,46 @@
         <v>125</v>
       </c>
       <c r="C529" t="n">
-        <v>125.99</v>
+        <v>90.3</v>
       </c>
       <c r="D529" t="n">
-        <v>124.27</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="E529" t="n">
-        <v>124.68</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="F529" t="n">
-        <v>97.88</v>
+        <v>80.42</v>
       </c>
       <c r="G529" t="n">
-        <v>62.92</v>
+        <v>71.69</v>
       </c>
       <c r="H529" t="n">
-        <v>62.71</v>
+        <v>68.48</v>
       </c>
       <c r="I529" t="n">
-        <v>62.86</v>
+        <v>62.76</v>
       </c>
       <c r="J529" t="n">
-        <v>62.68</v>
+        <v>64</v>
       </c>
       <c r="K529" t="n">
-        <v>62.93</v>
+        <v>62.77</v>
       </c>
       <c r="L529" t="n">
-        <v>63.58</v>
+        <v>71.44</v>
       </c>
       <c r="M529" t="n">
-        <v>70.06999999999999</v>
+        <v>80.56</v>
       </c>
       <c r="N529" t="n">
-        <v>70.09999999999999</v>
+        <v>85.44</v>
       </c>
       <c r="O529" t="n">
-        <v>69.11</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="P529" t="n">
-        <v>69.77</v>
+        <v>0</v>
       </c>
       <c r="Q529" t="n">
         <v>0</v>
@@ -54563,46 +54563,46 @@
         <v>125</v>
       </c>
       <c r="C531" t="n">
-        <v>123.21</v>
+        <v>91.48</v>
       </c>
       <c r="D531" t="n">
-        <v>124.7</v>
+        <v>87.92</v>
       </c>
       <c r="E531" t="n">
-        <v>124.49</v>
+        <v>80.31</v>
       </c>
       <c r="F531" t="n">
-        <v>95.01000000000001</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="G531" t="n">
-        <v>61.78</v>
+        <v>69.55</v>
       </c>
       <c r="H531" t="n">
-        <v>61.89</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="I531" t="n">
-        <v>62.75</v>
+        <v>62.11</v>
       </c>
       <c r="J531" t="n">
-        <v>61.42</v>
+        <v>62.41</v>
       </c>
       <c r="K531" t="n">
-        <v>61.88</v>
+        <v>62.7</v>
       </c>
       <c r="L531" t="n">
-        <v>63.04</v>
+        <v>70.41</v>
       </c>
       <c r="M531" t="n">
-        <v>68.43000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="N531" t="n">
-        <v>69.2</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="O531" t="n">
-        <v>68.95</v>
+        <v>90.89</v>
       </c>
       <c r="P531" t="n">
-        <v>69.29000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q531" t="n">
         <v>0</v>
@@ -54769,46 +54769,46 @@
         <v>130</v>
       </c>
       <c r="C533" t="n">
-        <v>131.42</v>
+        <v>91.44</v>
       </c>
       <c r="D533" t="n">
-        <v>130.06</v>
+        <v>88.47</v>
       </c>
       <c r="E533" t="n">
-        <v>129.54</v>
+        <v>90.17</v>
       </c>
       <c r="F533" t="n">
-        <v>100.72</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="G533" t="n">
-        <v>63.83</v>
+        <v>69.34</v>
       </c>
       <c r="H533" t="n">
-        <v>66.09</v>
+        <v>65.34</v>
       </c>
       <c r="I533" t="n">
-        <v>65.48</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="J533" t="n">
-        <v>66.23</v>
+        <v>64.22</v>
       </c>
       <c r="K533" t="n">
-        <v>66.48</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L533" t="n">
-        <v>65.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="M533" t="n">
-        <v>69.44</v>
+        <v>78.19</v>
       </c>
       <c r="N533" t="n">
-        <v>71.09999999999999</v>
+        <v>85.11</v>
       </c>
       <c r="O533" t="n">
-        <v>69.48</v>
+        <v>90.5</v>
       </c>
       <c r="P533" t="n">
-        <v>70.41</v>
+        <v>0</v>
       </c>
       <c r="Q533" t="n">
         <v>0</v>
@@ -55423,10 +55423,10 @@
         <v>0</v>
       </c>
       <c r="O539" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="P539" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q539" t="n">
         <v>0</v>
@@ -56003,46 +56003,46 @@
       </c>
       <c r="B545" t="inlineStr"/>
       <c r="C545" t="n">
-        <v>25605.9916</v>
+        <v>28252.25</v>
       </c>
       <c r="D545" t="n">
-        <v>25423.01693</v>
+        <v>27983.22</v>
       </c>
       <c r="E545" t="n">
-        <v>25379.85157</v>
+        <v>27769.14</v>
       </c>
       <c r="F545" t="n">
-        <v>24909.24505</v>
+        <v>27447.14</v>
       </c>
       <c r="G545" t="n">
-        <v>24569.35191</v>
+        <v>27186.56</v>
       </c>
       <c r="H545" t="n">
-        <v>24461.51241</v>
+        <v>26872.16</v>
       </c>
       <c r="I545" t="n">
-        <v>24469.7777</v>
+        <v>26775.62</v>
       </c>
       <c r="J545" t="n">
-        <v>24591.52878</v>
+        <v>26905.08</v>
       </c>
       <c r="K545" t="n">
-        <v>25426.01585</v>
+        <v>27562.91</v>
       </c>
       <c r="L545" t="n">
-        <v>26025.24211</v>
+        <v>28034.1</v>
       </c>
       <c r="M545" t="n">
-        <v>26602.92807</v>
+        <v>28644.16</v>
       </c>
       <c r="N545" t="n">
-        <v>26489.78626</v>
+        <v>563.8200000000001</v>
       </c>
       <c r="O545" t="n">
-        <v>559.63</v>
+        <v>576.49</v>
       </c>
       <c r="P545" t="n">
-        <v>566.76</v>
+        <v>0</v>
       </c>
       <c r="Q545" t="n">
         <v>0</v>

--- a/raw/RT.xlsx
+++ b/raw/RT.xlsx
@@ -406,242 +406,242 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>00.30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>01.00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>01.30</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>02.00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>02.30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>03.00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>03.30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>04.00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>04.30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>05.00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>05.30</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>06.00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>06.30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>07.00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>07.30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>08.00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>08.30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>09.00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>09.30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>15.30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>16.30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>17.30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>19.30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>21.30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>22.30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>23.30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>24:00</t>
         </is>
       </c>
     </row>
@@ -846,28 +846,28 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1050,28 +1050,28 @@
         <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1256,28 +1256,28 @@
         <v>248</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1462,28 +1462,28 @@
         <v>252</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1668,28 +1668,28 @@
         <v>262</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>363</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1874,28 +1874,28 @@
         <v>408</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2080,28 +2080,28 @@
         <v>402</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2286,28 +2286,28 @@
         <v>408</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>519</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2492,28 +2492,28 @@
         <v>88</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2698,28 +2698,28 @@
         <v>84</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2871,61 +2871,61 @@
         <v>125</v>
       </c>
       <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>2</v>
       </c>
-      <c r="D25" t="n">
+      <c r="P25" t="n">
         <v>2</v>
       </c>
-      <c r="E25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3110,28 +3110,28 @@
         <v>81</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3316,28 +3316,28 @@
         <v>40</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -3522,28 +3522,28 @@
         <v>85</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -3937,25 +3937,25 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4140,28 +4140,28 @@
         <v>250</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4346,28 +4346,28 @@
         <v>233</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -4552,28 +4552,28 @@
         <v>219</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -4931,61 +4931,61 @@
         <v>283.25</v>
       </c>
       <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="D45" t="n">
+      <c r="P45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="n">
+      <c r="Q45" t="n">
         <v>1</v>
       </c>
-      <c r="F45" t="n">
+      <c r="R45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" t="n">
+      <c r="S45" t="n">
         <v>1</v>
       </c>
-      <c r="H45" t="n">
+      <c r="T45" t="n">
         <v>1</v>
       </c>
-      <c r="I45" t="n">
+      <c r="U45" t="n">
         <v>1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -5376,28 +5376,28 @@
         <v>57</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -5582,28 +5582,28 @@
         <v>57</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -5788,28 +5788,28 @@
         <v>57</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -7230,28 +7230,28 @@
         <v>63</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -7403,61 +7403,61 @@
         <v>212</v>
       </c>
       <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
         <v>1</v>
       </c>
-      <c r="D69" t="n">
+      <c r="P69" t="n">
         <v>1</v>
       </c>
-      <c r="E69" t="n">
+      <c r="Q69" t="n">
         <v>1</v>
       </c>
-      <c r="F69" t="n">
+      <c r="R69" t="n">
         <v>1</v>
       </c>
-      <c r="G69" t="n">
+      <c r="S69" t="n">
         <v>1</v>
       </c>
-      <c r="H69" t="n">
+      <c r="T69" t="n">
         <v>1</v>
       </c>
-      <c r="I69" t="n">
+      <c r="U69" t="n">
         <v>1</v>
-      </c>
-      <c r="J69" t="n">
-        <v>1</v>
-      </c>
-      <c r="K69" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" t="n">
-        <v>1</v>
-      </c>
-      <c r="M69" t="n">
-        <v>1</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -7642,28 +7642,28 @@
         <v>104</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -7848,28 +7848,28 @@
         <v>264</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -8054,28 +8054,28 @@
         <v>248</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -8260,28 +8260,28 @@
         <v>468</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>484</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>487</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>484</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>477</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -8433,10 +8433,10 @@
         <v>323</v>
       </c>
       <c r="C79" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D79" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E79" t="n">
         <v>257</v>
@@ -8451,13 +8451,13 @@
         <v>258</v>
       </c>
       <c r="I79" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J79" t="n">
         <v>257</v>
       </c>
       <c r="K79" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L79" t="n">
         <v>257</v>
@@ -8466,28 +8466,28 @@
         <v>258</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -8672,28 +8672,28 @@
         <v>256</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -8845,61 +8845,61 @@
         <v>323</v>
       </c>
       <c r="C83" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D83" t="n">
+        <v>253</v>
+      </c>
+      <c r="E83" t="n">
+        <v>253</v>
+      </c>
+      <c r="F83" t="n">
+        <v>253</v>
+      </c>
+      <c r="G83" t="n">
+        <v>253</v>
+      </c>
+      <c r="H83" t="n">
+        <v>253</v>
+      </c>
+      <c r="I83" t="n">
+        <v>253</v>
+      </c>
+      <c r="J83" t="n">
+        <v>253</v>
+      </c>
+      <c r="K83" t="n">
+        <v>253</v>
+      </c>
+      <c r="L83" t="n">
+        <v>253</v>
+      </c>
+      <c r="M83" t="n">
+        <v>252</v>
+      </c>
+      <c r="N83" t="n">
+        <v>253</v>
+      </c>
+      <c r="O83" t="n">
         <v>255</v>
       </c>
-      <c r="E83" t="n">
+      <c r="P83" t="n">
+        <v>255</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>255</v>
+      </c>
+      <c r="R83" t="n">
         <v>254</v>
       </c>
-      <c r="F83" t="n">
+      <c r="S83" t="n">
         <v>255</v>
       </c>
-      <c r="G83" t="n">
+      <c r="T83" t="n">
         <v>255</v>
       </c>
-      <c r="H83" t="n">
+      <c r="U83" t="n">
         <v>255</v>
-      </c>
-      <c r="I83" t="n">
-        <v>255</v>
-      </c>
-      <c r="J83" t="n">
-        <v>255</v>
-      </c>
-      <c r="K83" t="n">
-        <v>255</v>
-      </c>
-      <c r="L83" t="n">
-        <v>255</v>
-      </c>
-      <c r="M83" t="n">
-        <v>255</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -9051,61 +9051,61 @@
         <v>280</v>
       </c>
       <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
         <v>3</v>
       </c>
-      <c r="D85" t="n">
+      <c r="P85" t="n">
         <v>3</v>
       </c>
-      <c r="E85" t="n">
+      <c r="Q85" t="n">
         <v>3</v>
       </c>
-      <c r="F85" t="n">
+      <c r="R85" t="n">
         <v>3</v>
       </c>
-      <c r="G85" t="n">
+      <c r="S85" t="n">
         <v>3</v>
       </c>
-      <c r="H85" t="n">
+      <c r="T85" t="n">
         <v>3</v>
       </c>
-      <c r="I85" t="n">
+      <c r="U85" t="n">
         <v>3</v>
-      </c>
-      <c r="J85" t="n">
-        <v>3</v>
-      </c>
-      <c r="K85" t="n">
-        <v>3</v>
-      </c>
-      <c r="L85" t="n">
-        <v>3</v>
-      </c>
-      <c r="M85" t="n">
-        <v>3</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" t="n">
-        <v>0</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -9290,28 +9290,28 @@
         <v>273</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -9463,61 +9463,61 @@
         <v>280</v>
       </c>
       <c r="C89" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D89" t="n">
+        <v>273</v>
+      </c>
+      <c r="E89" t="n">
+        <v>273</v>
+      </c>
+      <c r="F89" t="n">
+        <v>276</v>
+      </c>
+      <c r="G89" t="n">
+        <v>273</v>
+      </c>
+      <c r="H89" t="n">
+        <v>272</v>
+      </c>
+      <c r="I89" t="n">
+        <v>274</v>
+      </c>
+      <c r="J89" t="n">
+        <v>274</v>
+      </c>
+      <c r="K89" t="n">
+        <v>270</v>
+      </c>
+      <c r="L89" t="n">
+        <v>273</v>
+      </c>
+      <c r="M89" t="n">
+        <v>274</v>
+      </c>
+      <c r="N89" t="n">
+        <v>276</v>
+      </c>
+      <c r="O89" t="n">
+        <v>277</v>
+      </c>
+      <c r="P89" t="n">
+        <v>276</v>
+      </c>
+      <c r="Q89" t="n">
         <v>275</v>
       </c>
-      <c r="E89" t="n">
-        <v>278</v>
-      </c>
-      <c r="F89" t="n">
-        <v>278</v>
-      </c>
-      <c r="G89" t="n">
+      <c r="R89" t="n">
+        <v>275</v>
+      </c>
+      <c r="S89" t="n">
+        <v>275</v>
+      </c>
+      <c r="T89" t="n">
+        <v>277</v>
+      </c>
+      <c r="U89" t="n">
         <v>274</v>
-      </c>
-      <c r="H89" t="n">
-        <v>273</v>
-      </c>
-      <c r="I89" t="n">
-        <v>275</v>
-      </c>
-      <c r="J89" t="n">
-        <v>276</v>
-      </c>
-      <c r="K89" t="n">
-        <v>271</v>
-      </c>
-      <c r="L89" t="n">
-        <v>275</v>
-      </c>
-      <c r="M89" t="n">
-        <v>276</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
@@ -9702,28 +9702,28 @@
         <v>197</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -9875,61 +9875,61 @@
         <v>371.5</v>
       </c>
       <c r="C93" t="n">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="D93" t="n">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="E93" t="n">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F93" t="n">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="G93" t="n">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="H93" t="n">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I93" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="J93" t="n">
+        <v>256</v>
+      </c>
+      <c r="K93" t="n">
+        <v>264</v>
+      </c>
+      <c r="L93" t="n">
         <v>250</v>
       </c>
-      <c r="K93" t="n">
-        <v>258</v>
-      </c>
-      <c r="L93" t="n">
-        <v>254</v>
-      </c>
       <c r="M93" t="n">
+        <v>259</v>
+      </c>
+      <c r="N93" t="n">
         <v>264</v>
       </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
@@ -10114,28 +10114,28 @@
         <v>94</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="V95" t="n">
         <v>0</v>
@@ -10526,28 +10526,28 @@
         <v>25</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
@@ -10735,25 +10735,25 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
@@ -10950,16 +10950,16 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -11144,28 +11144,28 @@
         <v>96</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U105" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -11350,28 +11350,28 @@
         <v>34</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -11523,61 +11523,61 @@
         <v>235</v>
       </c>
       <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
         <v>1</v>
       </c>
-      <c r="D109" t="n">
+      <c r="P109" t="n">
         <v>1</v>
       </c>
-      <c r="E109" t="n">
+      <c r="Q109" t="n">
         <v>1</v>
       </c>
-      <c r="F109" t="n">
+      <c r="R109" t="n">
         <v>1</v>
       </c>
-      <c r="G109" t="n">
+      <c r="S109" t="n">
         <v>1</v>
       </c>
-      <c r="H109" t="n">
+      <c r="T109" t="n">
         <v>1</v>
       </c>
-      <c r="I109" t="n">
+      <c r="U109" t="n">
         <v>1</v>
-      </c>
-      <c r="J109" t="n">
-        <v>1</v>
-      </c>
-      <c r="K109" t="n">
-        <v>1</v>
-      </c>
-      <c r="L109" t="n">
-        <v>1</v>
-      </c>
-      <c r="M109" t="n">
-        <v>1</v>
-      </c>
-      <c r="N109" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" t="n">
-        <v>0</v>
-      </c>
-      <c r="U109" t="n">
-        <v>0</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -11762,28 +11762,28 @@
         <v>159</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -11968,28 +11968,28 @@
         <v>40</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -12353,7 +12353,7 @@
         <v>116</v>
       </c>
       <c r="E117" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F117" t="n">
         <v>109</v>
@@ -12380,28 +12380,28 @@
         <v>127</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="S117" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="T117" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="U117" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -12586,28 +12586,28 @@
         <v>236</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -12792,28 +12792,28 @@
         <v>64</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
@@ -12998,28 +12998,28 @@
         <v>64</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="S123" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="T123" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="U123" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
@@ -13204,28 +13204,28 @@
         <v>63</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="T125" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="U125" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
@@ -13614,28 +13614,28 @@
         <v>604</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>597</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>602</v>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="T129" t="n">
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="U129" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="V129" t="n">
         <v>0</v>
@@ -13787,61 +13787,61 @@
         <v>991</v>
       </c>
       <c r="C131" t="n">
+        <v>924</v>
+      </c>
+      <c r="D131" t="n">
         <v>928</v>
       </c>
-      <c r="D131" t="n">
-        <v>927</v>
-      </c>
       <c r="E131" t="n">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="F131" t="n">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="G131" t="n">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="H131" t="n">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="I131" t="n">
+        <v>866</v>
+      </c>
+      <c r="J131" t="n">
+        <v>864</v>
+      </c>
+      <c r="K131" t="n">
+        <v>864</v>
+      </c>
+      <c r="L131" t="n">
+        <v>867</v>
+      </c>
+      <c r="M131" t="n">
+        <v>863</v>
+      </c>
+      <c r="N131" t="n">
+        <v>857</v>
+      </c>
+      <c r="O131" t="n">
         <v>861</v>
       </c>
-      <c r="J131" t="n">
-        <v>859</v>
-      </c>
-      <c r="K131" t="n">
+      <c r="P131" t="n">
         <v>865</v>
       </c>
-      <c r="L131" t="n">
-        <v>864</v>
-      </c>
-      <c r="M131" t="n">
-        <v>864</v>
-      </c>
-      <c r="N131" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>924</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>914</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>911</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -14232,28 +14232,28 @@
         <v>797</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>736</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>847</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>847</v>
       </c>
       <c r="S135" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>983</v>
       </c>
       <c r="U135" t="n">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -14438,28 +14438,28 @@
         <v>797</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>766</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>736</v>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>736</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>845</v>
       </c>
       <c r="S137" t="n">
-        <v>0</v>
+        <v>894</v>
       </c>
       <c r="T137" t="n">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="U137" t="n">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -14611,40 +14611,40 @@
         <v>14.48911</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -14956,28 +14956,28 @@
         <v>2</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V143" t="n">
         <v>0</v>
@@ -15160,28 +15160,28 @@
         <v>6</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S145" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V145" t="n">
         <v>0</v>
@@ -15364,28 +15364,28 @@
         <v>3</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U147" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V147" t="n">
         <v>0</v>
@@ -15772,28 +15772,28 @@
         <v>6</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S151" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T151" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U151" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V151" t="n">
         <v>0</v>
@@ -15999,7 +15999,7 @@
         <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="V153" t="n">
         <v>0</v>
@@ -16596,7 +16596,7 @@
         <v>96</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -16802,28 +16802,28 @@
         <v>30</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O161" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S161" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T161" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="U161" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
@@ -17008,28 +17008,28 @@
         <v>52</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="O163" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="S163" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="T163" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="U163" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="V163" t="n">
         <v>0</v>
@@ -17214,28 +17214,28 @@
         <v>53</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="S165" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="T165" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="U165" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -17420,28 +17420,28 @@
         <v>47</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O167" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="S167" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="T167" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="U167" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -17626,28 +17626,28 @@
         <v>42</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="O169" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="S169" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="U169" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -17832,28 +17832,28 @@
         <v>42</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="O171" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="S171" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="T171" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="U171" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
@@ -19686,7 +19686,7 @@
         <v>90</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -21128,28 +21128,28 @@
         <v>47</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="O203" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="P203" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Q203" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="S203" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="T203" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="U203" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="V203" t="n">
         <v>0</v>
@@ -21343,19 +21343,19 @@
         <v>0</v>
       </c>
       <c r="Q205" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S205" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="T205" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U205" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V205" t="n">
         <v>0</v>
@@ -21540,28 +21540,28 @@
         <v>100</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S207" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T207" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U207" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V207" t="n">
         <v>0</v>
@@ -21752,22 +21752,22 @@
         <v>0</v>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S209" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T209" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="U209" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V209" t="n">
         <v>0</v>
@@ -22331,61 +22331,61 @@
         <v>140</v>
       </c>
       <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
         <v>100</v>
       </c>
-      <c r="D215" t="n">
+      <c r="P215" t="n">
         <v>100</v>
       </c>
-      <c r="E215" t="n">
+      <c r="Q215" t="n">
         <v>100</v>
       </c>
-      <c r="F215" t="n">
+      <c r="R215" t="n">
         <v>100</v>
       </c>
-      <c r="G215" t="n">
+      <c r="S215" t="n">
         <v>100</v>
       </c>
-      <c r="H215" t="n">
+      <c r="T215" t="n">
         <v>100</v>
       </c>
-      <c r="I215" t="n">
+      <c r="U215" t="n">
         <v>100</v>
-      </c>
-      <c r="J215" t="n">
-        <v>100</v>
-      </c>
-      <c r="K215" t="n">
-        <v>100</v>
-      </c>
-      <c r="L215" t="n">
-        <v>100</v>
-      </c>
-      <c r="M215" t="n">
-        <v>100</v>
-      </c>
-      <c r="N215" t="n">
-        <v>0</v>
-      </c>
-      <c r="O215" t="n">
-        <v>0</v>
-      </c>
-      <c r="P215" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0</v>
-      </c>
-      <c r="S215" t="n">
-        <v>0</v>
-      </c>
-      <c r="T215" t="n">
-        <v>0</v>
-      </c>
-      <c r="U215" t="n">
-        <v>0</v>
       </c>
       <c r="V215" t="n">
         <v>0</v>
@@ -23188,28 +23188,28 @@
         <v>194</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="O223" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P223" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="Q223" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="R223" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="S223" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="T223" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="U223" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="V223" t="n">
         <v>0</v>
@@ -23394,28 +23394,28 @@
         <v>194</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="O225" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="S225" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="T225" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="U225" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="V225" t="n">
         <v>0</v>
@@ -23600,28 +23600,28 @@
         <v>200</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="O227" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="P227" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="Q227" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="R227" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="S227" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="T227" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="U227" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="V227" t="n">
         <v>0</v>
@@ -23806,28 +23806,28 @@
         <v>23</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O229" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="P229" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q229" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R229" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S229" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T229" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="U229" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V229" t="n">
         <v>0</v>
@@ -24012,28 +24012,28 @@
         <v>23</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O231" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="P231" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q231" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S231" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T231" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="U231" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V231" t="n">
         <v>0</v>
@@ -24218,28 +24218,28 @@
         <v>23</v>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O233" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="P233" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q233" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S233" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T233" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="U233" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V233" t="n">
         <v>0</v>
@@ -24424,28 +24424,28 @@
         <v>27</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O235" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="P235" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q235" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R235" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S235" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="T235" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="U235" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V235" t="n">
         <v>0</v>
@@ -24630,28 +24630,28 @@
         <v>27</v>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O237" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S237" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="T237" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="U237" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V237" t="n">
         <v>0</v>
@@ -25042,28 +25042,28 @@
         <v>92</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="O241" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="P241" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="Q241" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="S241" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="T241" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="U241" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V241" t="n">
         <v>0</v>
@@ -25248,28 +25248,28 @@
         <v>127</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O243" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P243" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q243" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="S243" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="T243" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U243" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="V243" t="n">
         <v>0</v>
@@ -25454,28 +25454,28 @@
         <v>108</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="P245" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="Q245" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="S245" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="T245" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="U245" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="V245" t="n">
         <v>0</v>
@@ -25660,28 +25660,28 @@
         <v>116</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="O247" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="P247" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="Q247" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="S247" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="T247" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="U247" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="V247" t="n">
         <v>0</v>
@@ -25866,28 +25866,28 @@
         <v>27</v>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O249" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S249" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="T249" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="U249" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="V249" t="n">
         <v>0</v>
@@ -26072,28 +26072,28 @@
         <v>60</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O251" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P251" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q251" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="R251" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="S251" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="T251" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="U251" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="V251" t="n">
         <v>0</v>
@@ -26278,28 +26278,28 @@
         <v>33</v>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O253" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="P253" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Q253" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="S253" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="T253" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="U253" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="V253" t="n">
         <v>0</v>
@@ -26484,28 +26484,28 @@
         <v>644</v>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="O255" t="n">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="P255" t="n">
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="Q255" t="n">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="R255" t="n">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="S255" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="T255" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="U255" t="n">
-        <v>0</v>
+        <v>644</v>
       </c>
       <c r="V255" t="n">
         <v>0</v>
@@ -26863,61 +26863,61 @@
         <v>35.5</v>
       </c>
       <c r="C259" t="n">
+        <v>0</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" t="n">
+        <v>0</v>
+      </c>
+      <c r="M259" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
         <v>1</v>
       </c>
-      <c r="D259" t="n">
+      <c r="P259" t="n">
         <v>1</v>
       </c>
-      <c r="E259" t="n">
+      <c r="Q259" t="n">
         <v>1</v>
       </c>
-      <c r="F259" t="n">
+      <c r="R259" t="n">
         <v>1</v>
       </c>
-      <c r="G259" t="n">
+      <c r="S259" t="n">
         <v>1</v>
       </c>
-      <c r="H259" t="n">
+      <c r="T259" t="n">
         <v>1</v>
       </c>
-      <c r="I259" t="n">
+      <c r="U259" t="n">
         <v>1</v>
-      </c>
-      <c r="J259" t="n">
-        <v>1</v>
-      </c>
-      <c r="K259" t="n">
-        <v>1</v>
-      </c>
-      <c r="L259" t="n">
-        <v>1</v>
-      </c>
-      <c r="M259" t="n">
-        <v>1</v>
-      </c>
-      <c r="N259" t="n">
-        <v>0</v>
-      </c>
-      <c r="O259" t="n">
-        <v>0</v>
-      </c>
-      <c r="P259" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
-      <c r="R259" t="n">
-        <v>0</v>
-      </c>
-      <c r="S259" t="n">
-        <v>0</v>
-      </c>
-      <c r="T259" t="n">
-        <v>0</v>
-      </c>
-      <c r="U259" t="n">
-        <v>0</v>
       </c>
       <c r="V259" t="n">
         <v>0</v>
@@ -27308,28 +27308,28 @@
         <v>57</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="O263" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="P263" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="Q263" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="R263" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="S263" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="T263" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="U263" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="V263" t="n">
         <v>0</v>
@@ -27514,28 +27514,28 @@
         <v>16</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O265" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P265" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q265" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R265" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S265" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T265" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="U265" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V265" t="n">
         <v>0</v>
@@ -27926,28 +27926,28 @@
         <v>694</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="O269" t="n">
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="P269" t="n">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="Q269" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="R269" t="n">
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="S269" t="n">
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="T269" t="n">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="U269" t="n">
-        <v>0</v>
+        <v>749</v>
       </c>
       <c r="V269" t="n">
         <v>0</v>
@@ -28132,28 +28132,28 @@
         <v>673</v>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="O271" t="n">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="P271" t="n">
-        <v>0</v>
+        <v>484</v>
       </c>
       <c r="Q271" t="n">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="R271" t="n">
-        <v>0</v>
+        <v>582</v>
       </c>
       <c r="S271" t="n">
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="T271" t="n">
-        <v>0</v>
+        <v>747</v>
       </c>
       <c r="U271" t="n">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="V271" t="n">
         <v>0</v>
@@ -28338,28 +28338,28 @@
         <v>914</v>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>912</v>
       </c>
       <c r="O273" t="n">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>826</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>895</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="S273" t="n">
-        <v>0</v>
+        <v>933</v>
       </c>
       <c r="T273" t="n">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="U273" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="V273" t="n">
         <v>0</v>
@@ -28547,25 +28547,25 @@
         <v>0</v>
       </c>
       <c r="O275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P275" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q275" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R275" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S275" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T275" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="U275" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="V275" t="n">
         <v>0</v>
@@ -28753,25 +28753,25 @@
         <v>0</v>
       </c>
       <c r="O277" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q277" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S277" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="T277" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="U277" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="V277" t="n">
         <v>0</v>
@@ -29235,61 +29235,61 @@
       </c>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="n">
+        <v>3.49669</v>
+      </c>
+      <c r="D283" t="n">
+        <v>3.51176</v>
+      </c>
+      <c r="E283" t="n">
+        <v>3.50449</v>
+      </c>
+      <c r="F283" t="n">
+        <v>3.49702</v>
+      </c>
+      <c r="G283" t="n">
+        <v>3.50263</v>
+      </c>
+      <c r="H283" t="n">
+        <v>3.50322</v>
+      </c>
+      <c r="I283" t="n">
+        <v>3.50131</v>
+      </c>
+      <c r="J283" t="n">
+        <v>3.49386</v>
+      </c>
+      <c r="K283" t="n">
+        <v>3.50061</v>
+      </c>
+      <c r="L283" t="n">
+        <v>3.49928</v>
+      </c>
+      <c r="M283" t="n">
+        <v>3.49906</v>
+      </c>
+      <c r="N283" t="n">
+        <v>3.5024</v>
+      </c>
+      <c r="O283" t="n">
         <v>4</v>
       </c>
-      <c r="D283" t="n">
+      <c r="P283" t="n">
         <v>4</v>
       </c>
-      <c r="E283" t="n">
+      <c r="Q283" t="n">
         <v>4</v>
       </c>
-      <c r="F283" t="n">
+      <c r="R283" t="n">
         <v>4</v>
       </c>
-      <c r="G283" t="n">
+      <c r="S283" t="n">
         <v>4</v>
       </c>
-      <c r="H283" t="n">
+      <c r="T283" t="n">
         <v>4</v>
       </c>
-      <c r="I283" t="n">
+      <c r="U283" t="n">
         <v>4</v>
-      </c>
-      <c r="J283" t="n">
-        <v>3</v>
-      </c>
-      <c r="K283" t="n">
-        <v>4</v>
-      </c>
-      <c r="L283" t="n">
-        <v>4</v>
-      </c>
-      <c r="M283" t="n">
-        <v>4</v>
-      </c>
-      <c r="N283" t="n">
-        <v>0</v>
-      </c>
-      <c r="O283" t="n">
-        <v>0</v>
-      </c>
-      <c r="P283" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
-      <c r="R283" t="n">
-        <v>0</v>
-      </c>
-      <c r="S283" t="n">
-        <v>0</v>
-      </c>
-      <c r="T283" t="n">
-        <v>0</v>
-      </c>
-      <c r="U283" t="n">
-        <v>0</v>
       </c>
       <c r="V283" t="n">
         <v>0</v>
@@ -29439,61 +29439,61 @@
       </c>
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="n">
+        <v>2.63034</v>
+      </c>
+      <c r="D285" t="n">
+        <v>2.64104</v>
+      </c>
+      <c r="E285" t="n">
+        <v>2.64441</v>
+      </c>
+      <c r="F285" t="n">
+        <v>2.63596</v>
+      </c>
+      <c r="G285" t="n">
+        <v>2.64513</v>
+      </c>
+      <c r="H285" t="n">
+        <v>2.63633</v>
+      </c>
+      <c r="I285" t="n">
+        <v>2.64301</v>
+      </c>
+      <c r="J285" t="n">
+        <v>2.64258</v>
+      </c>
+      <c r="K285" t="n">
+        <v>2.63962</v>
+      </c>
+      <c r="L285" t="n">
+        <v>2.64225</v>
+      </c>
+      <c r="M285" t="n">
+        <v>2.64515</v>
+      </c>
+      <c r="N285" t="n">
+        <v>2.6421</v>
+      </c>
+      <c r="O285" t="n">
         <v>3</v>
       </c>
-      <c r="D285" t="n">
+      <c r="P285" t="n">
         <v>3</v>
       </c>
-      <c r="E285" t="n">
+      <c r="Q285" t="n">
         <v>3</v>
       </c>
-      <c r="F285" t="n">
+      <c r="R285" t="n">
         <v>3</v>
       </c>
-      <c r="G285" t="n">
+      <c r="S285" t="n">
         <v>3</v>
       </c>
-      <c r="H285" t="n">
+      <c r="T285" t="n">
         <v>3</v>
       </c>
-      <c r="I285" t="n">
+      <c r="U285" t="n">
         <v>3</v>
-      </c>
-      <c r="J285" t="n">
-        <v>3</v>
-      </c>
-      <c r="K285" t="n">
-        <v>3</v>
-      </c>
-      <c r="L285" t="n">
-        <v>3</v>
-      </c>
-      <c r="M285" t="n">
-        <v>3</v>
-      </c>
-      <c r="N285" t="n">
-        <v>0</v>
-      </c>
-      <c r="O285" t="n">
-        <v>0</v>
-      </c>
-      <c r="P285" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
-      <c r="R285" t="n">
-        <v>0</v>
-      </c>
-      <c r="S285" t="n">
-        <v>0</v>
-      </c>
-      <c r="T285" t="n">
-        <v>0</v>
-      </c>
-      <c r="U285" t="n">
-        <v>0</v>
       </c>
       <c r="V285" t="n">
         <v>0</v>
@@ -29643,61 +29643,61 @@
       </c>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
+        <v>0.44412</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0.46672</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0.46786</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0.48802</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0.49978</v>
+      </c>
+      <c r="H287" t="n">
+        <v>0.52205</v>
+      </c>
+      <c r="I287" t="n">
+        <v>0.54697</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0.51953</v>
+      </c>
+      <c r="K287" t="n">
+        <v>0.50564</v>
+      </c>
+      <c r="L287" t="n">
+        <v>0.51629</v>
+      </c>
+      <c r="M287" t="n">
+        <v>0.49221</v>
+      </c>
+      <c r="N287" t="n">
+        <v>0.42418</v>
+      </c>
+      <c r="O287" t="n">
         <v>2</v>
       </c>
-      <c r="D287" t="n">
+      <c r="P287" t="n">
         <v>2</v>
       </c>
-      <c r="E287" t="n">
+      <c r="Q287" t="n">
         <v>2</v>
       </c>
-      <c r="F287" t="n">
-        <v>2</v>
-      </c>
-      <c r="G287" t="n">
-        <v>2</v>
-      </c>
-      <c r="H287" t="n">
-        <v>2</v>
-      </c>
-      <c r="I287" t="n">
-        <v>2</v>
-      </c>
-      <c r="J287" t="n">
-        <v>2</v>
-      </c>
-      <c r="K287" t="n">
-        <v>2</v>
-      </c>
-      <c r="L287" t="n">
-        <v>2</v>
-      </c>
-      <c r="M287" t="n">
-        <v>2</v>
-      </c>
-      <c r="N287" t="n">
-        <v>0</v>
-      </c>
-      <c r="O287" t="n">
-        <v>0</v>
-      </c>
-      <c r="P287" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S287" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T287" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U287" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V287" t="n">
         <v>0</v>
@@ -30669,52 +30669,52 @@
       </c>
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="n">
+        <v>5.8742</v>
+      </c>
+      <c r="D297" t="n">
+        <v>5.86385</v>
+      </c>
+      <c r="E297" t="n">
+        <v>5.86441</v>
+      </c>
+      <c r="F297" t="n">
+        <v>5.87601</v>
+      </c>
+      <c r="G297" t="n">
+        <v>5.86228</v>
+      </c>
+      <c r="H297" t="n">
+        <v>5.87512</v>
+      </c>
+      <c r="I297" t="n">
+        <v>5.86922</v>
+      </c>
+      <c r="J297" t="n">
+        <v>5.87356</v>
+      </c>
+      <c r="K297" t="n">
+        <v>5.86484</v>
+      </c>
+      <c r="L297" t="n">
+        <v>5.8714</v>
+      </c>
+      <c r="M297" t="n">
+        <v>5.85255</v>
+      </c>
+      <c r="N297" t="n">
+        <v>5.85852</v>
+      </c>
+      <c r="O297" t="n">
         <v>6</v>
       </c>
-      <c r="D297" t="n">
+      <c r="P297" t="n">
         <v>6</v>
       </c>
-      <c r="E297" t="n">
+      <c r="Q297" t="n">
         <v>6</v>
       </c>
-      <c r="F297" t="n">
+      <c r="R297" t="n">
         <v>6</v>
-      </c>
-      <c r="G297" t="n">
-        <v>6</v>
-      </c>
-      <c r="H297" t="n">
-        <v>6</v>
-      </c>
-      <c r="I297" t="n">
-        <v>6</v>
-      </c>
-      <c r="J297" t="n">
-        <v>6</v>
-      </c>
-      <c r="K297" t="n">
-        <v>6</v>
-      </c>
-      <c r="L297" t="n">
-        <v>6</v>
-      </c>
-      <c r="M297" t="n">
-        <v>6</v>
-      </c>
-      <c r="N297" t="n">
-        <v>0</v>
-      </c>
-      <c r="O297" t="n">
-        <v>0</v>
-      </c>
-      <c r="P297" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
-      <c r="R297" t="n">
-        <v>0</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -31285,61 +31285,61 @@
         <v>126</v>
       </c>
       <c r="C303" t="n">
-        <v>26</v>
+        <v>26.09862</v>
       </c>
       <c r="D303" t="n">
-        <v>26</v>
+        <v>26.35423</v>
       </c>
       <c r="E303" t="n">
+        <v>30.43414</v>
+      </c>
+      <c r="F303" t="n">
+        <v>30.61309</v>
+      </c>
+      <c r="G303" t="n">
+        <v>30.58935</v>
+      </c>
+      <c r="H303" t="n">
+        <v>30.34866</v>
+      </c>
+      <c r="I303" t="n">
+        <v>30.72043</v>
+      </c>
+      <c r="J303" t="n">
+        <v>30.97141</v>
+      </c>
+      <c r="K303" t="n">
+        <v>30.61903</v>
+      </c>
+      <c r="L303" t="n">
+        <v>30.97292</v>
+      </c>
+      <c r="M303" t="n">
+        <v>30.77374</v>
+      </c>
+      <c r="N303" t="n">
+        <v>30.20533</v>
+      </c>
+      <c r="O303" t="n">
+        <v>31</v>
+      </c>
+      <c r="P303" t="n">
         <v>30</v>
       </c>
-      <c r="F303" t="n">
+      <c r="Q303" t="n">
         <v>31</v>
       </c>
-      <c r="G303" t="n">
+      <c r="R303" t="n">
         <v>31</v>
       </c>
-      <c r="H303" t="n">
+      <c r="S303" t="n">
+        <v>32</v>
+      </c>
+      <c r="T303" t="n">
+        <v>31</v>
+      </c>
+      <c r="U303" t="n">
         <v>30</v>
-      </c>
-      <c r="I303" t="n">
-        <v>31</v>
-      </c>
-      <c r="J303" t="n">
-        <v>31</v>
-      </c>
-      <c r="K303" t="n">
-        <v>31</v>
-      </c>
-      <c r="L303" t="n">
-        <v>31</v>
-      </c>
-      <c r="M303" t="n">
-        <v>31</v>
-      </c>
-      <c r="N303" t="n">
-        <v>0</v>
-      </c>
-      <c r="O303" t="n">
-        <v>0</v>
-      </c>
-      <c r="P303" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
-      <c r="R303" t="n">
-        <v>0</v>
-      </c>
-      <c r="S303" t="n">
-        <v>0</v>
-      </c>
-      <c r="T303" t="n">
-        <v>0</v>
-      </c>
-      <c r="U303" t="n">
-        <v>0</v>
       </c>
       <c r="V303" t="n">
         <v>0</v>
@@ -31545,7 +31545,7 @@
         <v>0</v>
       </c>
       <c r="U305" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V305" t="n">
         <v>0</v>
@@ -31697,61 +31697,61 @@
         <v>93</v>
       </c>
       <c r="C307" t="n">
-        <v>82</v>
+        <v>82.04858</v>
       </c>
       <c r="D307" t="n">
-        <v>81</v>
+        <v>81.05588</v>
       </c>
       <c r="E307" t="n">
+        <v>92.04407999999999</v>
+      </c>
+      <c r="F307" t="n">
+        <v>91.74724000000001</v>
+      </c>
+      <c r="G307" t="n">
+        <v>91.50704</v>
+      </c>
+      <c r="H307" t="n">
+        <v>91.67704000000001</v>
+      </c>
+      <c r="I307" t="n">
+        <v>91.41982</v>
+      </c>
+      <c r="J307" t="n">
+        <v>91.22631</v>
+      </c>
+      <c r="K307" t="n">
+        <v>91.09712</v>
+      </c>
+      <c r="L307" t="n">
+        <v>91.62885</v>
+      </c>
+      <c r="M307" t="n">
+        <v>91.99822</v>
+      </c>
+      <c r="N307" t="n">
+        <v>91.5231</v>
+      </c>
+      <c r="O307" t="n">
         <v>92</v>
       </c>
-      <c r="F307" t="n">
+      <c r="P307" t="n">
         <v>92</v>
       </c>
-      <c r="G307" t="n">
+      <c r="Q307" t="n">
         <v>92</v>
       </c>
-      <c r="H307" t="n">
+      <c r="R307" t="n">
         <v>92</v>
       </c>
-      <c r="I307" t="n">
+      <c r="S307" t="n">
+        <v>92</v>
+      </c>
+      <c r="T307" t="n">
+        <v>92</v>
+      </c>
+      <c r="U307" t="n">
         <v>91</v>
-      </c>
-      <c r="J307" t="n">
-        <v>91</v>
-      </c>
-      <c r="K307" t="n">
-        <v>91</v>
-      </c>
-      <c r="L307" t="n">
-        <v>92</v>
-      </c>
-      <c r="M307" t="n">
-        <v>92</v>
-      </c>
-      <c r="N307" t="n">
-        <v>0</v>
-      </c>
-      <c r="O307" t="n">
-        <v>0</v>
-      </c>
-      <c r="P307" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
-      <c r="R307" t="n">
-        <v>0</v>
-      </c>
-      <c r="S307" t="n">
-        <v>0</v>
-      </c>
-      <c r="T307" t="n">
-        <v>0</v>
-      </c>
-      <c r="U307" t="n">
-        <v>0</v>
       </c>
       <c r="V307" t="n">
         <v>0</v>
@@ -32109,61 +32109,61 @@
         <v>126</v>
       </c>
       <c r="C311" t="n">
-        <v>27</v>
+        <v>26.64414</v>
       </c>
       <c r="D311" t="n">
-        <v>67</v>
+        <v>67.20168</v>
       </c>
       <c r="E311" t="n">
+        <v>33.59052</v>
+      </c>
+      <c r="F311" t="n">
+        <v>33.65657</v>
+      </c>
+      <c r="G311" t="n">
+        <v>33.86303</v>
+      </c>
+      <c r="H311" t="n">
+        <v>33.85482</v>
+      </c>
+      <c r="I311" t="n">
+        <v>33.91759</v>
+      </c>
+      <c r="J311" t="n">
+        <v>33.85151</v>
+      </c>
+      <c r="K311" t="n">
+        <v>33.55093</v>
+      </c>
+      <c r="L311" t="n">
+        <v>33.56644</v>
+      </c>
+      <c r="M311" t="n">
+        <v>33.62851</v>
+      </c>
+      <c r="N311" t="n">
+        <v>33.79096</v>
+      </c>
+      <c r="O311" t="n">
+        <v>33</v>
+      </c>
+      <c r="P311" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q311" t="n">
         <v>34</v>
       </c>
-      <c r="F311" t="n">
-        <v>34</v>
-      </c>
-      <c r="G311" t="n">
-        <v>34</v>
-      </c>
-      <c r="H311" t="n">
-        <v>34</v>
-      </c>
-      <c r="I311" t="n">
-        <v>34</v>
-      </c>
-      <c r="J311" t="n">
-        <v>34</v>
-      </c>
-      <c r="K311" t="n">
-        <v>34</v>
-      </c>
-      <c r="L311" t="n">
-        <v>34</v>
-      </c>
-      <c r="M311" t="n">
-        <v>34</v>
-      </c>
-      <c r="N311" t="n">
-        <v>0</v>
-      </c>
-      <c r="O311" t="n">
-        <v>0</v>
-      </c>
-      <c r="P311" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="S311" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="T311" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="U311" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="V311" t="n">
         <v>0</v>
@@ -32315,10 +32315,10 @@
         <v>93</v>
       </c>
       <c r="C313" t="n">
-        <v>75</v>
+        <v>74.87339</v>
       </c>
       <c r="D313" t="n">
-        <v>60</v>
+        <v>59.59847</v>
       </c>
       <c r="E313" t="n">
         <v>0</v>
@@ -32521,61 +32521,61 @@
         <v>93</v>
       </c>
       <c r="C315" t="n">
-        <v>79</v>
+        <v>79.2165</v>
       </c>
       <c r="D315" t="n">
-        <v>79</v>
+        <v>79.25387000000001</v>
       </c>
       <c r="E315" t="n">
+        <v>91.67877</v>
+      </c>
+      <c r="F315" t="n">
+        <v>92.3111</v>
+      </c>
+      <c r="G315" t="n">
+        <v>92.02173000000001</v>
+      </c>
+      <c r="H315" t="n">
+        <v>92.1721</v>
+      </c>
+      <c r="I315" t="n">
+        <v>92.15299</v>
+      </c>
+      <c r="J315" t="n">
+        <v>92.88762</v>
+      </c>
+      <c r="K315" t="n">
+        <v>92.20581</v>
+      </c>
+      <c r="L315" t="n">
+        <v>91.88500000000001</v>
+      </c>
+      <c r="M315" t="n">
+        <v>91.7983</v>
+      </c>
+      <c r="N315" t="n">
+        <v>92.03057</v>
+      </c>
+      <c r="O315" t="n">
         <v>92</v>
       </c>
-      <c r="F315" t="n">
+      <c r="P315" t="n">
         <v>92</v>
       </c>
-      <c r="G315" t="n">
+      <c r="Q315" t="n">
         <v>92</v>
       </c>
-      <c r="H315" t="n">
+      <c r="R315" t="n">
         <v>92</v>
       </c>
-      <c r="I315" t="n">
+      <c r="S315" t="n">
         <v>92</v>
       </c>
-      <c r="J315" t="n">
-        <v>93</v>
-      </c>
-      <c r="K315" t="n">
+      <c r="T315" t="n">
         <v>92</v>
       </c>
-      <c r="L315" t="n">
+      <c r="U315" t="n">
         <v>92</v>
-      </c>
-      <c r="M315" t="n">
-        <v>92</v>
-      </c>
-      <c r="N315" t="n">
-        <v>0</v>
-      </c>
-      <c r="O315" t="n">
-        <v>0</v>
-      </c>
-      <c r="P315" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
-      <c r="R315" t="n">
-        <v>0</v>
-      </c>
-      <c r="S315" t="n">
-        <v>0</v>
-      </c>
-      <c r="T315" t="n">
-        <v>0</v>
-      </c>
-      <c r="U315" t="n">
-        <v>0</v>
       </c>
       <c r="V315" t="n">
         <v>0</v>
@@ -32766,22 +32766,22 @@
         <v>0</v>
       </c>
       <c r="P317" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="Q317" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="R317" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="S317" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="T317" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="U317" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="V317" t="n">
         <v>0</v>
@@ -33139,61 +33139,61 @@
         <v>615</v>
       </c>
       <c r="C321" t="n">
+        <v>458.77039</v>
+      </c>
+      <c r="D321" t="n">
+        <v>459.50021</v>
+      </c>
+      <c r="E321" t="n">
+        <v>457.35504</v>
+      </c>
+      <c r="F321" t="n">
+        <v>459.96048</v>
+      </c>
+      <c r="G321" t="n">
+        <v>458.47217</v>
+      </c>
+      <c r="H321" t="n">
+        <v>458.55512</v>
+      </c>
+      <c r="I321" t="n">
+        <v>458.89862</v>
+      </c>
+      <c r="J321" t="n">
+        <v>459.32819</v>
+      </c>
+      <c r="K321" t="n">
+        <v>457.83005</v>
+      </c>
+      <c r="L321" t="n">
+        <v>458.5751</v>
+      </c>
+      <c r="M321" t="n">
+        <v>459.81827</v>
+      </c>
+      <c r="N321" t="n">
+        <v>459.04849</v>
+      </c>
+      <c r="O321" t="n">
         <v>459</v>
       </c>
-      <c r="D321" t="n">
+      <c r="P321" t="n">
         <v>460</v>
       </c>
-      <c r="E321" t="n">
+      <c r="Q321" t="n">
+        <v>460</v>
+      </c>
+      <c r="R321" t="n">
+        <v>460</v>
+      </c>
+      <c r="S321" t="n">
+        <v>459</v>
+      </c>
+      <c r="T321" t="n">
         <v>457</v>
       </c>
-      <c r="F321" t="n">
-        <v>460</v>
-      </c>
-      <c r="G321" t="n">
-        <v>458</v>
-      </c>
-      <c r="H321" t="n">
-        <v>459</v>
-      </c>
-      <c r="I321" t="n">
-        <v>459</v>
-      </c>
-      <c r="J321" t="n">
-        <v>459</v>
-      </c>
-      <c r="K321" t="n">
-        <v>458</v>
-      </c>
-      <c r="L321" t="n">
-        <v>459</v>
-      </c>
-      <c r="M321" t="n">
-        <v>460</v>
-      </c>
-      <c r="N321" t="n">
-        <v>0</v>
-      </c>
-      <c r="O321" t="n">
-        <v>0</v>
-      </c>
-      <c r="P321" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
-      <c r="R321" t="n">
-        <v>0</v>
-      </c>
-      <c r="S321" t="n">
-        <v>0</v>
-      </c>
-      <c r="T321" t="n">
-        <v>0</v>
-      </c>
       <c r="U321" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="V321" t="n">
         <v>0</v>
@@ -33345,61 +33345,61 @@
         <v>280</v>
       </c>
       <c r="C323" t="n">
-        <v>251</v>
+        <v>250.80171</v>
       </c>
       <c r="D323" t="n">
-        <v>252</v>
+        <v>251.71555</v>
       </c>
       <c r="E323" t="n">
-        <v>252</v>
+        <v>251.50232</v>
       </c>
       <c r="F323" t="n">
-        <v>250</v>
+        <v>250.21005</v>
       </c>
       <c r="G323" t="n">
-        <v>251</v>
+        <v>251.33714</v>
       </c>
       <c r="H323" t="n">
-        <v>251</v>
+        <v>251.30228</v>
       </c>
       <c r="I323" t="n">
-        <v>252</v>
+        <v>251.55524</v>
       </c>
       <c r="J323" t="n">
-        <v>252</v>
+        <v>252.02911</v>
       </c>
       <c r="K323" t="n">
-        <v>245</v>
+        <v>245.09485</v>
       </c>
       <c r="L323" t="n">
-        <v>243</v>
+        <v>242.63756</v>
       </c>
       <c r="M323" t="n">
+        <v>241.15505</v>
+      </c>
+      <c r="N323" t="n">
+        <v>240.26212</v>
+      </c>
+      <c r="O323" t="n">
+        <v>238</v>
+      </c>
+      <c r="P323" t="n">
+        <v>237</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>238</v>
+      </c>
+      <c r="R323" t="n">
+        <v>238</v>
+      </c>
+      <c r="S323" t="n">
         <v>241</v>
       </c>
-      <c r="N323" t="n">
-        <v>0</v>
-      </c>
-      <c r="O323" t="n">
-        <v>0</v>
-      </c>
-      <c r="P323" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
-      <c r="R323" t="n">
-        <v>0</v>
-      </c>
-      <c r="S323" t="n">
-        <v>0</v>
-      </c>
       <c r="T323" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="U323" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="V323" t="n">
         <v>0</v>
@@ -33551,61 +33551,61 @@
         <v>280</v>
       </c>
       <c r="C325" t="n">
-        <v>253</v>
+        <v>252.98058</v>
       </c>
       <c r="D325" t="n">
-        <v>251</v>
+        <v>251.48076</v>
       </c>
       <c r="E325" t="n">
-        <v>251</v>
+        <v>251.43306</v>
       </c>
       <c r="F325" t="n">
-        <v>252</v>
+        <v>251.74841</v>
       </c>
       <c r="G325" t="n">
-        <v>255</v>
+        <v>254.63338</v>
       </c>
       <c r="H325" t="n">
-        <v>252</v>
+        <v>252.06235</v>
       </c>
       <c r="I325" t="n">
-        <v>252</v>
+        <v>252.09558</v>
       </c>
       <c r="J325" t="n">
-        <v>246</v>
+        <v>246.33405</v>
       </c>
       <c r="K325" t="n">
-        <v>252</v>
+        <v>251.85924</v>
       </c>
       <c r="L325" t="n">
-        <v>246</v>
+        <v>245.67535</v>
       </c>
       <c r="M325" t="n">
+        <v>240.11668</v>
+      </c>
+      <c r="N325" t="n">
+        <v>232.37824</v>
+      </c>
+      <c r="O325" t="n">
         <v>240</v>
       </c>
-      <c r="N325" t="n">
-        <v>0</v>
-      </c>
-      <c r="O325" t="n">
-        <v>0</v>
-      </c>
       <c r="P325" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="Q325" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="R325" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="S325" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="T325" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="U325" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="V325" t="n">
         <v>0</v>
@@ -33757,61 +33757,61 @@
         <v>54.56099</v>
       </c>
       <c r="C327" t="n">
+        <v>31.94167</v>
+      </c>
+      <c r="D327" t="n">
+        <v>31.66607</v>
+      </c>
+      <c r="E327" t="n">
+        <v>31.99851</v>
+      </c>
+      <c r="F327" t="n">
+        <v>31.94893</v>
+      </c>
+      <c r="G327" t="n">
+        <v>31.8407</v>
+      </c>
+      <c r="H327" t="n">
+        <v>31.86093</v>
+      </c>
+      <c r="I327" t="n">
+        <v>31.46805</v>
+      </c>
+      <c r="J327" t="n">
+        <v>31.87953</v>
+      </c>
+      <c r="K327" t="n">
+        <v>31.31509</v>
+      </c>
+      <c r="L327" t="n">
+        <v>31.75279</v>
+      </c>
+      <c r="M327" t="n">
+        <v>31.63424</v>
+      </c>
+      <c r="N327" t="n">
+        <v>31.63783</v>
+      </c>
+      <c r="O327" t="n">
         <v>32</v>
       </c>
-      <c r="D327" t="n">
+      <c r="P327" t="n">
         <v>32</v>
       </c>
-      <c r="E327" t="n">
+      <c r="Q327" t="n">
         <v>32</v>
       </c>
-      <c r="F327" t="n">
+      <c r="R327" t="n">
         <v>32</v>
       </c>
-      <c r="G327" t="n">
+      <c r="S327" t="n">
+        <v>31</v>
+      </c>
+      <c r="T327" t="n">
         <v>32</v>
       </c>
-      <c r="H327" t="n">
-        <v>32</v>
-      </c>
-      <c r="I327" t="n">
-        <v>32</v>
-      </c>
-      <c r="J327" t="n">
-        <v>32</v>
-      </c>
-      <c r="K327" t="n">
-        <v>32</v>
-      </c>
-      <c r="L327" t="n">
-        <v>32</v>
-      </c>
-      <c r="M327" t="n">
-        <v>32</v>
-      </c>
-      <c r="N327" t="n">
-        <v>0</v>
-      </c>
-      <c r="O327" t="n">
-        <v>0</v>
-      </c>
-      <c r="P327" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
-      <c r="R327" t="n">
-        <v>0</v>
-      </c>
-      <c r="S327" t="n">
-        <v>0</v>
-      </c>
-      <c r="T327" t="n">
-        <v>0</v>
-      </c>
       <c r="U327" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V327" t="n">
         <v>0</v>
@@ -33963,61 +33963,61 @@
         <v>281</v>
       </c>
       <c r="C329" t="n">
+        <v>277.75403</v>
+      </c>
+      <c r="D329" t="n">
+        <v>277.21097</v>
+      </c>
+      <c r="E329" t="n">
+        <v>276.92224</v>
+      </c>
+      <c r="F329" t="n">
+        <v>276.93347</v>
+      </c>
+      <c r="G329" t="n">
+        <v>276.60867</v>
+      </c>
+      <c r="H329" t="n">
+        <v>248.96037</v>
+      </c>
+      <c r="I329" t="n">
+        <v>249.52303</v>
+      </c>
+      <c r="J329" t="n">
+        <v>249.65218</v>
+      </c>
+      <c r="K329" t="n">
+        <v>256.75113</v>
+      </c>
+      <c r="L329" t="n">
+        <v>276.06799</v>
+      </c>
+      <c r="M329" t="n">
+        <v>275.33884</v>
+      </c>
+      <c r="N329" t="n">
+        <v>276.04947</v>
+      </c>
+      <c r="O329" t="n">
+        <v>275</v>
+      </c>
+      <c r="P329" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>276</v>
+      </c>
+      <c r="R329" t="n">
+        <v>276</v>
+      </c>
+      <c r="S329" t="n">
+        <v>277</v>
+      </c>
+      <c r="T329" t="n">
         <v>278</v>
       </c>
-      <c r="D329" t="n">
-        <v>277</v>
-      </c>
-      <c r="E329" t="n">
-        <v>277</v>
-      </c>
-      <c r="F329" t="n">
-        <v>277</v>
-      </c>
-      <c r="G329" t="n">
-        <v>277</v>
-      </c>
-      <c r="H329" t="n">
-        <v>249</v>
-      </c>
-      <c r="I329" t="n">
-        <v>250</v>
-      </c>
-      <c r="J329" t="n">
-        <v>250</v>
-      </c>
-      <c r="K329" t="n">
-        <v>257</v>
-      </c>
-      <c r="L329" t="n">
-        <v>276</v>
-      </c>
-      <c r="M329" t="n">
-        <v>275</v>
-      </c>
-      <c r="N329" t="n">
-        <v>0</v>
-      </c>
-      <c r="O329" t="n">
-        <v>0</v>
-      </c>
-      <c r="P329" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
-      <c r="R329" t="n">
-        <v>0</v>
-      </c>
-      <c r="S329" t="n">
-        <v>0</v>
-      </c>
-      <c r="T329" t="n">
-        <v>0</v>
-      </c>
       <c r="U329" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="V329" t="n">
         <v>0</v>
@@ -34169,61 +34169,61 @@
         <v>281</v>
       </c>
       <c r="C331" t="n">
+        <v>277.13062</v>
+      </c>
+      <c r="D331" t="n">
+        <v>276.9184</v>
+      </c>
+      <c r="E331" t="n">
+        <v>276.20358</v>
+      </c>
+      <c r="F331" t="n">
+        <v>275.91882</v>
+      </c>
+      <c r="G331" t="n">
+        <v>275.95792</v>
+      </c>
+      <c r="H331" t="n">
+        <v>248.81505</v>
+      </c>
+      <c r="I331" t="n">
+        <v>248.8589</v>
+      </c>
+      <c r="J331" t="n">
+        <v>248.64636</v>
+      </c>
+      <c r="K331" t="n">
+        <v>256.5766</v>
+      </c>
+      <c r="L331" t="n">
+        <v>275.18216</v>
+      </c>
+      <c r="M331" t="n">
+        <v>275.75427</v>
+      </c>
+      <c r="N331" t="n">
+        <v>276.35532</v>
+      </c>
+      <c r="O331" t="n">
+        <v>278</v>
+      </c>
+      <c r="P331" t="n">
+        <v>276</v>
+      </c>
+      <c r="Q331" t="n">
         <v>277</v>
       </c>
-      <c r="D331" t="n">
-        <v>277</v>
-      </c>
-      <c r="E331" t="n">
-        <v>276</v>
-      </c>
-      <c r="F331" t="n">
-        <v>276</v>
-      </c>
-      <c r="G331" t="n">
-        <v>276</v>
-      </c>
-      <c r="H331" t="n">
-        <v>249</v>
-      </c>
-      <c r="I331" t="n">
-        <v>249</v>
-      </c>
-      <c r="J331" t="n">
-        <v>249</v>
-      </c>
-      <c r="K331" t="n">
-        <v>257</v>
-      </c>
-      <c r="L331" t="n">
-        <v>275</v>
-      </c>
-      <c r="M331" t="n">
-        <v>276</v>
-      </c>
-      <c r="N331" t="n">
-        <v>0</v>
-      </c>
-      <c r="O331" t="n">
-        <v>0</v>
-      </c>
-      <c r="P331" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="S331" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="T331" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="U331" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="V331" t="n">
         <v>0</v>
@@ -34581,61 +34581,61 @@
         <v>945</v>
       </c>
       <c r="C335" t="n">
+        <v>507.13162</v>
+      </c>
+      <c r="D335" t="n">
+        <v>503.54312</v>
+      </c>
+      <c r="E335" t="n">
+        <v>502.40231</v>
+      </c>
+      <c r="F335" t="n">
+        <v>502.00067</v>
+      </c>
+      <c r="G335" t="n">
+        <v>510.85318</v>
+      </c>
+      <c r="H335" t="n">
+        <v>502.78809</v>
+      </c>
+      <c r="I335" t="n">
+        <v>490.88525</v>
+      </c>
+      <c r="J335" t="n">
+        <v>495.07849</v>
+      </c>
+      <c r="K335" t="n">
+        <v>504.26581</v>
+      </c>
+      <c r="L335" t="n">
+        <v>496.73865</v>
+      </c>
+      <c r="M335" t="n">
+        <v>493.78253</v>
+      </c>
+      <c r="N335" t="n">
+        <v>493.20786</v>
+      </c>
+      <c r="O335" t="n">
+        <v>499</v>
+      </c>
+      <c r="P335" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>513</v>
+      </c>
+      <c r="R335" t="n">
+        <v>499</v>
+      </c>
+      <c r="S335" t="n">
+        <v>500</v>
+      </c>
+      <c r="T335" t="n">
+        <v>500</v>
+      </c>
+      <c r="U335" t="n">
         <v>507</v>
-      </c>
-      <c r="D335" t="n">
-        <v>504</v>
-      </c>
-      <c r="E335" t="n">
-        <v>502</v>
-      </c>
-      <c r="F335" t="n">
-        <v>502</v>
-      </c>
-      <c r="G335" t="n">
-        <v>511</v>
-      </c>
-      <c r="H335" t="n">
-        <v>503</v>
-      </c>
-      <c r="I335" t="n">
-        <v>491</v>
-      </c>
-      <c r="J335" t="n">
-        <v>495</v>
-      </c>
-      <c r="K335" t="n">
-        <v>504</v>
-      </c>
-      <c r="L335" t="n">
-        <v>497</v>
-      </c>
-      <c r="M335" t="n">
-        <v>494</v>
-      </c>
-      <c r="N335" t="n">
-        <v>0</v>
-      </c>
-      <c r="O335" t="n">
-        <v>0</v>
-      </c>
-      <c r="P335" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
-      <c r="R335" t="n">
-        <v>0</v>
-      </c>
-      <c r="S335" t="n">
-        <v>0</v>
-      </c>
-      <c r="T335" t="n">
-        <v>0</v>
-      </c>
-      <c r="U335" t="n">
-        <v>0</v>
       </c>
       <c r="V335" t="n">
         <v>0</v>
@@ -34787,61 +34787,61 @@
         <v>950</v>
       </c>
       <c r="C337" t="n">
-        <v>895</v>
+        <v>895.23688</v>
       </c>
       <c r="D337" t="n">
-        <v>896</v>
+        <v>895.61536</v>
       </c>
       <c r="E337" t="n">
-        <v>893</v>
+        <v>892.71857</v>
       </c>
       <c r="F337" t="n">
-        <v>894</v>
+        <v>893.53052</v>
       </c>
       <c r="G337" t="n">
-        <v>886</v>
+        <v>886.1058399999999</v>
       </c>
       <c r="H337" t="n">
-        <v>892</v>
+        <v>892.0835</v>
       </c>
       <c r="I337" t="n">
-        <v>894</v>
+        <v>893.92468</v>
       </c>
       <c r="J337" t="n">
-        <v>893</v>
+        <v>892.98877</v>
       </c>
       <c r="K337" t="n">
-        <v>906</v>
+        <v>906.15118</v>
       </c>
       <c r="L337" t="n">
+        <v>910.88525</v>
+      </c>
+      <c r="M337" t="n">
+        <v>910.55725</v>
+      </c>
+      <c r="N337" t="n">
+        <v>902.46686</v>
+      </c>
+      <c r="O337" t="n">
+        <v>904</v>
+      </c>
+      <c r="P337" t="n">
+        <v>912</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>902</v>
+      </c>
+      <c r="R337" t="n">
+        <v>909</v>
+      </c>
+      <c r="S337" t="n">
+        <v>914</v>
+      </c>
+      <c r="T337" t="n">
         <v>911</v>
       </c>
-      <c r="M337" t="n">
+      <c r="U337" t="n">
         <v>911</v>
-      </c>
-      <c r="N337" t="n">
-        <v>0</v>
-      </c>
-      <c r="O337" t="n">
-        <v>0</v>
-      </c>
-      <c r="P337" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
-      <c r="R337" t="n">
-        <v>0</v>
-      </c>
-      <c r="S337" t="n">
-        <v>0</v>
-      </c>
-      <c r="T337" t="n">
-        <v>0</v>
-      </c>
-      <c r="U337" t="n">
-        <v>0</v>
       </c>
       <c r="V337" t="n">
         <v>0</v>
@@ -34993,61 +34993,61 @@
         <v>950</v>
       </c>
       <c r="C339" t="n">
-        <v>892</v>
+        <v>892.37067</v>
       </c>
       <c r="D339" t="n">
-        <v>891</v>
+        <v>891.03436</v>
       </c>
       <c r="E339" t="n">
-        <v>889</v>
+        <v>888.93219</v>
       </c>
       <c r="F339" t="n">
-        <v>887</v>
+        <v>887.3905</v>
       </c>
       <c r="G339" t="n">
-        <v>893</v>
+        <v>892.63202</v>
       </c>
       <c r="H339" t="n">
-        <v>887</v>
+        <v>887.31549</v>
       </c>
       <c r="I339" t="n">
-        <v>889</v>
+        <v>888.85376</v>
       </c>
       <c r="J339" t="n">
-        <v>885</v>
+        <v>884.97205</v>
       </c>
       <c r="K339" t="n">
+        <v>906.89166</v>
+      </c>
+      <c r="L339" t="n">
+        <v>906.16742</v>
+      </c>
+      <c r="M339" t="n">
+        <v>906.61285</v>
+      </c>
+      <c r="N339" t="n">
+        <v>904.86298</v>
+      </c>
+      <c r="O339" t="n">
         <v>907</v>
       </c>
-      <c r="L339" t="n">
-        <v>906</v>
-      </c>
-      <c r="M339" t="n">
+      <c r="P339" t="n">
+        <v>904</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>909</v>
+      </c>
+      <c r="R339" t="n">
         <v>907</v>
       </c>
-      <c r="N339" t="n">
-        <v>0</v>
-      </c>
-      <c r="O339" t="n">
-        <v>0</v>
-      </c>
-      <c r="P339" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
-      <c r="R339" t="n">
-        <v>0</v>
-      </c>
       <c r="S339" t="n">
-        <v>0</v>
+        <v>911</v>
       </c>
       <c r="T339" t="n">
-        <v>0</v>
+        <v>909</v>
       </c>
       <c r="U339" t="n">
-        <v>0</v>
+        <v>902</v>
       </c>
       <c r="V339" t="n">
         <v>0</v>
@@ -35199,61 +35199,61 @@
         <v>1000</v>
       </c>
       <c r="C341" t="n">
-        <v>967</v>
+        <v>966.88953</v>
       </c>
       <c r="D341" t="n">
-        <v>978</v>
+        <v>978.4890799999999</v>
       </c>
       <c r="E341" t="n">
-        <v>977</v>
+        <v>976.99127</v>
       </c>
       <c r="F341" t="n">
-        <v>977</v>
+        <v>976.98596</v>
       </c>
       <c r="G341" t="n">
-        <v>977</v>
+        <v>977.19696</v>
       </c>
       <c r="H341" t="n">
-        <v>964</v>
+        <v>964.44013</v>
       </c>
       <c r="I341" t="n">
-        <v>929</v>
+        <v>928.83746</v>
       </c>
       <c r="J341" t="n">
-        <v>934</v>
+        <v>933.70447</v>
       </c>
       <c r="K341" t="n">
-        <v>977</v>
+        <v>977.36993</v>
       </c>
       <c r="L341" t="n">
-        <v>977</v>
+        <v>976.75952</v>
       </c>
       <c r="M341" t="n">
-        <v>980</v>
+        <v>980.34564</v>
       </c>
       <c r="N341" t="n">
-        <v>0</v>
+        <v>977.90527</v>
       </c>
       <c r="O341" t="n">
-        <v>0</v>
+        <v>932</v>
       </c>
       <c r="P341" t="n">
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="Q341" t="n">
-        <v>0</v>
+        <v>937</v>
       </c>
       <c r="R341" t="n">
-        <v>0</v>
+        <v>974</v>
       </c>
       <c r="S341" t="n">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="T341" t="n">
-        <v>0</v>
+        <v>971</v>
       </c>
       <c r="U341" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="V341" t="n">
         <v>0</v>
@@ -35405,61 +35405,61 @@
         <v>1000</v>
       </c>
       <c r="C343" t="n">
-        <v>972</v>
+        <v>971.6615</v>
       </c>
       <c r="D343" t="n">
+        <v>978.04089</v>
+      </c>
+      <c r="E343" t="n">
+        <v>972.77582</v>
+      </c>
+      <c r="F343" t="n">
+        <v>972.12225</v>
+      </c>
+      <c r="G343" t="n">
+        <v>977.03235</v>
+      </c>
+      <c r="H343" t="n">
+        <v>955.70892</v>
+      </c>
+      <c r="I343" t="n">
+        <v>930.2533</v>
+      </c>
+      <c r="J343" t="n">
+        <v>930.55261</v>
+      </c>
+      <c r="K343" t="n">
+        <v>976.4140599999999</v>
+      </c>
+      <c r="L343" t="n">
+        <v>974.15112</v>
+      </c>
+      <c r="M343" t="n">
+        <v>977.56091</v>
+      </c>
+      <c r="N343" t="n">
+        <v>981.68628</v>
+      </c>
+      <c r="O343" t="n">
+        <v>928</v>
+      </c>
+      <c r="P343" t="n">
+        <v>907</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>942</v>
+      </c>
+      <c r="R343" t="n">
+        <v>971</v>
+      </c>
+      <c r="S343" t="n">
         <v>978</v>
       </c>
-      <c r="E343" t="n">
-        <v>973</v>
-      </c>
-      <c r="F343" t="n">
-        <v>972</v>
-      </c>
-      <c r="G343" t="n">
-        <v>977</v>
-      </c>
-      <c r="H343" t="n">
-        <v>956</v>
-      </c>
-      <c r="I343" t="n">
-        <v>930</v>
-      </c>
-      <c r="J343" t="n">
-        <v>931</v>
-      </c>
-      <c r="K343" t="n">
-        <v>976</v>
-      </c>
-      <c r="L343" t="n">
-        <v>974</v>
-      </c>
-      <c r="M343" t="n">
-        <v>978</v>
-      </c>
-      <c r="N343" t="n">
-        <v>0</v>
-      </c>
-      <c r="O343" t="n">
-        <v>0</v>
-      </c>
-      <c r="P343" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
-      <c r="R343" t="n">
-        <v>0</v>
-      </c>
-      <c r="S343" t="n">
-        <v>0</v>
-      </c>
       <c r="T343" t="n">
-        <v>0</v>
+        <v>965</v>
       </c>
       <c r="U343" t="n">
-        <v>0</v>
+        <v>993</v>
       </c>
       <c r="V343" t="n">
         <v>0</v>
@@ -35611,61 +35611,61 @@
         <v>660.8</v>
       </c>
       <c r="C345" t="n">
-        <v>553</v>
+        <v>553.11414</v>
       </c>
       <c r="D345" t="n">
-        <v>411</v>
+        <v>410.56223</v>
       </c>
       <c r="E345" t="n">
-        <v>372</v>
+        <v>371.86826</v>
       </c>
       <c r="F345" t="n">
-        <v>374</v>
+        <v>373.72067</v>
       </c>
       <c r="G345" t="n">
-        <v>376</v>
+        <v>375.57623</v>
       </c>
       <c r="H345" t="n">
-        <v>375</v>
+        <v>375.19461</v>
       </c>
       <c r="I345" t="n">
-        <v>376</v>
+        <v>375.96747</v>
       </c>
       <c r="J345" t="n">
-        <v>374</v>
+        <v>373.99728</v>
       </c>
       <c r="K345" t="n">
-        <v>373</v>
+        <v>372.90762</v>
       </c>
       <c r="L345" t="n">
-        <v>377</v>
+        <v>376.85407</v>
       </c>
       <c r="M345" t="n">
-        <v>436</v>
+        <v>436.0621</v>
       </c>
       <c r="N345" t="n">
-        <v>0</v>
+        <v>532.32239</v>
       </c>
       <c r="O345" t="n">
-        <v>0</v>
+        <v>629</v>
       </c>
       <c r="P345" t="n">
-        <v>0</v>
+        <v>654</v>
       </c>
       <c r="Q345" t="n">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="R345" t="n">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="S345" t="n">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="T345" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="U345" t="n">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="V345" t="n">
         <v>0</v>
@@ -35817,61 +35817,61 @@
         <v>660.8</v>
       </c>
       <c r="C347" t="n">
-        <v>646</v>
+        <v>645.75958</v>
       </c>
       <c r="D347" t="n">
+        <v>644.0153800000001</v>
+      </c>
+      <c r="E347" t="n">
+        <v>645.81476</v>
+      </c>
+      <c r="F347" t="n">
+        <v>645.24377</v>
+      </c>
+      <c r="G347" t="n">
+        <v>644.76978</v>
+      </c>
+      <c r="H347" t="n">
+        <v>645.17755</v>
+      </c>
+      <c r="I347" t="n">
+        <v>646.84174</v>
+      </c>
+      <c r="J347" t="n">
+        <v>647.1051</v>
+      </c>
+      <c r="K347" t="n">
+        <v>650.52191</v>
+      </c>
+      <c r="L347" t="n">
+        <v>646.87763</v>
+      </c>
+      <c r="M347" t="n">
+        <v>644.20557</v>
+      </c>
+      <c r="N347" t="n">
+        <v>643.27564</v>
+      </c>
+      <c r="O347" t="n">
+        <v>642</v>
+      </c>
+      <c r="P347" t="n">
         <v>644</v>
       </c>
-      <c r="E347" t="n">
-        <v>646</v>
-      </c>
-      <c r="F347" t="n">
+      <c r="Q347" t="n">
         <v>645</v>
       </c>
-      <c r="G347" t="n">
-        <v>645</v>
-      </c>
-      <c r="H347" t="n">
-        <v>645</v>
-      </c>
-      <c r="I347" t="n">
-        <v>647</v>
-      </c>
-      <c r="J347" t="n">
-        <v>647</v>
-      </c>
-      <c r="K347" t="n">
+      <c r="R347" t="n">
+        <v>644</v>
+      </c>
+      <c r="S347" t="n">
         <v>651</v>
       </c>
-      <c r="L347" t="n">
-        <v>647</v>
-      </c>
-      <c r="M347" t="n">
-        <v>644</v>
-      </c>
-      <c r="N347" t="n">
-        <v>0</v>
-      </c>
-      <c r="O347" t="n">
-        <v>0</v>
-      </c>
-      <c r="P347" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
-      <c r="R347" t="n">
-        <v>0</v>
-      </c>
-      <c r="S347" t="n">
-        <v>0</v>
-      </c>
       <c r="T347" t="n">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="U347" t="n">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="V347" t="n">
         <v>0</v>
@@ -36023,61 +36023,61 @@
         <v>661.1</v>
       </c>
       <c r="C349" t="n">
+        <v>643.16968</v>
+      </c>
+      <c r="D349" t="n">
+        <v>640.91632</v>
+      </c>
+      <c r="E349" t="n">
+        <v>639.76465</v>
+      </c>
+      <c r="F349" t="n">
+        <v>639.95502</v>
+      </c>
+      <c r="G349" t="n">
+        <v>639.55988</v>
+      </c>
+      <c r="H349" t="n">
+        <v>644.21729</v>
+      </c>
+      <c r="I349" t="n">
+        <v>644.09192</v>
+      </c>
+      <c r="J349" t="n">
+        <v>644.46765</v>
+      </c>
+      <c r="K349" t="n">
+        <v>645.93481</v>
+      </c>
+      <c r="L349" t="n">
+        <v>637.8006</v>
+      </c>
+      <c r="M349" t="n">
+        <v>644.38843</v>
+      </c>
+      <c r="N349" t="n">
+        <v>637.78351</v>
+      </c>
+      <c r="O349" t="n">
+        <v>642</v>
+      </c>
+      <c r="P349" t="n">
+        <v>644</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>644</v>
+      </c>
+      <c r="R349" t="n">
+        <v>647</v>
+      </c>
+      <c r="S349" t="n">
+        <v>648</v>
+      </c>
+      <c r="T349" t="n">
         <v>643</v>
       </c>
-      <c r="D349" t="n">
-        <v>641</v>
-      </c>
-      <c r="E349" t="n">
-        <v>640</v>
-      </c>
-      <c r="F349" t="n">
-        <v>640</v>
-      </c>
-      <c r="G349" t="n">
-        <v>640</v>
-      </c>
-      <c r="H349" t="n">
-        <v>644</v>
-      </c>
-      <c r="I349" t="n">
-        <v>644</v>
-      </c>
-      <c r="J349" t="n">
-        <v>644</v>
-      </c>
-      <c r="K349" t="n">
-        <v>646</v>
-      </c>
-      <c r="L349" t="n">
-        <v>638</v>
-      </c>
-      <c r="M349" t="n">
-        <v>644</v>
-      </c>
-      <c r="N349" t="n">
-        <v>0</v>
-      </c>
-      <c r="O349" t="n">
-        <v>0</v>
-      </c>
-      <c r="P349" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
-      <c r="R349" t="n">
-        <v>0</v>
-      </c>
-      <c r="S349" t="n">
-        <v>0</v>
-      </c>
-      <c r="T349" t="n">
-        <v>0</v>
-      </c>
       <c r="U349" t="n">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="V349" t="n">
         <v>0</v>
@@ -36229,61 +36229,61 @@
         <v>661.1</v>
       </c>
       <c r="C351" t="n">
+        <v>637.32654</v>
+      </c>
+      <c r="D351" t="n">
+        <v>630.8673700000001</v>
+      </c>
+      <c r="E351" t="n">
+        <v>636.7027</v>
+      </c>
+      <c r="F351" t="n">
+        <v>633.76996</v>
+      </c>
+      <c r="G351" t="n">
+        <v>636.4547700000001</v>
+      </c>
+      <c r="H351" t="n">
+        <v>639.1403800000001</v>
+      </c>
+      <c r="I351" t="n">
+        <v>637.6922</v>
+      </c>
+      <c r="J351" t="n">
+        <v>639.69251</v>
+      </c>
+      <c r="K351" t="n">
+        <v>639.77478</v>
+      </c>
+      <c r="L351" t="n">
+        <v>636.75317</v>
+      </c>
+      <c r="M351" t="n">
+        <v>636.61414</v>
+      </c>
+      <c r="N351" t="n">
+        <v>628.9765</v>
+      </c>
+      <c r="O351" t="n">
+        <v>635</v>
+      </c>
+      <c r="P351" t="n">
+        <v>633</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>636</v>
+      </c>
+      <c r="R351" t="n">
         <v>637</v>
       </c>
-      <c r="D351" t="n">
-        <v>631</v>
-      </c>
-      <c r="E351" t="n">
+      <c r="S351" t="n">
+        <v>640</v>
+      </c>
+      <c r="T351" t="n">
         <v>637</v>
       </c>
-      <c r="F351" t="n">
-        <v>634</v>
-      </c>
-      <c r="G351" t="n">
-        <v>636</v>
-      </c>
-      <c r="H351" t="n">
+      <c r="U351" t="n">
         <v>639</v>
-      </c>
-      <c r="I351" t="n">
-        <v>638</v>
-      </c>
-      <c r="J351" t="n">
-        <v>640</v>
-      </c>
-      <c r="K351" t="n">
-        <v>640</v>
-      </c>
-      <c r="L351" t="n">
-        <v>637</v>
-      </c>
-      <c r="M351" t="n">
-        <v>637</v>
-      </c>
-      <c r="N351" t="n">
-        <v>0</v>
-      </c>
-      <c r="O351" t="n">
-        <v>0</v>
-      </c>
-      <c r="P351" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
-      <c r="R351" t="n">
-        <v>0</v>
-      </c>
-      <c r="S351" t="n">
-        <v>0</v>
-      </c>
-      <c r="T351" t="n">
-        <v>0</v>
-      </c>
-      <c r="U351" t="n">
-        <v>0</v>
       </c>
       <c r="V351" t="n">
         <v>0</v>
@@ -37400,28 +37400,28 @@
         <v>54</v>
       </c>
       <c r="N363" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="O363" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="P363" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Q363" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="R363" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="S363" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="T363" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="U363" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="V363" t="n">
         <v>0</v>
@@ -37615,19 +37615,19 @@
         <v>0</v>
       </c>
       <c r="Q365" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R365" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S365" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="T365" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="U365" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="V365" t="n">
         <v>0</v>
@@ -37833,7 +37833,7 @@
         <v>0</v>
       </c>
       <c r="U367" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V367" t="n">
         <v>0</v>
@@ -38018,28 +38018,28 @@
         <v>106</v>
       </c>
       <c r="N369" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="O369" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="P369" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="Q369" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R369" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S369" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="T369" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U369" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="V369" t="n">
         <v>0</v>
@@ -39048,28 +39048,28 @@
         <v>31</v>
       </c>
       <c r="N379" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O379" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P379" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q379" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R379" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="S379" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="T379" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="U379" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V379" t="n">
         <v>0</v>
@@ -39460,7 +39460,7 @@
         <v>10</v>
       </c>
       <c r="N383" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O383" t="n">
         <v>0</v>
@@ -39475,13 +39475,13 @@
         <v>0</v>
       </c>
       <c r="S383" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T383" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U383" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V383" t="n">
         <v>0</v>
@@ -39870,28 +39870,28 @@
         <v>8</v>
       </c>
       <c r="N387" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O387" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P387" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q387" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R387" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S387" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T387" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U387" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V387" t="n">
         <v>0</v>
@@ -40074,28 +40074,28 @@
         <v>6</v>
       </c>
       <c r="N389" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O389" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P389" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q389" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R389" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S389" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T389" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U389" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V389" t="n">
         <v>0</v>
@@ -40280,28 +40280,28 @@
         <v>2</v>
       </c>
       <c r="N391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V391" t="n">
         <v>0</v>
@@ -40507,7 +40507,7 @@
         <v>0</v>
       </c>
       <c r="U393" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V393" t="n">
         <v>0</v>
@@ -41722,28 +41722,28 @@
         <v>91</v>
       </c>
       <c r="N405" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="O405" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="P405" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="Q405" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="R405" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="S405" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="T405" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="U405" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="V405" t="n">
         <v>0</v>
@@ -41928,28 +41928,28 @@
         <v>90</v>
       </c>
       <c r="N407" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O407" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="P407" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q407" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="R407" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="S407" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="T407" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="U407" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="V407" t="n">
         <v>0</v>
@@ -42134,28 +42134,28 @@
         <v>322</v>
       </c>
       <c r="N409" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="O409" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="P409" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="Q409" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="R409" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="S409" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="T409" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="U409" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="V409" t="n">
         <v>0</v>
@@ -42340,28 +42340,28 @@
         <v>311</v>
       </c>
       <c r="N411" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="O411" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="P411" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="Q411" t="n">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="R411" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="S411" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="T411" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="U411" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="V411" t="n">
         <v>0</v>
@@ -42958,28 +42958,28 @@
         <v>65</v>
       </c>
       <c r="N417" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="O417" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="P417" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Q417" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R417" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="S417" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="T417" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="U417" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="V417" t="n">
         <v>0</v>
@@ -43164,28 +43164,28 @@
         <v>49</v>
       </c>
       <c r="N419" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="O419" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P419" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Q419" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="R419" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S419" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="T419" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="U419" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="V419" t="n">
         <v>0</v>
@@ -43370,28 +43370,28 @@
         <v>49</v>
       </c>
       <c r="N421" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O421" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="P421" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Q421" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R421" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="S421" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="T421" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="U421" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="V421" t="n">
         <v>0</v>
@@ -43579,25 +43579,25 @@
         <v>0</v>
       </c>
       <c r="O423" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P423" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Q423" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="R423" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="S423" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="T423" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="U423" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V423" t="n">
         <v>0</v>
@@ -43782,28 +43782,28 @@
         <v>39</v>
       </c>
       <c r="N425" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O425" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P425" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q425" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R425" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S425" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T425" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="U425" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="V425" t="n">
         <v>0</v>
@@ -44400,28 +44400,28 @@
         <v>79</v>
       </c>
       <c r="N431" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="O431" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="P431" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="Q431" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="R431" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="S431" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="T431" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="U431" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="V431" t="n">
         <v>0</v>
@@ -44606,28 +44606,28 @@
         <v>38</v>
       </c>
       <c r="N433" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="O433" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="P433" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Q433" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="R433" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S433" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T433" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="U433" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="V433" t="n">
         <v>0</v>
@@ -44812,28 +44812,28 @@
         <v>76</v>
       </c>
       <c r="N435" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="O435" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="P435" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="Q435" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="R435" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="S435" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T435" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="U435" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="V435" t="n">
         <v>0</v>
@@ -45838,13 +45838,13 @@
         <v>1</v>
       </c>
       <c r="N445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q445" t="n">
         <v>0</v>
@@ -46042,7 +46042,7 @@
         <v>1</v>
       </c>
       <c r="N447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O447" t="n">
         <v>0</v>
@@ -46248,28 +46248,28 @@
         <v>1</v>
       </c>
       <c r="N449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V449" t="n">
         <v>0</v>
@@ -46454,28 +46454,28 @@
         <v>278</v>
       </c>
       <c r="N451" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="O451" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="P451" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="Q451" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="R451" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="S451" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="T451" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="U451" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="V451" t="n">
         <v>0</v>
@@ -46866,28 +46866,28 @@
         <v>588</v>
       </c>
       <c r="N455" t="n">
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="O455" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="P455" t="n">
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="Q455" t="n">
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="R455" t="n">
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="S455" t="n">
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="T455" t="n">
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="U455" t="n">
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="V455" t="n">
         <v>0</v>
@@ -47072,28 +47072,28 @@
         <v>204</v>
       </c>
       <c r="N457" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="O457" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="P457" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="Q457" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="R457" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="S457" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="T457" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="U457" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="V457" t="n">
         <v>0</v>
@@ -48102,28 +48102,28 @@
         <v>595</v>
       </c>
       <c r="N467" t="n">
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="O467" t="n">
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="P467" t="n">
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="Q467" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="R467" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="S467" t="n">
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="T467" t="n">
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="U467" t="n">
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="V467" t="n">
         <v>0</v>
@@ -48308,28 +48308,28 @@
         <v>606</v>
       </c>
       <c r="N469" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="O469" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="P469" t="n">
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="Q469" t="n">
-        <v>0</v>
+        <v>595</v>
       </c>
       <c r="R469" t="n">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="S469" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="T469" t="n">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="U469" t="n">
-        <v>0</v>
+        <v>605</v>
       </c>
       <c r="V469" t="n">
         <v>0</v>
@@ -48481,61 +48481,61 @@
         <v>811</v>
       </c>
       <c r="C471" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D471" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E471" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F471" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G471" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H471" t="n">
+        <v>0</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0</v>
+      </c>
+      <c r="J471" t="n">
+        <v>0</v>
+      </c>
+      <c r="K471" t="n">
+        <v>0</v>
+      </c>
+      <c r="L471" t="n">
+        <v>0</v>
+      </c>
+      <c r="M471" t="n">
+        <v>0</v>
+      </c>
+      <c r="N471" t="n">
+        <v>0</v>
+      </c>
+      <c r="O471" t="n">
+        <v>0</v>
+      </c>
+      <c r="P471" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>0</v>
+      </c>
+      <c r="R471" t="n">
+        <v>0</v>
+      </c>
+      <c r="S471" t="n">
+        <v>0</v>
+      </c>
+      <c r="T471" t="n">
         <v>23</v>
       </c>
-      <c r="I471" t="n">
-        <v>22</v>
-      </c>
-      <c r="J471" t="n">
-        <v>22</v>
-      </c>
-      <c r="K471" t="n">
-        <v>22</v>
-      </c>
-      <c r="L471" t="n">
-        <v>22</v>
-      </c>
-      <c r="M471" t="n">
-        <v>22</v>
-      </c>
-      <c r="N471" t="n">
-        <v>0</v>
-      </c>
-      <c r="O471" t="n">
-        <v>0</v>
-      </c>
-      <c r="P471" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q471" t="n">
-        <v>0</v>
-      </c>
-      <c r="R471" t="n">
-        <v>0</v>
-      </c>
-      <c r="S471" t="n">
-        <v>0</v>
-      </c>
-      <c r="T471" t="n">
-        <v>0</v>
-      </c>
       <c r="U471" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V471" t="n">
         <v>0</v>
@@ -48720,28 +48720,28 @@
         <v>603</v>
       </c>
       <c r="N473" t="n">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="O473" t="n">
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="P473" t="n">
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="Q473" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="R473" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="S473" t="n">
-        <v>0</v>
+        <v>595</v>
       </c>
       <c r="T473" t="n">
-        <v>0</v>
+        <v>587</v>
       </c>
       <c r="U473" t="n">
-        <v>0</v>
+        <v>597</v>
       </c>
       <c r="V473" t="n">
         <v>0</v>
@@ -49132,28 +49132,28 @@
         <v>33</v>
       </c>
       <c r="N477" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O477" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="P477" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q477" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R477" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="S477" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="T477" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="U477" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="V477" t="n">
         <v>0</v>
@@ -49658,28 +49658,28 @@
         <v>6.14</v>
       </c>
       <c r="P483" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Q483" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="R483" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S483" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="T483" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="U483" t="n">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="V483" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W483" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="X483" t="n">
         <v>0</v>
@@ -50482,28 +50482,28 @@
         <v>100.37</v>
       </c>
       <c r="P491" t="n">
-        <v>0</v>
+        <v>100.4</v>
       </c>
       <c r="Q491" t="n">
-        <v>0</v>
+        <v>100.35</v>
       </c>
       <c r="R491" t="n">
-        <v>0</v>
+        <v>100.2</v>
       </c>
       <c r="S491" t="n">
-        <v>0</v>
+        <v>100.45</v>
       </c>
       <c r="T491" t="n">
-        <v>0</v>
+        <v>99.95</v>
       </c>
       <c r="U491" t="n">
-        <v>0</v>
+        <v>99.81</v>
       </c>
       <c r="V491" t="n">
-        <v>0</v>
+        <v>100.23</v>
       </c>
       <c r="W491" t="n">
-        <v>0</v>
+        <v>100.47</v>
       </c>
       <c r="X491" t="n">
         <v>0</v>
@@ -50688,28 +50688,28 @@
         <v>85.87</v>
       </c>
       <c r="P493" t="n">
-        <v>0</v>
+        <v>85.8</v>
       </c>
       <c r="Q493" t="n">
-        <v>0</v>
+        <v>86.34</v>
       </c>
       <c r="R493" t="n">
-        <v>0</v>
+        <v>85.88</v>
       </c>
       <c r="S493" t="n">
-        <v>0</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="T493" t="n">
-        <v>0</v>
+        <v>85.78</v>
       </c>
       <c r="U493" t="n">
-        <v>0</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="V493" t="n">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="W493" t="n">
-        <v>0</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="X493" t="n">
         <v>0</v>
@@ -50906,16 +50906,16 @@
         <v>0</v>
       </c>
       <c r="T495" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="U495" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V495" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="W495" t="n">
-        <v>0</v>
+        <v>41.4</v>
       </c>
       <c r="X495" t="n">
         <v>0</v>
@@ -51924,28 +51924,28 @@
         <v>12.86</v>
       </c>
       <c r="P505" t="n">
-        <v>0</v>
+        <v>14.09</v>
       </c>
       <c r="Q505" t="n">
-        <v>0</v>
+        <v>13.88</v>
       </c>
       <c r="R505" t="n">
-        <v>0</v>
+        <v>13.59</v>
       </c>
       <c r="S505" t="n">
-        <v>0</v>
+        <v>13.13</v>
       </c>
       <c r="T505" t="n">
-        <v>0</v>
+        <v>13.87</v>
       </c>
       <c r="U505" t="n">
-        <v>0</v>
+        <v>15.67</v>
       </c>
       <c r="V505" t="n">
-        <v>0</v>
+        <v>14.78</v>
       </c>
       <c r="W505" t="n">
-        <v>0</v>
+        <v>14.56</v>
       </c>
       <c r="X505" t="n">
         <v>0</v>
@@ -52130,28 +52130,28 @@
         <v>14.17</v>
       </c>
       <c r="P507" t="n">
-        <v>0</v>
+        <v>14.33</v>
       </c>
       <c r="Q507" t="n">
-        <v>0</v>
+        <v>14.24</v>
       </c>
       <c r="R507" t="n">
-        <v>0</v>
+        <v>13.87</v>
       </c>
       <c r="S507" t="n">
-        <v>0</v>
+        <v>15.07</v>
       </c>
       <c r="T507" t="n">
-        <v>0</v>
+        <v>14.47</v>
       </c>
       <c r="U507" t="n">
-        <v>0</v>
+        <v>15.19</v>
       </c>
       <c r="V507" t="n">
-        <v>0</v>
+        <v>15.31</v>
       </c>
       <c r="W507" t="n">
-        <v>0</v>
+        <v>14.28</v>
       </c>
       <c r="X507" t="n">
         <v>0</v>
@@ -52336,28 +52336,28 @@
         <v>13.54</v>
       </c>
       <c r="P509" t="n">
-        <v>0</v>
+        <v>14.72</v>
       </c>
       <c r="Q509" t="n">
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="R509" t="n">
-        <v>0</v>
+        <v>14.79</v>
       </c>
       <c r="S509" t="n">
-        <v>0</v>
+        <v>14.27</v>
       </c>
       <c r="T509" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="U509" t="n">
-        <v>0</v>
+        <v>14.77</v>
       </c>
       <c r="V509" t="n">
-        <v>0</v>
+        <v>14.81</v>
       </c>
       <c r="W509" t="n">
-        <v>0</v>
+        <v>14.79</v>
       </c>
       <c r="X509" t="n">
         <v>0</v>
@@ -52748,28 +52748,28 @@
         <v>15.53</v>
       </c>
       <c r="P513" t="n">
-        <v>0</v>
+        <v>14.87</v>
       </c>
       <c r="Q513" t="n">
-        <v>0</v>
+        <v>14.45</v>
       </c>
       <c r="R513" t="n">
-        <v>0</v>
+        <v>14.52</v>
       </c>
       <c r="S513" t="n">
-        <v>0</v>
+        <v>14.84</v>
       </c>
       <c r="T513" t="n">
-        <v>0</v>
+        <v>14.83</v>
       </c>
       <c r="U513" t="n">
-        <v>0</v>
+        <v>13.95</v>
       </c>
       <c r="V513" t="n">
-        <v>0</v>
+        <v>13.95</v>
       </c>
       <c r="W513" t="n">
-        <v>0</v>
+        <v>14.52</v>
       </c>
       <c r="X513" t="n">
         <v>0</v>
@@ -52954,28 +52954,28 @@
         <v>14.63</v>
       </c>
       <c r="P515" t="n">
-        <v>0</v>
+        <v>15.71</v>
       </c>
       <c r="Q515" t="n">
-        <v>0</v>
+        <v>14.94</v>
       </c>
       <c r="R515" t="n">
-        <v>0</v>
+        <v>15.08</v>
       </c>
       <c r="S515" t="n">
-        <v>0</v>
+        <v>14.98</v>
       </c>
       <c r="T515" t="n">
-        <v>0</v>
+        <v>14.22</v>
       </c>
       <c r="U515" t="n">
-        <v>0</v>
+        <v>15.28</v>
       </c>
       <c r="V515" t="n">
-        <v>0</v>
+        <v>14.72</v>
       </c>
       <c r="W515" t="n">
-        <v>0</v>
+        <v>15.06</v>
       </c>
       <c r="X515" t="n">
         <v>0</v>
@@ -53366,28 +53366,28 @@
         <v>13.24</v>
       </c>
       <c r="P519" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q519" t="n">
-        <v>0</v>
+        <v>13.59</v>
       </c>
       <c r="R519" t="n">
-        <v>0</v>
+        <v>14.13</v>
       </c>
       <c r="S519" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="T519" t="n">
-        <v>0</v>
+        <v>14.12</v>
       </c>
       <c r="U519" t="n">
-        <v>0</v>
+        <v>14.85</v>
       </c>
       <c r="V519" t="n">
-        <v>0</v>
+        <v>14.37</v>
       </c>
       <c r="W519" t="n">
-        <v>0</v>
+        <v>14.61</v>
       </c>
       <c r="X519" t="n">
         <v>0</v>
@@ -53572,28 +53572,28 @@
         <v>13.19</v>
       </c>
       <c r="P521" t="n">
-        <v>0</v>
+        <v>13.78</v>
       </c>
       <c r="Q521" t="n">
-        <v>0</v>
+        <v>13.64</v>
       </c>
       <c r="R521" t="n">
-        <v>0</v>
+        <v>13.69</v>
       </c>
       <c r="S521" t="n">
-        <v>0</v>
+        <v>13.85</v>
       </c>
       <c r="T521" t="n">
-        <v>0</v>
+        <v>13.94</v>
       </c>
       <c r="U521" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="V521" t="n">
-        <v>0</v>
+        <v>13.82</v>
       </c>
       <c r="W521" t="n">
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="X521" t="n">
         <v>0</v>
@@ -54190,28 +54190,28 @@
         <v>14.62</v>
       </c>
       <c r="P527" t="n">
-        <v>0</v>
+        <v>14.11</v>
       </c>
       <c r="Q527" t="n">
-        <v>0</v>
+        <v>14.04</v>
       </c>
       <c r="R527" t="n">
-        <v>0</v>
+        <v>14.14</v>
       </c>
       <c r="S527" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="T527" t="n">
-        <v>0</v>
+        <v>14.51</v>
       </c>
       <c r="U527" t="n">
-        <v>0</v>
+        <v>15.23</v>
       </c>
       <c r="V527" t="n">
-        <v>0</v>
+        <v>14.77</v>
       </c>
       <c r="W527" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="X527" t="n">
         <v>0</v>
@@ -54396,28 +54396,28 @@
         <v>90.54000000000001</v>
       </c>
       <c r="P529" t="n">
-        <v>0</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="Q529" t="n">
-        <v>0</v>
+        <v>95.02</v>
       </c>
       <c r="R529" t="n">
-        <v>0</v>
+        <v>105.63</v>
       </c>
       <c r="S529" t="n">
-        <v>0</v>
+        <v>113.95</v>
       </c>
       <c r="T529" t="n">
-        <v>0</v>
+        <v>114.91</v>
       </c>
       <c r="U529" t="n">
-        <v>0</v>
+        <v>124.37</v>
       </c>
       <c r="V529" t="n">
-        <v>0</v>
+        <v>123.26</v>
       </c>
       <c r="W529" t="n">
-        <v>0</v>
+        <v>124.02</v>
       </c>
       <c r="X529" t="n">
         <v>0</v>
@@ -54602,28 +54602,28 @@
         <v>90.89</v>
       </c>
       <c r="P531" t="n">
-        <v>0</v>
+        <v>89.36</v>
       </c>
       <c r="Q531" t="n">
-        <v>0</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="R531" t="n">
-        <v>0</v>
+        <v>104.98</v>
       </c>
       <c r="S531" t="n">
-        <v>0</v>
+        <v>114.49</v>
       </c>
       <c r="T531" t="n">
-        <v>0</v>
+        <v>114.52</v>
       </c>
       <c r="U531" t="n">
-        <v>0</v>
+        <v>124.89</v>
       </c>
       <c r="V531" t="n">
-        <v>0</v>
+        <v>124.07</v>
       </c>
       <c r="W531" t="n">
-        <v>0</v>
+        <v>125.16</v>
       </c>
       <c r="X531" t="n">
         <v>0</v>
@@ -54808,28 +54808,28 @@
         <v>90.5</v>
       </c>
       <c r="P533" t="n">
-        <v>0</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="Q533" t="n">
-        <v>0</v>
+        <v>94.64</v>
       </c>
       <c r="R533" t="n">
-        <v>0</v>
+        <v>106.44</v>
       </c>
       <c r="S533" t="n">
-        <v>0</v>
+        <v>114.03</v>
       </c>
       <c r="T533" t="n">
-        <v>0</v>
+        <v>116.08</v>
       </c>
       <c r="U533" t="n">
-        <v>0</v>
+        <v>129.57</v>
       </c>
       <c r="V533" t="n">
-        <v>0</v>
+        <v>128.41</v>
       </c>
       <c r="W533" t="n">
-        <v>0</v>
+        <v>127.61</v>
       </c>
       <c r="X533" t="n">
         <v>0</v>
@@ -55032,10 +55032,10 @@
         <v>0</v>
       </c>
       <c r="V535" t="n">
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="W535" t="n">
-        <v>0</v>
+        <v>46.15</v>
       </c>
       <c r="X535" t="n">
         <v>0</v>
@@ -55426,28 +55426,28 @@
         <v>0.4</v>
       </c>
       <c r="P539" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q539" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="R539" t="n">
-        <v>0</v>
+        <v>10.29</v>
       </c>
       <c r="S539" t="n">
-        <v>0</v>
+        <v>14.94</v>
       </c>
       <c r="T539" t="n">
-        <v>0</v>
+        <v>18.22</v>
       </c>
       <c r="U539" t="n">
-        <v>0</v>
+        <v>19.54</v>
       </c>
       <c r="V539" t="n">
-        <v>0</v>
+        <v>20.28</v>
       </c>
       <c r="W539" t="n">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="X539" t="n">
         <v>0</v>
@@ -55635,25 +55635,25 @@
         <v>0</v>
       </c>
       <c r="Q541" t="n">
-        <v>0</v>
+        <v>20.15</v>
       </c>
       <c r="R541" t="n">
-        <v>0</v>
+        <v>20.1</v>
       </c>
       <c r="S541" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="T541" t="n">
-        <v>0</v>
+        <v>20.3</v>
       </c>
       <c r="U541" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V541" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W541" t="n">
-        <v>0</v>
+        <v>50.74</v>
       </c>
       <c r="X541" t="n">
         <v>0</v>
@@ -55847,19 +55847,19 @@
         <v>0</v>
       </c>
       <c r="S543" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T543" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="U543" t="n">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="V543" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W543" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="X543" t="n">
         <v>0</v>
@@ -56003,67 +56003,67 @@
       </c>
       <c r="B545" t="inlineStr"/>
       <c r="C545" t="n">
-        <v>28252.25</v>
+        <v>28118.61572</v>
       </c>
       <c r="D545" t="n">
-        <v>27983.22</v>
+        <v>27857.74357</v>
       </c>
       <c r="E545" t="n">
-        <v>27769.14</v>
+        <v>27639.75396</v>
       </c>
       <c r="F545" t="n">
-        <v>27447.14</v>
+        <v>27323.40449</v>
       </c>
       <c r="G545" t="n">
-        <v>27186.56</v>
+        <v>27059.08196</v>
       </c>
       <c r="H545" t="n">
-        <v>26872.16</v>
+        <v>26750.3714</v>
       </c>
       <c r="I545" t="n">
-        <v>26775.62</v>
+        <v>26659.13854</v>
       </c>
       <c r="J545" t="n">
-        <v>26905.08</v>
+        <v>26792.97473</v>
       </c>
       <c r="K545" t="n">
-        <v>27562.91</v>
+        <v>27442.55232</v>
       </c>
       <c r="L545" t="n">
-        <v>28034.1</v>
+        <v>27906.56081</v>
       </c>
       <c r="M545" t="n">
-        <v>28644.16</v>
+        <v>28511.79451</v>
       </c>
       <c r="N545" t="n">
-        <v>563.8200000000001</v>
+        <v>28172.01592</v>
       </c>
       <c r="O545" t="n">
-        <v>576.49</v>
+        <v>28041.49</v>
       </c>
       <c r="P545" t="n">
-        <v>0</v>
+        <v>28054.64</v>
       </c>
       <c r="Q545" t="n">
-        <v>0</v>
+        <v>29214.74</v>
       </c>
       <c r="R545" t="n">
-        <v>0</v>
+        <v>30137.61</v>
       </c>
       <c r="S545" t="n">
-        <v>0</v>
+        <v>31281.08</v>
       </c>
       <c r="T545" t="n">
-        <v>0</v>
+        <v>31768.87</v>
       </c>
       <c r="U545" t="n">
-        <v>0</v>
+        <v>32344.89</v>
       </c>
       <c r="V545" t="n">
-        <v>0</v>
+        <v>817.23</v>
       </c>
       <c r="W545" t="n">
-        <v>0</v>
+        <v>852.4</v>
       </c>
       <c r="X545" t="n">
         <v>0</v>
